--- a/docs/datasheets/FSAE-Sim Parameters.xlsx
+++ b/docs/datasheets/FSAE-Sim Parameters.xlsx
@@ -504,12 +504,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -591,7 +591,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>environment.g</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -606,12 +606,12 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>m/s²</t>
+          <t>m/s^2</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>constant</t>
+          <t>CONSTANT (physical)</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -638,12 +638,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>ρ</t>
+          <t>rho</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>RHO_AIR</t>
+          <t>environment.rho_air</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>kg/m³</t>
+          <t>kg/m^3</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Downforce and drag are ½ρ·(coeff·A)·v² — 5% density = 5% aero.</t>
+          <t>Downforce and drag are 0.5*rho*(coeff*A)*v^2 — 5% density = 5% aero.</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>CAR_MASS_NO_DRIVER</t>
+          <t>mass.car_no_driver</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>kg (400.1 lb)</t>
+          <t>kg (weighed as 400.1 lb)</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Corner scales (Intercomp SW500): 87.5/86.3/114.8/111.5 lb</t>
+          <t>Corner scales (E-Z Weight Intercomp SW500), no driver: LF 87.5 lb, RF 86.3 lb (front pair 173.8 lb = 43.44%); LR 114.8 lb, RR 111.5 lb (rear pair 226.3 lb); total 400.1 lb, left 50.56%, cross (RF+LR) 50.26%. Left/right is 0.56% asymmetric (~1 kg heavier left) — the sim assumes perfect L/R symmetry; at that size the error is noise. Cross weight is a setup number this sim does not use; recorded for the suspension crew.</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -754,12 +754,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>DRIVER_MASS</t>
+          <t>mass.driver</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Driver in full gear (suit, helmet, shoes). Convention: use the HEAVIEST regular driver.</t>
+          <t>Driver in full gear (suit, helmet, shoes). Convention: use the HEAVIEST regular driver for conservative tuning.</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>kg (entered 156 lb)</t>
+          <t>kg (entered as 156 lb)</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
@@ -789,93 +789,92 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>The car never runs without one. Confirm 156 lb is heaviest + includes gear (~5–8 lb).</t>
+          <t>The car never runs without one. Confirm 156 lb is the heaviest driver and includes gear (~5-8 lb).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Total mass (computed)</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>m_total</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>mass.total</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Total vehicle mass with the driver seated.</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>252.2</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>DERIVED (car + driver, never entered directly)</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="3">
+        <f> mass.car_no_driver + mass.driver</f>
+        <v/>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>The mass every inertial term in the equations of motion uses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>GEOMETRY &amp; CG</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Wheelbase</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>WHEELBASE</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Front-axle to rear-axle distance.</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>FROM REPORT (2023 car)</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>Axle-center to axle-center distance</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>Tape measure / CAD</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>Sets yaw geometry, the bicycle-model reference, and CG position math.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Front track</t>
+          <t>Wheelbase</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>t_f</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>TRACK_FRONT</t>
+          <t>geometry.wheelbase</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Distance between the two FRONT contact-patch centers.</t>
+          <t>Front-axle to rear-axle centerline distance.</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -885,12 +884,12 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>FROM REPORT</t>
+          <t>FROM REPORT (2023 car)</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Center-of-tire to center-of-tire, front</t>
+          <t>Axle-center to axle-center distance</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -900,29 +899,29 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Lever arm for front lateral load transfer.</t>
+          <t>Sets yaw geometry, the bicycle-model reference, and CG position math.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Rear track</t>
+          <t>Front track</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>t_r</t>
+          <t>t_f</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>TRACK_REAR</t>
+          <t>geometry.track_front</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Same, rear axle.</t>
+          <t>Front track width — distance between the CENTERS of the two front tire contact patches (NOT outside-to-outside of the tires).</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -942,7 +941,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Center-of-tire to center-of-tire, rear</t>
+          <t>Center-of-tire to center-of-tire, front</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -952,1794 +951,1835 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>THE torque-vectoring lever arm: Mz = (t_r/2)·ΔFx. Bigger track = more yaw per N·m of split.</t>
+          <t>Lever arm for front lateral load transfer.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Front weight fraction</t>
+          <t>Rear track</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>%front</t>
+          <t>t_r</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>WEIGHT_FRACTION_FRONT</t>
+          <t>geometry.track_rear</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Share of total weight on the front axle, driver seated.</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>0.4344</t>
+          <t>Rear track width, same definition as front.</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>1.34</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>0–1</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>MEASURED 2026-08-31 (scales, NO driver)</t>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>FROM REPORT</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Front axle share WITH DRIVER SEATED (expect ~1–2% lower than the 43.44% car-only)</t>
+          <t>Center-of-tire to center-of-tire, rear</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Repeat the corner-scale session with the driver in the seat</t>
+          <t>Tape measure / CAD</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Decides how much grip each axle owns — understeer/oversteer balance starts here.</t>
+          <t>THE torque-vectoring lever arm: Mz = (t_r/2)*dFx. Bigger track = more yaw per N*m of split.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>CG height</t>
+          <t>Front weight fraction</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>pct_front</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>H_CG</t>
+          <t>geometry.weight_fraction_front</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Height of the center of gravity above ground.</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>0.23</t>
+          <t>Static front weight fraction = front axle weight / total weight. By statics this equals (CG-to-REAR-axle distance)/wheelbase.</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>0.4344</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>FROM REPORT</t>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED 2026-08-31 (scales, NO driver — redo seated)</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>CG height</t>
+          <t>Front axle share WITH DRIVER SEATED (expect ~1-2% lower than the 43.44% car-only number, so roughly 41.5-43%)</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Tilt test (weigh one axle while lifting the other) or CAD</t>
+          <t>Repeat the corner-scale session with the driver in the seat</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Drives ALL load transfer — every grip shift in braking, accel, and cornering is proportional to h.</t>
+          <t>Decides how much grip each axle owns — understeer/oversteer balance starts here.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
+          <t>CG height</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>geometry.h_cg</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Height of the center of gravity above the ground.</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>FROM REPORT</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>CG height</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Tilt test (weigh one axle while lifting the other) or CAD</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Drives ALL load transfer — every grip shift in braking, accel and cornering is proportional to h.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
           <t>Yaw inertia</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>I_z</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>I_Z</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Resistance of the whole car to changing its yaw (spin) rate.</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>geometry.I_z</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Yaw moment of inertia of the whole vehicle about the vertical axis through the CG. Sets how fast yaw rate responds to the TV yaw moment.</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>70.38</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>kg·m²</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>kg*m^2</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>FROM REPORT</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>Yaw moment of inertia</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>CAD mass model (practical) or trifilar pendulum test</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>Sets how fast the car responds to the TV yaw moment — directly in Iz·ṙ = ΣMz.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Directly in Iz*rdot = sum(Mz) — how fast the car answers a yaw moment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>WHEELS &amp; DRIVETRAIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Tire radius (loaded)</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>r_w</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>WHEEL_RADIUS</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Ground-to-axle-center distance with the car's weight on the tire.</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>0.2286</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>m (18" OD / 2)</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT CAR</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>Axle-center height, car on the ground</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>Ruler to the axle center</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>Converts wheel torque to drive force (F = T/r) and wheel speed to ground speed. Loaded is a few mm less than free.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Upright planetary ratio</t>
+          <t>Tire outer diameter</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>gr</t>
+          <t>d_w</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>GEAR_RATIO</t>
+          <t>drivetrain.tire_outer_diameter</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Reduction of the planetary gear stage in each upright, motor shaft → wheel.</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>13</t>
+          <t>Outer diameter of the fitted tire. wheel_radius is derived from it.</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>0.4572</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>FROM REPORT ⚠ confirm with powertrain</t>
+          <t>m (18 in OD)</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (18in tire OD, 10in rim)</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>The planetary's reduction ratio</t>
+          <t>Confirmed tire size</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Ask powertrain / count gear teeth in CAD</t>
+          <t>Tire sidewall / team spec</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Wheel torque = motor torque × gr; reflected rotor inertia = rotor J × gr². The 21 N·m motor is useless without it.</t>
+          <t>The rim size does not enter the sim — only the tire's rolling radius does.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Motor peak torque</t>
+          <t>Tire radius (loaded)</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>T_pk</t>
+          <t>r_w</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>MOTOR_TORQUE_PEAK</t>
+          <t>drivetrain.wheel_radius</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Peak torque of ONE motor at its shaft.</t>
+          <t>LOADED tire radius — ground to axle center with the car's weight on the tire.</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0.2286</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>N·m</t>
+          <t>m (18 in OD / 2)</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>CURRENT CAR (AMK kit datasheet)</t>
+          <t>CURRENT CAR</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Nothing (datasheet value)</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>AMK kit manual §6.5.3; dyno confirms someday</t>
-        </is>
+          <t>Axle-center height, car on the ground</t>
+        </is>
+      </c>
+      <c r="I18" s="3">
+        <f> drivetrain.tire_outer_diameter / 2.0</f>
+        <v/>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>×13 gear = 273 N·m per wheel — the ceiling every torque command lives under.</t>
+          <t>Converts wheel torque to drive force (F = T/r) and wheel speed to ground speed. Loaded radius is a few mm less than free radius (tire squish) — measure axle-center height with the car on the ground to refine.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Pack voltage</t>
+          <t>Upright planetary ratio</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>V_DC</t>
+          <t>gr</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>PACK_VOLTAGE</t>
+          <t>drivetrain.gear_ratio</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Accumulator nominal voltage.</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>380</t>
+          <t>Total reduction between motor shaft and wheel (motor revs per wheel rev). With one motor PER WHEEL this is the PLANETARY gear stage packaged in each upright with the motor — not a chain or gearbox.</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT CAR (design decision)</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>FROM REPORT — confirm upright planetary ratio</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Nothing (design value)</t>
+          <t>The planetary's reduction ratio</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Accumulator design</t>
+          <t>Ask powertrain / count gear teeth in CAD</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Sets motor peak power. 4 motors × ~20 kW @ 380 V = 80 kW = the rules cap exactly — sized for the 4WD end state.</t>
+          <t>Wheel torque = motor torque * gr; reflected rotor inertia = rotor J * gr^2. The 21 N*m motor is useless without it — direct drive would give 92 N of drive force per wheel (0.08 g) and a 479 m/s speed match.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Motor peak power</t>
+          <t>Motor peak torque</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>P_pk</t>
+          <t>T_pk</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>MOTOR_POWER_PEAK</t>
+          <t>drivetrain.motor_torque_peak</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Peak mechanical power of ONE motor at OUR pack voltage.</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>20,000</t>
+          <t>Peak torque of ONE motor at its shaft (before the gear reduction).</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>21</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>DERIVED (kit curves scaled to 380 V)</t>
+          <t>N*m</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (AMK kit datasheet)</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Actual peak power at 380 V</t>
+          <t>Nothing (datasheet value)</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Read the 380 V curve in the AMK manual; dyno pull once the pack exists</t>
+          <t>AMK kit manual 6.5.3 torque curve; dyno confirms someday</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>Caps torque above ~17 m/s (37 mph): at 40 mph only 256 of 273 N·m is available. 2-rear build tops out ~40 kW.</t>
+          <t>x13 gear = 273 N*m per wheel — the ceiling every torque command lives under.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Motor max speed</t>
+          <t>Pack voltage</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>n_max</t>
+          <t>V_DC</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>MOTOR_MAX_SPEED</t>
+          <t>drivetrain.pack_voltage</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Maximum motor shaft speed.</t>
+          <t>Accumulator (HV pack) nominal voltage.</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>2,094</t>
+          <t>380</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>rad/s (20,000 rpm)</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>CURRENT CAR (AMK kit datasheet)</t>
+          <t>CURRENT CAR (design decision 2026-08-30)</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Nothing (datasheet value)</t>
+          <t>Nothing (design value)</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>AMK kit manual</t>
-        </is>
-      </c>
-      <c r="J21" s="3">
-        <f> ~36 m/s (80 mph) ground speed at 13:1 — comfortably above the 40 mph envelope, not the limiter.</f>
-        <v/>
+          <t>Accumulator design</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Not used directly by the physics — it SETS motor peak power below. 4 motors x ~20 kW at 380 V = 80 kW exactly (the 4WD end state); the current 2-rear build tops out at ~40 kW, so the 80 kW cap is unreachable until 4WD.</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Wheel spin inertia</t>
+          <t>Motor peak power</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>I_w</t>
+          <t>P_pk</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>I_WHEEL</t>
+          <t>drivetrain.motor_power_peak</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Spin inertia of one rear corner: tire + rim + hub + brake rotor + motor rotor × gr².</t>
+          <t>Peak mechanical power of ONE motor at OUR pack voltage.</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>kg·m²</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>DERIVED estimate ⚠ replace with CAD</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>DERIVED (kit curves scaled to 380 V)</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Rotating inertia of one corner</t>
+          <t>Actual peak power at 380 V</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>CAD mass properties + rotor J from the exact AMK motor sheet</t>
+          <t>Read the 380 V curve in the AMK manual; dyno pull once the pack exists</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>Sets how fast an unloaded wheel spins up — the s-diff's whole problem. Controller gains are sensitive to it: retune when it changes.</t>
+          <t>Caps torque above ~17 m/s (37 mph): at 40 mph only 256 of 273 N*m is available. The 2-rear build tops out around 40 kW.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Total power cap</t>
+          <t>Motor max speed</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>P_max</t>
+          <t>n_max</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>POWER_CAP_TOTAL</t>
+          <t>drivetrain.motor_max_speed</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>FSAE EV rules limit on total drive power (EV.4.2).</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>80,000</t>
+          <t>Maximum motor shaft speed.</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>2,094</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>RULES VALUE</t>
+          <t>rad/s (entered as 20,000 rpm)</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (AMK kit datasheet)</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Nothing (rulebook)</t>
+          <t>Nothing (datasheet value)</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Confirm in the current-year rulebook</t>
+          <t>AMK kit manual 6.5.3 (characteristics end at 20,000 rpm)</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>Hard ceiling. Sim applies it to mechanical power (no drivetrain losses modeled) — real car hits it ~10–15% earlier.</t>
+          <t>~36 m/s (80 mph) ground speed at 13:1 — comfortably above the 40 mph envelope, not the limiter. NOT enforced by this basic sim; recorded for completeness and future top-speed studies.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Regen speed cutoff</t>
+          <t>Wheel spin inertia</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>I_w</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>REGEN_SPEED_CUTOFF</t>
+          <t>drivetrain.I_wheel</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Below this speed no negative (regen) torque is commanded.</t>
+          <t>Spin inertia of ONE rear corner about the axle: tire + rim + brake rotor + hub + (motor rotor inertia * gear_ratio^2).</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>m/s (≈5 km/h)</t>
+          <t>kg*m^2</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>RULES VALUE</t>
+          <t>DERIVED estimate — replace with CAD</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
+          <t>Rotating inertia of one corner</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>CAD mass properties + rotor J from the exact AMK motor sheet</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Sets how fast an unloaded wheel spins up — the s-diff's whole problem. Controller gains are sensitive to it: retune when it changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Total power cap</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>P_max</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>drivetrain.power_cap_total</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>FSAE EV rules limit on total drive power (EV.4.2, 80 kW at the accumulator).</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>80,000</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>RULES VALUE (simplified)</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
           <t>Nothing (rulebook)</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>Confirm in the current-year rulebook</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>Rules restrict regen near standstill; also keeps the sim's low-speed slip math out of its untrustworthy zone.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>AERO</t>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>Hard ceiling. The sim applies it to mechanical power (no drivetrain losses modeled) — the real car hits it ~10-15% earlier.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Lift coefficient</t>
+          <t>Regen speed cutoff</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>C_L</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>CL_COEFF</t>
+          <t>drivetrain.regen_speed_cutoff</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Downforce coefficient, referenced to the frontal area.</t>
+          <t>Below this speed no negative (regen) torque is commanded.</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>m/s (~5 km/h)</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>FROM REPORT (old car's aero)</t>
+          <t>RULES VALUE (approx.)</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Current car's downforce coefficient</t>
+          <t>Nothing (rulebook)</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>CFD, then straight-line coast-down / load-cell validation</t>
+          <t>Confirm in the current-year rulebook</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>Downforce = ½ρ·C_L·A·v² — free grip that grows with speed².</t>
+          <t>Rules restrict regen near standstill; also keeps the sim's low-speed slip math out of its untrustworthy zone.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Drag coefficient</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>C_D</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>CD_COEFF</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Aerodynamic drag coefficient, same reference area.</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>FROM REPORT (old car's aero)</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>Current car's drag coefficient</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>CFD + coast-down test</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>Sets top-speed force budget and the torque needed to hold speed in every maneuver.</t>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>AERO</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Frontal area</t>
+          <t>Lift coefficient</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>A_F</t>
+          <t>C_L</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>FRONTAL_AREA</t>
+          <t>aero.cl_coeff</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Aerodynamic reference area.</t>
+          <t>Lift (downforce) coefficient, referenced to frontal_area.</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>1.106</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>FROM REPORT</t>
+          <t>FROM REPORT (old car's aero)</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Projected frontal area</t>
+          <t>Current car's downforce coefficient</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>CAD projection</t>
+          <t>CFD, then straight-line coast-down / load-cell validation</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>Only the products C·A enter the physics — keep coefficient and area consistent with each other.</t>
+          <t>Downforce = 0.5*rho*C_L*A*v^2 — free grip that grows with speed^2.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>ClA (computed)</t>
+          <t>Drag coefficient</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>C_L·A</t>
+          <t>C_D</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>CLA</t>
+          <t>aero.cd_coeff</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>The downforce product the sim actually uses.</t>
+          <t>Drag coefficient, same reference area.</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>3.517</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>FROM REPORT (old car's aero)</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I29" s="3">
-        <f> C_L × A_F, never edited directly</f>
-        <v/>
+          <t>Current car's drag coefficient</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>CFD + coast-down test</t>
+        </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sets top-speed force budget and the torque needed to hold speed in every maneuver.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>CdA (computed)</t>
+          <t>Frontal area</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>C_D·A</t>
+          <t>A_F</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>aero.frontal_area</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>The drag product the sim actually uses.</t>
+          <t>Aerodynamic frontal reference area.</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>1.106</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m^2</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>FROM REPORT</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I30" s="3">
-        <f> C_D × A_F, never edited directly</f>
-        <v/>
+          <t>Projected frontal area</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>CAD projection</t>
+        </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Only the products C*A enter the physics — keep coefficient and area consistent.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Aero balance</t>
+          <t>ClA (computed)</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>%aero_f</t>
+          <t>C_L*A</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>AERO_BALANCE_FRONT</t>
+          <t>aero.ClA</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Fraction of total downforce landing on the FRONT axle.</t>
+          <t>The downforce product the sim actually uses.</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>3.517</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>0–1</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER ⚠ pure guess</t>
+          <t>m^2</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Center-of-pressure position</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>CFD (aero team) — ask for CP height too</t>
-        </is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I31" s="3">
+        <f> aero.cl_coeff * aero.frontal_area</f>
+        <v/>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>Moves grip between axles as speed rises — shapes high-speed balance directly. One of the last pure guesses outside tires.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>STEERING GEOMETRY</t>
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>CdA (computed)</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>C_D*A</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>aero.CdA</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>The drag product the sim actually uses.</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>1.504</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>m^2</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I32" s="3">
+        <f> aero.cd_coeff * aero.frontal_area</f>
+        <v/>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Ackermann fraction</t>
+          <t>Aero balance</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>%A</t>
+          <t>pct_aero_f</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>ACKERMANN_FRACTION</t>
+          <t>aero.balance_front</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>How much of the geometric inner/outer steer split the linkage delivers (0 = parallel, 1 = full Ackermann).</t>
+          <t>Fraction of total downforce landing on the FRONT axle (0.45 = 45/55).</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (parallel) ⚠ RWheel curve needed</t>
+          <t>PLACEHOLDER — pure guess</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>The steering curve: both wheels' angles vs handwheel angle</t>
+          <t>Center-of-pressure position</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>From the steering chart: LWheel curve is on file, need the RWheel polynomial from the same chart</t>
+          <t>CFD (aero team) — ask for CP height too</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>±4°/wheel at the 23° full lock; proven to flip whether s-diff-only survives the hairpin (runs 007 vs 008).</t>
+          <t>Moves grip between axles as speed rises — shapes high-speed balance directly. One of the last pure guesses outside tires.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>SENSORS &amp; VCU — what the controller is allowed to know (sensors.py)</t>
+          <t>STEERING GEOMETRY</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>VCU loop rate</t>
+          <t>Ackermann fraction</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>pct_A</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>VCU_RATE_HZ</t>
+          <t>steering.ackermann_fraction</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>How often sensors are sampled and torque is recomputed (physics runs at 4 kHz regardless).</t>
+          <t>How much of the geometric (100%) Ackermann inner/outer steer split the steering actually delivers. 0.0 = parallel steer (both fronts get the same angle), 1.0 = full geometric Ackermann, negative = anti-Ackermann.</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Hz</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>PLACEHOLDER ⚠ ask software team</t>
+          <t>PLACEHOLDER (parallel) — RWheel curve needed</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>The real VCU loop rate</t>
+          <t>The steering curve: both wheels' angles vs handwheel angle</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Software team</t>
+          <t>From the steering chart: the LWheel curve is on file, need the RWheel polynomial from the same chart (or a few x, LWheel, RWheel point triples).</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>Gains proven stable at 100 Hz; make it match reality before quoting controller performance.</t>
+          <t>Only matters at large steer angles: at 5 deg the split is ~+/-0.2 deg; at the 23 deg full-lock hairpin it is ~+/-4 deg per wheel. Proven to flip whether s-diff-only survives the hairpin (runs 007 vs 008).</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Steering map A0/A1/A2</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>y=A0+A1x+A2x²</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>STEER_MAP_A0/A1/A2</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>Handwheel angle → road-wheel angle, the team chart's LWheel curve (centered, odd-extended).</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>−0.0797 / 0.31 / −8.44E-04</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>deg→deg</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT CAR (team chart)</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>The steering curve incl. RWheel</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>Steering chart / kinematics sweep</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>How the VCU turns the SAS reading into a road-wheel angle. Full lock 23° ≈ 103° handwheel.</t>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>LOAD TRANSFER</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>SAS quantization</t>
+          <t>Front spring rate</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ks_f</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>SAS_QUANT_DEG</t>
+          <t>loads.spring_rate_front</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Steering-angle sensor resolution at the handwheel.</t>
+          <t>Front suspension spring rate. Used ONLY through its ratio to the rear.</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>deg/LSB</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+          <t>N/mm (ratio only)</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>FROM REPORT</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Sensor spec</t>
+          <t>Front roll stiffness incl. ARBs and motion ratios</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Datasheet of the chosen SAS</t>
+          <t>Suspension team</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>Steering resolution the VCU actually sees.</t>
+          <t>Numerator of the lateral load-transfer split.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>WSS quantization</t>
+          <t>Rear spring rate</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ks_r</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>WSS_QUANT_RPM</t>
+          <t>loads.spring_rate_rear</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Motor-speed resolution over CAN (WSS = motor resolver ÷ planetary ratio).</t>
+          <t>Rear suspension spring rate. Used ONLY through its ratio to the front.</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>rpm/LSB</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+          <t>N/mm (ratio only)</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>FROM REPORT</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>AMK CAN speed resolution</t>
+          <t>Rear roll stiffness incl. ARBs and motion ratios</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>AMK CAN spec</t>
+          <t>Suspension team</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1 motor rpm ≈ 1.8 mm/s ground speed — effectively noise-free wheel speed.</t>
+          <t>Denominator half of the lateral load-transfer split.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>IMU gyro noise / bias</t>
+          <t>Front lateral-transfer fraction</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>σ, b</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>IMU_GYRO_NOISE_STD / _BIAS</t>
+          <t>loads.lat_transfer_frac_front</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Yaw-gyro 1σ noise and constant bias.</t>
+          <t>Share of total LATERAL load transfer reacted by the FRONT axle, set by the front/rear roll-stiffness split.</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>0.3 / 0.1 °/s</t>
+          <t>0.4376</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>rad/s</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>FROM REPORT (spring-rate ratio only) — crude</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>IMU datasheet numbers</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>Chosen IMU's spec sheet</t>
-        </is>
+          <t>Front vs rear roll stiffness</t>
+        </is>
+      </c>
+      <c r="I39" s="3">
+        <f> loads.spring_rate_front / (loads.spring_rate_front + loads.spring_rate_rear)</f>
+        <v/>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>Goes straight into the TV feedback — sets how clean the yaw control can be.</t>
+          <t>Which axle eats the load transfer = which axle loses grip first — trades understeer/oversteer at the limit.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>IMU accel noise</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>σ</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>IMU_ACCEL_NOISE_STD</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>Accelerometer 1σ noise (ax, ay).</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>m/s²</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>IMU datasheet</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>Spec sheet</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>Feeds future estimation (vx observer, validation logging).</t>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>TIRES — TTC ROUND 9 FIT (R20 compound, 2026-08-31); surrogate sizes, road µ = belt × 0.67 pending skidpad</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>VCU gyro low-pass</t>
+          <t>Belt→road grip scale</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>f_c</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>IMU_LPF_HZ</t>
+          <t>tires.mu_road_scale</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>First-order filter the VCU applies to the gyro before feedback.</t>
+          <t>Belt-&gt;asphalt grip scaling. Calspan's sandpaper belt grips harder than track asphalt; common practice scales the fitted peak mu by ~0.65-0.70 for on-road prediction (stiffnesses/shapes carry over unscaled).</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Hz</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>PLACEHOLDER</t>
+          <t>PLACEHOLDER — skidpad measures this</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Steady-state skidpad lateral g</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>Software choice; tune against noise</t>
+          <t>Skidpad test vs sim prediction</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>Trade: more filtering = less dither but more phase lag in the yaw loop.</t>
+          <t>Multiplies EVERY grip number — the single biggest absolute-accuracy lever left. VALIDATE on skidpad; that measurement replaces this guess with truth.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>APPS quantization</t>
+          <t>Belt peak µ, lateral</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mu_belt_y</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>APPS_QUANT_PCT</t>
+          <t>tires.belt_mu_lat</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Accelerator pedal position resolution. Pedal map: 100% = full axle torque.</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>0.5</t>
+          <t>Peak LATERAL friction coefficient as fitted on the Calspan belt.</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>2.593</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>%/LSB</t>
-        </is>
-      </c>
-      <c r="G42" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>TTC FIT R9</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>APPS sensor spec</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>Datasheet</t>
+          <t>tire_fit.py on Round 9 cornering runs (surrogate spread +/-6%)</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>Torque request granularity.</t>
+          <t>Scaled by mu_road_scale to give the road value the sim uses.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>BPS range / quant / actuated</t>
+          <t>Belt peak µ, longitudinal</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mu_belt_x</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>BPS_RANGE_BAR / _QUANT_BAR / _ACTUATED_BAR</t>
+          <t>tires.belt_mu_long</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Brake pressure sensor range, resolution, and the pressure that counts as 'braking' for the rules check.</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>100 / 0.5 / 3 bar</t>
+          <t>Peak LONGITUDINAL friction coefficient as fitted on the belt.</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>2.359</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="G43" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>TTC FIT R9</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>BPS spec + brake system pressures</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>Brake team: line pressure at threshold/full braking</t>
+          <t>tire_fit.py on Round 9 drive/brake runs</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>Defines braking for regen mapping and EV.4.7.</t>
+          <t>Scaled by mu_road_scale to give the road value the sim uses.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Max regen torque</t>
+          <t>Peak friction coefficient</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mu0</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>T_REGEN_MAX</t>
+          <t>tires.mu0</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Total rear-axle regen torque at full brake pressure (mechanical brakes NOT modeled).</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>250</t>
+          <t>Peak grip per newton of load, at the nominal load (road value).</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>1.737</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>N·m</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER ⚠ battery charge limit sets this</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>TTC FIT R9</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Allowed charge current → torque</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>Accumulator team: max charge C-rate</t>
-        </is>
+          <t>Peak mu at several loads</t>
+        </is>
+      </c>
+      <c r="I44" s="3">
+        <f> tires.mu_road_scale * tires.belt_mu_lat</f>
+        <v/>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>Caps how much 'braking' the sim's BPS can command.</t>
+          <t>THE grip number. Max lateral g, spin thresholds, everything — the single most important number in the sim.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Plausibility thresholds</t>
+          <t>Peak longitudinal friction</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mu0x</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>PLAUS_APPS_CUT / _RESTORE</t>
+          <t>tires.mu0_long</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>FSAE EV.4.7: &gt;25% APPS while braking cuts power until APPS &lt;5%.</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>25 / 5</t>
+          <t>Drive/brake grip peak — fitted 9% below lateral; combined slip caps on the friction ELLIPSE in tire.py.</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>1.581</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>RULES VALUE</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>TTC FIT R9</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>Rulebook (confirm current year)</t>
-        </is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I45" s="3">
+        <f> tires.mu_road_scale * tires.belt_mu_long</f>
+        <v/>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>Implemented and unit-tested (verify I3); pedal_check maneuver demonstrates it.</t>
+          <t>Sets wheelspin threshold and traction capability.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Sensor noise seed</t>
+          <t>Load sensitivity</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>s_mu</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>SENSOR_SEED</t>
+          <t>tires.s_mu</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Seed for the noise generator — runs repeatable, all configs see identical noise.</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>2026</t>
+          <t>Load sensitivity — how much the friction COEFFICIENT drops as vertical load rises: mu = mu0 * (1 - s_mu*(Fz/Fz_nom - 1)). Shared by the lateral and longitudinal peaks.</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>0.112</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>NUMERICAL GUARD</t>
+          <t>—/100% load</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>TTC FIT R9</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mu at low vs high load</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Same TTC fit</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>Fair comparisons and reproducible runs.</t>
+          <t>The reason load transfer costs grip and torque placement matters at all. Zero would make TV pointless.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>LOAD TRANSFER</t>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Nominal tire load</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Fz_nom</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>tires.Fz_nom</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>The "nominal" vertical load at which mu0 is defined (~one static corner weight).</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>618.6</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>DERIVED (follows the masses automatically)</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I47" s="3">
+        <f> (mass.car_no_driver + mass.driver) * environment.g / 4.0</f>
+        <v/>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>Reference point for the load-sensitivity line.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Front lateral-transfer fraction</t>
+          <t>Front cornering stiffness</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>c_alpha_f</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>LAT_TRANSFER_FRAC_FRONT</t>
+          <t>tires.c_alpha_front</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Share of total lateral load transfer reacted by the FRONT axle (roll-stiffness split).</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>0.4376</t>
+          <t>Normalized cornering stiffness of a FRONT tire: lateral force per radian of slip angle, per newton of load (C_alpha = this * Fz).</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>37</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>0–1</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="inlineStr">
-        <is>
-          <t>FROM REPORT (spring-rate ratio only) ⚠ crude</t>
+          <t>1/rad</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>TTC FIT R9 (same tire all round)</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Front vs rear roll stiffness</t>
+          <t>Slope of Fy vs slip angle at small angles</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>Suspension team: roll rates incl. ARBs, motion ratios, roll-center heights</t>
+          <t>TTC cornering sweep</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>Which axle eats the load transfer = which axle loses grip first — trades understeer/oversteer at the limit.</t>
+          <t>Front-axle responsiveness; with rear stiffness sets the understeer gradient K_us the TV reference uses.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TIRES — TTC ROUND 9 FIT (R20 compound, 2026-08-31) — surrogate sizes; road µ = belt × 0.67 pending skidpad</t>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Rear cornering stiffness</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>c_alpha_r</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>tires.c_alpha_rear</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Same, for a REAR tire.</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>1/rad</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>TTC FIT R9 (same tire all round)</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Same, rear</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>TTC cornering sweep</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>Rear grip slope — stability side of the understeer gradient.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Belt→road grip scale</t>
+          <t>Longitudinal slip stiffness</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>c_kappa</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>TIRE_MU_ROAD_SCALE</t>
+          <t>tires.c_kappa</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Calspan's belt grips harder than asphalt; peak µ scaled by this for road prediction.</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>0.67</t>
+          <t>Normalized longitudinal slip stiffness: drive/brake force per unit slip ratio per newton (C_kappa = this * Fz).</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>41.9</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER ⚠ skidpad measures this</t>
+          <t>1/slip</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>TTC FIT R9</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Steady-state skidpad lateral g</t>
+          <t>Slope of Fx vs slip ratio</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>Skidpad test vs sim prediction</t>
+          <t>TTC drive/brake sweep</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>Multiplies EVERY grip number — the single biggest absolute-accuracy lever left.</t>
+          <t>Sets wheel-spin dynamics speed — the s-diff's plant. Gains retune if it moves.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Peak longitudinal friction</t>
+          <t>Lateral shape factor</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>µ₀x</t>
+          <t>C_y</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>TIRE_MU0_LONG</t>
+          <t>tires.shape_c_lat</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Drive/brake grip peak — fitted 9% below lateral; combined slip caps on the friction ELLIPSE.</t>
+          <t>Magic Formula shape factor — how sharply lateral force peaks.</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>1.581</t>
+          <t>1.397</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
@@ -2749,49 +2789,49 @@
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Curve shape near/past the peak</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>tire_fit.py on Round 9 drive/brake runs</t>
+          <t>TTC fit</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>Sets wheelspin threshold and traction capability.</t>
+          <t>With E_y, sets where the curve peaks (currently 11.6 deg — real slicks ~6-10 deg) and how it lets go.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Peak friction coefficient</t>
+          <t>Lateral curvature factor</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>µ₀</t>
+          <t>E_y</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>TIRE_MU0</t>
+          <t>tires.curv_e_lat</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Peak grip per newton of load, at the nominal load.</t>
+          <t>Magic Formula curvature factor — fall-off past the lateral peak.</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>1.737</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
@@ -2801,49 +2841,49 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Peak µ at several loads</t>
+          <t>Post-peak behavior</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>TTC data fit (if access ever appears) or skidpad testing</t>
+          <t>TTC fit</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>THE grip number. Max lateral g, spin thresholds, everything — the single most important number in the sim.</t>
+          <t>Gentle vs snappy breakaway — currently more forgiving than a real slick.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Load sensitivity</t>
+          <t>Longitudinal shape factor</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>s_µ</t>
+          <t>C_x</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>TIRE_S_MU</t>
+          <t>tires.shape_c_long</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>How fast the grip COEFFICIENT falls as load rises.</t>
+          <t>Same idea, drive/brake direction.</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>1.705</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>—/100% load</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
@@ -2853,996 +2893,1676 @@
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>µ at low vs high load</t>
+          <t>Curve shape</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>Same TTC fit</t>
+          <t>TTC fit</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>The reason load transfer costs grip and torque placement matters at all. Zero would make TV pointless.</t>
+          <t>Sets the peak slip ratio (~0.10) — also the replay's red-wheel spin threshold.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Nominal tire load</t>
+          <t>Longitudinal curvature factor</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Fz_nom</t>
+          <t>E_x</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>TIRE_FZ_NOM</t>
+          <t>tires.curv_e_long</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>The load at which µ₀ is defined (≈ one static corner weight).</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>618.6</t>
+          <t>Fall-off past the longitudinal peak.</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>0.389</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t>DERIVED (follows the masses automatically)</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>TTC FIT R9</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I54" s="3">
-        <f> (m_car + m_driver)·g / 4</f>
-        <v/>
+          <t>Post-peak behavior</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>TTC fit</t>
+        </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>Reference point for the load-sensitivity line.</t>
+          <t>How violently a spinning wheel loses force — feeds the wheelspin runaway.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>Front cornering stiffness</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>c_α,f</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>TIRE_C_ALPHA_FRONT</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>Lateral force per radian of slip angle, per newton of load (front tire).</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>1/rad</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>TTC FIT R9</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>Slope of Fy vs slip angle at small angles</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>TTC cornering sweep</t>
-        </is>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>Front-axle responsiveness; with rear stiffness sets the understeer gradient K_us the TV reference uses.</t>
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>SENSORS &amp; VCU — the VCU itself</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Rear cornering stiffness</t>
+          <t>VCU loop rate</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>c_α,r</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>TIRE_C_ALPHA_REAR</t>
+          <t>sensors.vcu.rate_hz</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Same, rear tire.</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>37</t>
+          <t>VCU control-loop rate — how often sensors are sampled and torque commands are recomputed (physics still integrates at 4 kHz).</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>1/rad</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>TTC FIT R9</t>
+          <t>Hz</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — ask software team</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Same, rear</t>
+          <t>The real VCU loop rate</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>TTC cornering sweep</t>
+          <t>Software team</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>Rear grip slope — stability side of the understeer gradient.</t>
+          <t>Gains proven stable at 100 Hz (verify.py section H); make it match reality before quoting controller performance.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Longitudinal slip stiffness</t>
+          <t>Plausibility cut threshold</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>c_κ</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>TIRE_C_KAPPA</t>
+          <t>sensors.vcu.plaus_apps_cut</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Drive/brake force per unit slip ratio, per newton of load.</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>41.9</t>
+          <t>APPS percentage above which, while braking, motor power must be cut.</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>1/unit slip</t>
-        </is>
-      </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>TTC FIT R9</t>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>RULES VALUE (EV.4.7)</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>Slope of Fx vs slip ratio</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>TTC drive/brake sweep</t>
+          <t>Rulebook (confirm current year)</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>Sets wheel-spin dynamics speed — the s-diff's plant. Gains retune if it moves.</t>
+          <t>Implemented and unit-tested (verify I3); the pedal_check maneuver demonstrates it.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>Lateral shape factor</t>
+          <t>Plausibility restore threshold</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>C_y</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>TIRE_SHAPE_C_LAT</t>
+          <t>sensors.vcu.plaus_apps_restore</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Magic Formula: how sharply lateral force peaks.</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>1.397</t>
+          <t>APPS percentage the pedal must fall below before power is restored.</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>TTC FIT R9</t>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>RULES VALUE (EV.4.7)</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Curve shape near/past the peak</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>TTC fit</t>
+          <t>Rulebook (confirm current year)</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>With E_y, sets where the curve peaks (currently 11.6° — real slicks ~6–10°) and how it lets go.</t>
+          <t>The latch that makes the cut a latch and not a flicker.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>Lateral curvature factor</t>
+          <t>Sensor noise seed</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>E_y</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>TIRE_CURV_E_LAT</t>
+          <t>sensors.vcu.seed</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Magic Formula: fall-off past the lateral peak.</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>0.365</t>
+          <t>Seed for the sensor-noise generator — runs are exactly repeatable and all four controller configs see IDENTICAL noise.</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G59" s="6" t="inlineStr">
-        <is>
-          <t>TTC FIT R9</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>NUMERICAL GUARD (repeatability)</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>Post-peak behavior</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>TTC fit</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>Gentle vs snappy breakaway — currently more forgiving than a real slick.</t>
+          <t>Fair comparisons and reproducible runs.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>Longitudinal shape factor</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>C_x</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>TIRE_SHAPE_C_LONG</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>Same idea, drive/brake direction.</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>1.705</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>TTC FIT R9</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>Curve shape</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>TTC fit</t>
-        </is>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>Sets the peak slip ratio (~0.10) — also the replay's red-wheel spin threshold.</t>
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>SENSORS — APPS, accelerator pedal position</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>Longitudinal curvature factor</t>
+          <t>APPS quantization</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>E_x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>TIRE_CURV_E_LONG</t>
+          <t>sensors.throttle_pos.quant_pct</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Fall-off past the longitudinal peak.</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>0.389</t>
+          <t>Accelerator pedal position resolution.</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>0.5</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G61" s="6" t="inlineStr">
-        <is>
-          <t>TTC FIT R9</t>
+          <t>%/LSB</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — sensor spec</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>Post-peak behavior</t>
+          <t>APPS sensor spec</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>TTC fit</t>
+          <t>Datasheet</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>How violently a spinning wheel loses force — feeds the wheelspin runaway.</t>
+          <t>Torque request granularity.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>CONTROLLER GAINS — tuned in-sim; retune whenever vehicle/tire numbers move</t>
+          <t>SENSORS — BPS, brake pressure</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>s-diff proportional gain</t>
+          <t>BPS full range</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Kp</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>KP_SDIFF</t>
+          <t>sensors.brake_pressure_sens.range_bar</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Torque per rad/s of wheel-speed-difference error.</t>
+          <t>Brake pressure sensor full range.</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>N·m/(rad/s)</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim)</t>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — sensor spec</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BPS spec + brake system pressures</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>Re-tune in sim: oscillation = too hot, sluggish = too cold</t>
+          <t>Brake team: line pressure at threshold/full braking</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>How hard the s-diff fights wheel-speed error.</t>
+          <t>Sets the pressure that maps to full regen.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>s-diff integral gain</t>
+          <t>BPS quantization</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Ki</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>KI_SDIFF</t>
+          <t>sensors.brake_pressure_sens.quant_bar</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Torque per accumulated rad of error.</t>
+          <t>Brake pressure sensor resolution.</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>N·m/rad</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim)</t>
+          <t>bar/LSB</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — sensor spec</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BPS spec</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>Datasheet</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>Removes steady error (e.g. constant-radius corners).</t>
+          <t>Regen command granularity.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>s-diff integral clamp</t>
+          <t>BPS actuated threshold</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>I_SDIFF_MAX</t>
+          <t>sensors.brake_pressure_sens.actuated_bar</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Anti-windup limit on the integral term.</t>
+          <t>Pressure above which the brake counts as "actuated" for the rules check.</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>N·m</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim)</t>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — calibration choice</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Brake system pressures</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>Brake team: line pressure at threshold braking</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>Stops the integral charging up during saturation and overshooting after.</t>
+          <t>Defines "braking" for the EV.4.7 plausibility check.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>s-diff torque-split clamp</t>
+          <t>Max regen torque</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>ΔT_max</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>DT_SDIFF_MAX</t>
+          <t>sensors.brake_pressure_sens.t_regen_max</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Hard cap on how much torque the s-diff may move between wheels.</t>
+          <t>Total rear-axle REGEN torque at full brake pressure (both motors).</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>250</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>N·m</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim) — SAFETY-CRITICAL</t>
+          <t>N*m</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — battery charge limit sets this</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Allowed charge current -&gt; torque</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>Sized in sim against the spin scenario</t>
+          <t>Accumulator team: max charge C-rate</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>Without it the s-diff dumps torque onto the loaded outer tire near the limit and power-oversteers the car. Proven in sim.</t>
+          <t>Caps how much "braking" the sim's BPS can command.</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>TV proportional gain</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>Kp</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>KP_TV</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>Yaw moment per rad/s of yaw-rate error.</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>2,500</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>N·m/(rad/s)</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim)</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>Re-tune in sim</t>
-        </is>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>How hard TV chases the yaw reference.</t>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>SENSORS — WSS, motor resolver over CAN</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>TV integral gain</t>
+          <t>WSS quantization</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Ki</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>KI_TV</t>
+          <t>sensors.wheel_speed.quant_rpm</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Yaw moment per accumulated rad of error.</t>
+          <t>Motor-speed resolution over CAN (motor side, before the planetary divide).</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>N·m/rad</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim)</t>
+          <t>rpm/LSB</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — AMK CAN resolution</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>AMK CAN speed resolution</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>AMK CAN spec</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>Steady-state yaw accuracy in long corners.</t>
+          <t>1 motor rpm is about 1.8 mm/s of ground speed — the resolver-over-CAN path is effectively noise-free wheel speed.</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>TV integral clamp</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>I_TV_MAX</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>Anti-windup limit on the TV integral.</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t>N·m</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim)</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="inlineStr">
-        <is>
-          <t>Same</t>
-        </is>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>Bounds windup when the reference is unreachable (e.g. full lock at speed).</t>
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>SENSORS — SAS, steering angle, and the steering map</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>Yaw-moment clamp</t>
+          <t>Steering map A0 (intercept)</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Mz_max</t>
+          <t>A0</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>MZ_MAX</t>
+          <t>sensors.steering_angle.map_a0</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Cap on total commanded yaw moment.</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>600</t>
+          <t>Constant term of the handwheel -&gt; road-wheel polynomial.</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>-0.0797</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>N·m</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim)</t>
+          <t>deg (intercept)</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (team chart)</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>The steering curve including RWheel</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>Steering chart / kinematics sweep</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>Keeps TV authority bounded.</t>
+          <t>Subtracted out to center the map; kept so the raw fit stays visible.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>Reference aggressiveness</t>
+          <t>Steering map A1 (linear)</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>AY_FRAC</t>
+          <t>sensors.steering_angle.map_a1</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>The yaw-rate reference is capped at this fraction of friction-limited lateral accel.</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>0.95</t>
+          <t>Linear term — the near-center steering ratio.</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>0.31</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>0–1</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim)</t>
+          <t>deg/deg</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (team chart)</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>The steering curve including RWheel</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>Steering chart / kinematics sweep</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>0.95 = ask for 95% of what grip allows — margin against an optimistic reference.</t>
+          <t>How the VCU turns the SAS reading into a road-wheel angle.</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>NUMERICAL</t>
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Steering map A2 (quadratic)</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>sensors.steering_angle.map_a2</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Quadratic term — the ratio falling off toward lock.</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>-0.000844</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>deg/deg^2</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (team chart; -844E-04 read as -8.44E-04)</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>The steering curve including RWheel</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>Steering chart / kinematics sweep</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>Full lock 23 deg is about 103 deg of handwheel.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
+          <t>SAS quantization</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>sensors.steering_angle.quant_deg</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Steering-angle sensor resolution, at the handwheel.</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>deg/LSB</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — sensor spec</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>Sensor spec</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>Datasheet of the chosen SAS</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>Steering resolution the VCU actually sees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>SENSORS — IMU, yaw gyro and accelerometers</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>IMU gyro noise (1σ)</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>sigma_g</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>sensors.imu_6axis.gyro_noise_std</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Yaw-gyro 1-sigma noise.</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>0.005236</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>rad/s (entered as deg/s, 1 sigma)</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — IMU spec</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>IMU datasheet numbers</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>Chosen IMU's spec sheet</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>Goes straight into the TV feedback — sets how clean the yaw control can be.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>IMU gyro bias</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>b_g</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>sensors.imu_6axis.gyro_bias</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Constant yaw-gyro zero offset.</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>0.001745</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>rad/s (entered as deg/s)</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — uncalibrated bias</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>IMU datasheet numbers</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>Chosen IMU's spec sheet, then a stationary calibration on the car</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>Biases the yaw-rate error the TV controller integrates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>VCU gyro low-pass</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>f_c</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>sensors.imu_6axis.lpf_hz</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>First-order low-pass the VCU applies to the gyro before feedback.</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>Hz</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — VCU filter choice</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>Software choice; tune against noise</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>Trade: more filtering = less dither but more phase lag in the yaw loop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>IMU accel noise</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>sigma_a</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>sensors.imu_6axis.accel_noise_std</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>Accelerometer 1-sigma noise (ax, ay channels).</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>m/s^2</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — IMU spec</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>IMU datasheet</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>Spec sheet</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>Feeds future estimation (vx observer, validation logging).</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>CONTROLLER GAINS — tuned in-sim; retune whenever vehicle/tire numbers move</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>s-diff proportional gain</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Kp</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>controllers.kp_sdiff</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Software differential: torque per rad/s of wheel-speed-difference error.</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>N*m/(rad/s)</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>TUNED (sim)</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>Re-tune in sim: oscillation = too hot, sluggish = too cold</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>How hard the s-diff fights wheel-speed error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>s-diff integral gain</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>Ki</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>controllers.ki_sdiff</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>Software differential: torque per accumulated rad of error.</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>N*m/rad</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>TUNED (sim)</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>Same</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>Removes steady error (e.g. constant-radius corners).</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>s-diff integral clamp</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>controllers.i_sdiff_max</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>Anti-windup limit on the s-diff integral term.</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>N*m</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>TUNED (sim)</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>Same</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>Stops the integral charging up during saturation and overshooting after.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>s-diff torque-split clamp</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>dT_max</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>controllers.dt_sdiff_max</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>Hard cap on how much torque the s-diff may transfer between the wheels.</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>N*m</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>TUNED (sim) — SAFETY-CRITICAL</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>Sized in sim against the spin scenario</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>Without it, an unbounded speed-difference PI dumps torque onto the loaded outer tire near the limit, burns its lateral grip (friction circle), and power-oversteers the car — the sim demonstrates exactly this if you raise the cap. The s-diff's job is trimming wheel speeds, not large torque moves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>TV proportional gain</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Kp</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>controllers.kp_tv</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>Torque vectoring: yaw moment per rad/s of yaw-rate error.</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>N*m/(rad/s)</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>TUNED (sim)</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>Re-tune in sim</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>How hard TV chases the yaw reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>TV integral gain</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Ki</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>controllers.ki_tv</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Torque vectoring: yaw moment per accumulated rad of error.</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>N*m/rad</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>TUNED (sim)</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>Same</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>Steady-state yaw accuracy in long corners.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>TV integral clamp</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>controllers.i_tv_max</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>Anti-windup limit on the TV integral.</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>N*m</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>TUNED (sim)</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>Same</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>Bounds windup when the reference is unreachable (e.g. full lock at speed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>Yaw-moment clamp</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>Mz_max</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>controllers.mz_max</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>Clamp on total commanded yaw moment.</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>N*m</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>TUNED (sim)</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>Same</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>Keeps TV authority bounded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>Reference aggressiveness</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>controllers.ay_frac</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>The yaw-rate reference is capped at this fraction of the friction-limited lateral acceleration.</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>TUNED (sim)</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>Same</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>0.95 = ask for 95% of what grip allows — margin against an optimistic reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>SOFTWARE-IN-THE-LOOP (sil/)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>SIL firmware boot time</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>sil.boot_s</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>How long the real firmware is left to boot — bench check (55 ms) plus the ADC settle loop (1 s) — before a maneuver's t = 0, measured on the firmware's own clock.</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — from main.c / initializations.c</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>The firmware's true settle time</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>Read main.c / initializations.c, or instrument the boot</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>Too short and the first samples come from an unsettled ADC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>NUMERICAL GUARDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
           <t>Low-speed guard</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>v_ε</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>V_EPS</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>Minimum speed used in slip-angle/slip-ratio denominators.</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>v_eps</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>numerical.v_eps</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>Minimum speed used in slip-angle / slip-ratio denominators.</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="F73" s="3" t="inlineStr">
+      <c r="F92" s="3" t="inlineStr">
         <is>
           <t>m/s</t>
         </is>
       </c>
-      <c r="G73" s="3" t="inlineStr">
+      <c r="G92" s="3" t="inlineStr">
         <is>
           <t>NUMERICAL GUARD</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
         <is>
           <t>Below ~0.5 m/s wheel-slip math is untrustworthy — launches are out of scope until reworked.</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="8" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
         <is>
           <t>Legend:</t>
         </is>
       </c>
-      <c r="B75" s="9" t="inlineStr">
-        <is>
-          <t>GREEN value = confirmed for the CURRENT car/driver (or MEASURED). Black = report car, guess, rules, or sim-tuned. Orange status = placeholder/needs attention.</t>
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t>GREEN value = confirmed for the CURRENT car/driver (or MEASURED). Black = report car, guess, rules, or sim-tuned. Orange status = placeholder/needs attention. Every row is generated from a params.yaml file — edit the number there, not here.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
-  <mergeCells count="12">
-    <mergeCell ref="A47:J47"/>
+  <mergeCells count="18">
     <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A32:J32"/>
-    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="A79:J79"/>
+    <mergeCell ref="A89:J89"/>
+    <mergeCell ref="A74:J74"/>
+    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A62:J62"/>
+    <mergeCell ref="A67:J67"/>
+    <mergeCell ref="A91:J91"/>
     <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A15:J15"/>
-    <mergeCell ref="B75:J75"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A72:J72"/>
-    <mergeCell ref="A25:J25"/>
-    <mergeCell ref="A49:J49"/>
+    <mergeCell ref="A55:J55"/>
+    <mergeCell ref="A69:J69"/>
+    <mergeCell ref="B94:J94"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A60:J60"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/datasheets/FSAE-Sim Parameters.xlsx
+++ b/docs/datasheets/FSAE-Sim Parameters.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J94"/>
+  <dimension ref="A1:J93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1380,398 +1380,398 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Pack voltage</t>
+          <t>Motor torque constant</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>V_DC</t>
+          <t>Kt</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>drivetrain.pack_voltage</t>
+          <t>drivetrain.motor_kt</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Accumulator (HV pack) nominal voltage.</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>380</t>
+          <t>Shaft torque per amp of motor (q-axis) current. Turns a VESC current command into torque.</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>0.2</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT CAR (design decision 2026-08-30)</t>
+          <t>N*m/A</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — UNMEASURED; AMK-era motor numbers above may not apply to the in-hub motors</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Nothing (design value)</t>
+          <t>The in-hub motor's Kt</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Accumulator design</t>
+          <t>Motor datasheet, or once VESC status frames are parsed: measured wheel torque / (reported motor current x gear ratio). Cross-check against motor_torque_peak / peak current.</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>Not used directly by the physics — it SETS motor peak power below. 4 motors x ~20 kW at 380 V = 80 kW exactly (the 4WD end state); the current 2-rear build tops out at ~40 kW, so the 80 kW cap is unreachable until 4WD.</t>
+          <t>The ONLY number that makes the VCU's milliamp command mean anything in the sim: T_wheel = I[A] * Kt * gear_ratio. At 0.2 the firmware's 125 A full-throttle command asks for 325 N*m per wheel, above the 273 N*m peak.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Motor peak power</t>
+          <t>Pack voltage</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>P_pk</t>
+          <t>V_DC</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>drivetrain.motor_power_peak</t>
+          <t>drivetrain.pack_voltage</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Peak mechanical power of ONE motor at OUR pack voltage.</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>20,000</t>
+          <t>Accumulator (HV pack) nominal voltage.</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>380</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>DERIVED (kit curves scaled to 380 V)</t>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (design decision 2026-08-30)</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Actual peak power at 380 V</t>
+          <t>Nothing (design value)</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>Read the 380 V curve in the AMK manual; dyno pull once the pack exists</t>
+          <t>Accumulator design</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>Caps torque above ~17 m/s (37 mph): at 40 mph only 256 of 273 N*m is available. The 2-rear build tops out around 40 kW.</t>
+          <t>Not used directly by the physics — it SETS motor peak power below. 4 motors x ~20 kW at 380 V = 80 kW exactly (the 4WD end state); the current 2-rear build tops out at ~40 kW, so the 80 kW cap is unreachable until 4WD.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Motor max speed</t>
+          <t>Motor peak power</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>n_max</t>
+          <t>P_pk</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>drivetrain.motor_max_speed</t>
+          <t>drivetrain.motor_power_peak</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Maximum motor shaft speed.</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>2,094</t>
+          <t>Peak mechanical power of ONE motor at OUR pack voltage.</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>20,000</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>rad/s (entered as 20,000 rpm)</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT CAR (AMK kit datasheet)</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>DERIVED (kit curves scaled to 380 V)</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Nothing (datasheet value)</t>
+          <t>Actual peak power at 380 V</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>AMK kit manual 6.5.3 (characteristics end at 20,000 rpm)</t>
+          <t>Read the 380 V curve in the AMK manual; dyno pull once the pack exists</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>~36 m/s (80 mph) ground speed at 13:1 — comfortably above the 40 mph envelope, not the limiter. NOT enforced by this basic sim; recorded for completeness and future top-speed studies.</t>
+          <t>Caps torque above ~17 m/s (37 mph): at 40 mph only 256 of 273 N*m is available. The 2-rear build tops out around 40 kW.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Wheel spin inertia</t>
+          <t>Motor max speed</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>I_w</t>
+          <t>n_max</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>drivetrain.I_wheel</t>
+          <t>drivetrain.motor_max_speed</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Spin inertia of ONE rear corner about the axle: tire + rim + brake rotor + hub + (motor rotor inertia * gear_ratio^2).</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>0.35</t>
+          <t>Maximum motor shaft speed.</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>2,094</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>kg*m^2</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>DERIVED estimate — replace with CAD</t>
+          <t>rad/s (entered as 20,000 rpm)</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (AMK kit datasheet)</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Rotating inertia of one corner</t>
+          <t>Nothing (datasheet value)</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>CAD mass properties + rotor J from the exact AMK motor sheet</t>
+          <t>AMK kit manual 6.5.3 (characteristics end at 20,000 rpm)</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>Sets how fast an unloaded wheel spins up — the s-diff's whole problem. Controller gains are sensitive to it: retune when it changes.</t>
+          <t>~36 m/s (80 mph) ground speed at 13:1 — comfortably above the 40 mph envelope, not the limiter. NOT enforced by this basic sim; recorded for completeness and future top-speed studies.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Total power cap</t>
+          <t>Wheel spin inertia</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>P_max</t>
+          <t>I_w</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>drivetrain.power_cap_total</t>
+          <t>drivetrain.I_wheel</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>FSAE EV rules limit on total drive power (EV.4.2, 80 kW at the accumulator).</t>
+          <t>Spin inertia of ONE rear corner about the axle: tire + rim + brake rotor + hub + (motor rotor inertia * gear_ratio^2).</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>80,000</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>kg*m^2</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>RULES VALUE (simplified)</t>
+          <t>DERIVED estimate — replace with CAD</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Nothing (rulebook)</t>
+          <t>Rotating inertia of one corner</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Confirm in the current-year rulebook</t>
+          <t>CAD mass properties + rotor J from the exact AMK motor sheet</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>Hard ceiling. The sim applies it to mechanical power (no drivetrain losses modeled) — the real car hits it ~10-15% earlier.</t>
+          <t>Sets how fast an unloaded wheel spins up — the s-diff's whole problem. Controller gains are sensitive to it: retune when it changes.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
+          <t>Total power cap</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>P_max</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>drivetrain.power_cap_total</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>FSAE EV rules limit on total drive power (EV.4.2, 80 kW at the accumulator).</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>80,000</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>RULES VALUE (simplified)</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Nothing (rulebook)</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Confirm in the current-year rulebook</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>Hard ceiling. The sim applies it to mechanical power (no drivetrain losses modeled) — the real car hits it ~10-15% earlier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
           <t>Regen speed cutoff</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>drivetrain.regen_speed_cutoff</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Below this speed no negative (regen) torque is commanded.</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>m/s (~5 km/h)</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>RULES VALUE (approx.)</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>Nothing (rulebook)</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>Confirm in the current-year rulebook</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>Rules restrict regen near standstill; also keeps the sim's low-speed slip math out of its untrustworthy zone.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>AERO</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Lift coefficient</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>C_L</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>aero.cl_coeff</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Lift (downforce) coefficient, referenced to frontal_area.</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>3.18</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>FROM REPORT (old car's aero)</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Current car's downforce coefficient</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>CFD, then straight-line coast-down / load-cell validation</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>Downforce = 0.5*rho*C_L*A*v^2 — free grip that grows with speed^2.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Drag coefficient</t>
+          <t>Lift coefficient</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>C_D</t>
+          <t>C_L</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>aero.cd_coeff</t>
+          <t>aero.cl_coeff</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Drag coefficient, same reference area.</t>
+          <t>Lift (downforce) coefficient, referenced to frontal_area.</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -1786,368 +1786,368 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Current car's drag coefficient</t>
+          <t>Current car's downforce coefficient</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>CFD + coast-down test</t>
+          <t>CFD, then straight-line coast-down / load-cell validation</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>Sets top-speed force budget and the torque needed to hold speed in every maneuver.</t>
+          <t>Downforce = 0.5*rho*C_L*A*v^2 — free grip that grows with speed^2.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Frontal area</t>
+          <t>Drag coefficient</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>A_F</t>
+          <t>C_D</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>aero.frontal_area</t>
+          <t>aero.cd_coeff</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Aerodynamic frontal reference area.</t>
+          <t>Drag coefficient, same reference area.</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>1.106</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>m^2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>FROM REPORT</t>
+          <t>FROM REPORT (old car's aero)</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Projected frontal area</t>
+          <t>Current car's drag coefficient</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>CAD projection</t>
+          <t>CFD + coast-down test</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>Only the products C*A enter the physics — keep coefficient and area consistent.</t>
+          <t>Sets top-speed force budget and the torque needed to hold speed in every maneuver.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
+          <t>Frontal area</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>A_F</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>aero.frontal_area</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Aerodynamic frontal reference area.</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>1.106</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>m^2</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>FROM REPORT</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Projected frontal area</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>CAD projection</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>Only the products C*A enter the physics — keep coefficient and area consistent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
           <t>ClA (computed)</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>C_L*A</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>aero.ClA</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>The downforce product the sim actually uses.</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>3.517</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>m^2</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="3">
+      <c r="I32" s="3">
         <f> aero.cl_coeff * aero.frontal_area</f>
         <v/>
       </c>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>CdA (computed)</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>C_D*A</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>aero.CdA</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>The drag product the sim actually uses.</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>1.504</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>m^2</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="3">
+      <c r="I33" s="3">
         <f> aero.cd_coeff * aero.frontal_area</f>
         <v/>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>Aero balance</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>pct_aero_f</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>aero.balance_front</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Fraction of total downforce landing on the FRONT axle (0.45 = 45/55).</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="G34" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER — pure guess</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>Center-of-pressure position</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>CFD (aero team) — ask for CP height too</t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>Moves grip between axles as speed rises — shapes high-speed balance directly. One of the last pure guesses outside tires.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>STEERING GEOMETRY</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>Ackermann fraction</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>pct_A</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>steering.ackermann_fraction</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>How much of the geometric (100%) Ackermann inner/outer steer split the steering actually delivers. 0.0 = parallel steer (both fronts get the same angle), 1.0 = full geometric Ackermann, negative = anti-Ackermann.</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER (parallel) — RWheel curve needed</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>The steering curve: both wheels' angles vs handwheel angle</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="I36" s="3" t="inlineStr">
         <is>
           <t>From the steering chart: the LWheel curve is on file, need the RWheel polynomial from the same chart (or a few x, LWheel, RWheel point triples).</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>Only matters at large steer angles: at 5 deg the split is ~+/-0.2 deg; at the 23 deg full-lock hairpin it is ~+/-4 deg per wheel. Proven to flip whether s-diff-only survives the hairpin (runs 007 vs 008).</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>LOAD TRANSFER</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Front spring rate</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>ks_f</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>loads.spring_rate_front</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>Front suspension spring rate. Used ONLY through its ratio to the rear.</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>19.3</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>N/mm (ratio only)</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>FROM REPORT</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>Front roll stiffness incl. ARBs and motion ratios</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>Suspension team</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>Numerator of the lateral load-transfer split.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Rear spring rate</t>
+          <t>Front spring rate</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>ks_r</t>
+          <t>ks_f</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>loads.spring_rate_rear</t>
+          <t>loads.spring_rate_front</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Rear suspension spring rate. Used ONLY through its ratio to the front.</t>
+          <t>Front suspension spring rate. Used ONLY through its ratio to the rear.</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Rear roll stiffness incl. ARBs and motion ratios</t>
+          <t>Front roll stiffness incl. ARBs and motion ratios</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -2172,144 +2172,144 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>Denominator half of the lateral load-transfer split.</t>
+          <t>Numerator of the lateral load-transfer split.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
+          <t>Rear spring rate</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>ks_r</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>loads.spring_rate_rear</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Rear suspension spring rate. Used ONLY through its ratio to the front.</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>24.8</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>N/mm (ratio only)</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>FROM REPORT</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Rear roll stiffness incl. ARBs and motion ratios</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Suspension team</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>Denominator half of the lateral load-transfer split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
           <t>Front lateral-transfer fraction</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>loads.lat_transfer_frac_front</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>Share of total LATERAL load transfer reacted by the FRONT axle, set by the front/rear roll-stiffness split.</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>0.4376</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>FROM REPORT (spring-rate ratio only) — crude</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>Front vs rear roll stiffness</t>
         </is>
       </c>
-      <c r="I39" s="3">
+      <c r="I40" s="3">
         <f> loads.spring_rate_front / (loads.spring_rate_front + loads.spring_rate_rear)</f>
         <v/>
       </c>
-      <c r="J39" s="3" t="inlineStr">
+      <c r="J40" s="3" t="inlineStr">
         <is>
           <t>Which axle eats the load transfer = which axle loses grip first — trades understeer/oversteer at the limit.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>TIRES — TTC ROUND 9 FIT (R20 compound, 2026-08-31); surrogate sizes, road µ = belt × 0.67 pending skidpad</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Belt→road grip scale</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>tires.mu_road_scale</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>Belt-&gt;asphalt grip scaling. Calspan's sandpaper belt grips harder than track asphalt; common practice scales the fitted peak mu by ~0.65-0.70 for on-road prediction (stiffnesses/shapes carry over unscaled).</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>0.67</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G41" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER — skidpad measures this</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>Steady-state skidpad lateral g</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>Skidpad test vs sim prediction</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>Multiplies EVERY grip number — the single biggest absolute-accuracy lever left. VALIDATE on skidpad; that measurement replaces this guess with truth.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Belt peak µ, lateral</t>
+          <t>Belt→road grip scale</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>mu_belt_y</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>tires.belt_mu_lat</t>
+          <t>tires.mu_road_scale</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Peak LATERAL friction coefficient as fitted on the Calspan belt.</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>2.593</t>
+          <t>Belt-&gt;asphalt grip scaling. Calspan's sandpaper belt grips harder than track asphalt; common practice scales the fitted peak mu by ~0.65-0.70 for on-road prediction (stiffnesses/shapes carry over unscaled).</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>0.67</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -2317,51 +2317,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>TTC FIT R9</t>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — skidpad measures this</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Steady-state skidpad lateral g</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>tire_fit.py on Round 9 cornering runs (surrogate spread +/-6%)</t>
+          <t>Skidpad test vs sim prediction</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>Scaled by mu_road_scale to give the road value the sim uses.</t>
+          <t>Multiplies EVERY grip number — the single biggest absolute-accuracy lever left. VALIDATE on skidpad; that measurement replaces this guess with truth.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Belt peak µ, longitudinal</t>
+          <t>Belt peak µ, lateral</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>mu_belt_x</t>
+          <t>mu_belt_y</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>tires.belt_mu_long</t>
+          <t>tires.belt_mu_lat</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Peak LONGITUDINAL friction coefficient as fitted on the belt.</t>
+          <t>Peak LATERAL friction coefficient as fitted on the Calspan belt.</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>2.359</t>
+          <t>2.593</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>tire_fit.py on Round 9 drive/brake runs</t>
+          <t>tire_fit.py on Round 9 cornering runs (surrogate spread +/-6%)</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -2393,279 +2393,279 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
+          <t>Belt peak µ, longitudinal</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>mu_belt_x</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>tires.belt_mu_long</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Peak LONGITUDINAL friction coefficient as fitted on the belt.</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>2.359</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>TTC FIT R9</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>tire_fit.py on Round 9 drive/brake runs</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>Scaled by mu_road_scale to give the road value the sim uses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
           <t>Peak friction coefficient</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>mu0</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>tires.mu0</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>Peak grip per newton of load, at the nominal load (road value).</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>1.737</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G44" s="6" t="inlineStr">
+      <c r="G45" s="6" t="inlineStr">
         <is>
           <t>TTC FIT R9</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>Peak mu at several loads</t>
         </is>
       </c>
-      <c r="I44" s="3">
+      <c r="I45" s="3">
         <f> tires.mu_road_scale * tires.belt_mu_lat</f>
         <v/>
       </c>
-      <c r="J44" s="3" t="inlineStr">
+      <c r="J45" s="3" t="inlineStr">
         <is>
           <t>THE grip number. Max lateral g, spin thresholds, everything — the single most important number in the sim.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>Peak longitudinal friction</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>mu0x</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>tires.mu0_long</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Drive/brake grip peak — fitted 9% below lateral; combined slip caps on the friction ELLIPSE in tire.py.</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>1.581</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G45" s="6" t="inlineStr">
+      <c r="G46" s="6" t="inlineStr">
         <is>
           <t>TTC FIT R9</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="3">
+      <c r="I46" s="3">
         <f> tires.mu_road_scale * tires.belt_mu_long</f>
         <v/>
       </c>
-      <c r="J45" s="3" t="inlineStr">
+      <c r="J46" s="3" t="inlineStr">
         <is>
           <t>Sets wheelspin threshold and traction capability.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Load sensitivity</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>s_mu</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>tires.s_mu</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>Load sensitivity — how much the friction COEFFICIENT drops as vertical load rises: mu = mu0 * (1 - s_mu*(Fz/Fz_nom - 1)). Shared by the lateral and longitudinal peaks.</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>0.112</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>—/100% load</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="inlineStr">
-        <is>
-          <t>TTC FIT R9</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>mu at low vs high load</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>Same TTC fit</t>
-        </is>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>The reason load transfer costs grip and torque placement matters at all. Zero would make TV pointless.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
+          <t>Load sensitivity</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>s_mu</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>tires.s_mu</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Load sensitivity — how much the friction COEFFICIENT drops as vertical load rises: mu = mu0 * (1 - s_mu*(Fz/Fz_nom - 1)). Shared by the lateral and longitudinal peaks.</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>0.112</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>—/100% load</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>TTC FIT R9</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>mu at low vs high load</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>Same TTC fit</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>The reason load transfer costs grip and torque placement matters at all. Zero would make TV pointless.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
           <t>Nominal tire load</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>Fz_nom</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>tires.Fz_nom</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>The "nominal" vertical load at which mu0 is defined (~one static corner weight).</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>618.6</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="G48" s="3" t="inlineStr">
         <is>
           <t>DERIVED (follows the masses automatically)</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="3">
+      <c r="I48" s="3">
         <f> (mass.car_no_driver + mass.driver) * environment.g / 4.0</f>
         <v/>
       </c>
-      <c r="J47" s="3" t="inlineStr">
+      <c r="J48" s="3" t="inlineStr">
         <is>
           <t>Reference point for the load-sensitivity line.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Front cornering stiffness</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>c_alpha_f</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>tires.c_alpha_front</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>Normalized cornering stiffness of a FRONT tire: lateral force per radian of slip angle, per newton of load (C_alpha = this * Fz).</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>1/rad</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="inlineStr">
-        <is>
-          <t>TTC FIT R9 (same tire all round)</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>Slope of Fy vs slip angle at small angles</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>TTC cornering sweep</t>
-        </is>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>Front-axle responsiveness; with rear stiffness sets the understeer gradient K_us the TV reference uses.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Rear cornering stiffness</t>
+          <t>Front cornering stiffness</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>c_alpha_r</t>
+          <t>c_alpha_f</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>tires.c_alpha_rear</t>
+          <t>tires.c_alpha_front</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Same, for a REAR tire.</t>
+          <t>Normalized cornering stiffness of a FRONT tire: lateral force per radian of slip angle, per newton of load (C_alpha = this * Fz).</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>Same, rear</t>
+          <t>Slope of Fy vs slip angle at small angles</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
@@ -2695,91 +2695,91 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>Rear grip slope — stability side of the understeer gradient.</t>
+          <t>Front-axle responsiveness; with rear stiffness sets the understeer gradient K_us the TV reference uses.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Longitudinal slip stiffness</t>
+          <t>Rear cornering stiffness</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>c_kappa</t>
+          <t>c_alpha_r</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>tires.c_kappa</t>
+          <t>tires.c_alpha_rear</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Normalized longitudinal slip stiffness: drive/brake force per unit slip ratio per newton (C_kappa = this * Fz).</t>
+          <t>Same, for a REAR tire.</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>1/slip</t>
+          <t>1/rad</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>TTC FIT R9</t>
+          <t>TTC FIT R9 (same tire all round)</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Slope of Fx vs slip ratio</t>
+          <t>Same, rear</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>TTC drive/brake sweep</t>
+          <t>TTC cornering sweep</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>Sets wheel-spin dynamics speed — the s-diff's plant. Gains retune if it moves.</t>
+          <t>Rear grip slope — stability side of the understeer gradient.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Lateral shape factor</t>
+          <t>Longitudinal slip stiffness</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>C_y</t>
+          <t>c_kappa</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>tires.shape_c_lat</t>
+          <t>tires.c_kappa</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Magic Formula shape factor — how sharply lateral force peaks.</t>
+          <t>Normalized longitudinal slip stiffness: drive/brake force per unit slip ratio per newton (C_kappa = this * Fz).</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>1.397</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1/slip</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
@@ -2789,44 +2789,44 @@
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>Curve shape near/past the peak</t>
+          <t>Slope of Fx vs slip ratio</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>TTC fit</t>
+          <t>TTC drive/brake sweep</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>With E_y, sets where the curve peaks (currently 11.6 deg — real slicks ~6-10 deg) and how it lets go.</t>
+          <t>Sets wheel-spin dynamics speed — the s-diff's plant. Gains retune if it moves.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Lateral curvature factor</t>
+          <t>Lateral shape factor</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>E_y</t>
+          <t>C_y</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>tires.curv_e_lat</t>
+          <t>tires.shape_c_lat</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Magic Formula curvature factor — fall-off past the lateral peak.</t>
+          <t>Magic Formula shape factor — how sharply lateral force peaks.</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>1.397</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Post-peak behavior</t>
+          <t>Curve shape near/past the peak</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
@@ -2851,34 +2851,34 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>Gentle vs snappy breakaway — currently more forgiving than a real slick.</t>
+          <t>With E_y, sets where the curve peaks (currently 11.6 deg — real slicks ~6-10 deg) and how it lets go.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Longitudinal shape factor</t>
+          <t>Lateral curvature factor</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>C_x</t>
+          <t>E_y</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>tires.shape_c_long</t>
+          <t>tires.curv_e_lat</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Same idea, drive/brake direction.</t>
+          <t>Magic Formula curvature factor — fall-off past the lateral peak.</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>1.705</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>Curve shape</t>
+          <t>Post-peak behavior</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
@@ -2903,125 +2903,125 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>Sets the peak slip ratio (~0.10) — also the replay's red-wheel spin threshold.</t>
+          <t>Gentle vs snappy breakaway — currently more forgiving than a real slick.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
+          <t>Longitudinal shape factor</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>C_x</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>tires.shape_c_long</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Same idea, drive/brake direction.</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>1.705</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>TTC FIT R9</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Curve shape</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>TTC fit</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>Sets the peak slip ratio (~0.10) — also the replay's red-wheel spin threshold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
           <t>Longitudinal curvature factor</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>E_x</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>tires.curv_e_long</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>Fall-off past the longitudinal peak.</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>0.389</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G54" s="6" t="inlineStr">
+      <c r="G55" s="6" t="inlineStr">
         <is>
           <t>TTC FIT R9</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr">
         <is>
           <t>Post-peak behavior</t>
         </is>
       </c>
-      <c r="I54" s="3" t="inlineStr">
+      <c r="I55" s="3" t="inlineStr">
         <is>
           <t>TTC fit</t>
         </is>
       </c>
-      <c r="J54" s="3" t="inlineStr">
+      <c r="J55" s="3" t="inlineStr">
         <is>
           <t>How violently a spinning wheel loses force — feeds the wheelspin runaway.</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>SENSORS &amp; VCU — the VCU itself</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>VCU loop rate</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>sensors.vcu.rate_hz</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>VCU control-loop rate — how often sensors are sampled and torque commands are recomputed (physics still integrates at 4 kHz).</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>Hz</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER — ask software team</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>The real VCU loop rate</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="inlineStr">
-        <is>
-          <t>Software team</t>
-        </is>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>Gains proven stable at 100 Hz (verify.py section H); make it match reality before quoting controller performance.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Plausibility cut threshold</t>
+          <t>VCU loop rate</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -3031,49 +3031,49 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>sensors.vcu.plaus_apps_cut</t>
+          <t>sensors.vcu.rate_hz</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>APPS percentage above which, while braking, motor power must be cut.</t>
+          <t>VCU control-loop rate — how often sensors are sampled and torque commands are recomputed (physics still integrates at 4 kHz).</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>RULES VALUE (EV.4.7)</t>
+          <t>Hz</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — ask software team</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>The real VCU loop rate</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>Rulebook (confirm current year)</t>
+          <t>Software team</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>Implemented and unit-tested (verify I3); the pedal_check maneuver demonstrates it.</t>
+          <t>Gains proven stable at 100 Hz (verify.py section H); make it match reality before quoting controller performance.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>Plausibility restore threshold</t>
+          <t>Plausibility cut threshold</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -3083,17 +3083,17 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>sensors.vcu.plaus_apps_restore</t>
+          <t>sensors.vcu.plaus_apps_cut</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>APPS percentage the pedal must fall below before power is restored.</t>
+          <t>APPS percentage above which, while braking, motor power must be cut.</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -3118,184 +3118,184 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>The latch that makes the cut a latch and not a flicker.</t>
+          <t>Implemented and unit-tested (verify I3); the pedal_check maneuver demonstrates it.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
+          <t>Plausibility restore threshold</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>sensors.vcu.plaus_apps_restore</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>APPS percentage the pedal must fall below before power is restored.</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>RULES VALUE (EV.4.7)</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>Rulebook (confirm current year)</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>The latch that makes the cut a latch and not a flicker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
           <t>Sensor noise seed</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>sensors.vcu.seed</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>Seed for the sensor-noise generator — runs are exactly repeatable and all four controller configs see IDENTICAL noise.</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="F60" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
+      <c r="G60" s="3" t="inlineStr">
         <is>
           <t>NUMERICAL GUARD (repeatability)</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr">
+      <c r="H60" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="3" t="inlineStr">
+      <c r="I60" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J59" s="3" t="inlineStr">
+      <c r="J60" s="3" t="inlineStr">
         <is>
           <t>Fair comparisons and reproducible runs.</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>SENSORS — APPS, accelerator pedal position</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>APPS quantization</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>sensors.throttle_pos.quant_pct</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>Accelerator pedal position resolution.</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="F61" s="3" t="inlineStr">
+      <c r="F62" s="3" t="inlineStr">
         <is>
           <t>%/LSB</t>
         </is>
       </c>
-      <c r="G61" s="7" t="inlineStr">
+      <c r="G62" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER — sensor spec</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr">
+      <c r="H62" s="3" t="inlineStr">
         <is>
           <t>APPS sensor spec</t>
         </is>
       </c>
-      <c r="I61" s="3" t="inlineStr">
+      <c r="I62" s="3" t="inlineStr">
         <is>
           <t>Datasheet</t>
         </is>
       </c>
-      <c r="J61" s="3" t="inlineStr">
+      <c r="J62" s="3" t="inlineStr">
         <is>
           <t>Torque request granularity.</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>SENSORS — BPS, brake pressure</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>BPS full range</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>sensors.brake_pressure_sens.range_bar</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>Brake pressure sensor full range.</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="G63" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER — sensor spec</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>BPS spec + brake system pressures</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>Brake team: line pressure at threshold/full braking</t>
-        </is>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>Sets the pressure that maps to full regen.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>BPS quantization</t>
+          <t>BPS full range</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -3305,22 +3305,22 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>sensors.brake_pressure_sens.quant_bar</t>
+          <t>sensors.brake_pressure_sens.range_bar</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Brake pressure sensor resolution.</t>
+          <t>Brake pressure sensor full range.</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>bar/LSB</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
@@ -3330,24 +3330,24 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>BPS spec</t>
+          <t>BPS spec + brake system pressures</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>Datasheet</t>
+          <t>Brake team: line pressure at threshold/full braking</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>Regen command granularity.</t>
+          <t>Sets the pressure that maps to full regen.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>BPS actuated threshold</t>
+          <t>BPS quantization</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -3357,244 +3357,244 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>sensors.brake_pressure_sens.actuated_bar</t>
+          <t>sensors.brake_pressure_sens.quant_bar</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Pressure above which the brake counts as "actuated" for the rules check.</t>
+          <t>Brake pressure sensor resolution.</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>bar</t>
+          <t>bar/LSB</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — calibration choice</t>
+          <t>PLACEHOLDER — sensor spec</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>Brake system pressures</t>
+          <t>BPS spec</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>Brake team: line pressure at threshold braking</t>
+          <t>Datasheet</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>Defines "braking" for the EV.4.7 plausibility check.</t>
+          <t>Regen command granularity.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
+          <t>BPS actuated threshold</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>sensors.brake_pressure_sens.actuated_bar</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Pressure above which the brake counts as "actuated" for the rules check.</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — calibration choice</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>Brake system pressures</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>Brake team: line pressure at threshold braking</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>Defines "braking" for the EV.4.7 plausibility check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
           <t>Max regen torque</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>sensors.brake_pressure_sens.t_regen_max</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>Total rear-axle REGEN torque at full brake pressure (both motors).</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
+      <c r="E67" s="4" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="F66" s="3" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>N*m</t>
         </is>
       </c>
-      <c r="G66" s="7" t="inlineStr">
+      <c r="G67" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER — battery charge limit sets this</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr">
+      <c r="H67" s="3" t="inlineStr">
         <is>
           <t>Allowed charge current -&gt; torque</t>
         </is>
       </c>
-      <c r="I66" s="3" t="inlineStr">
+      <c r="I67" s="3" t="inlineStr">
         <is>
           <t>Accumulator team: max charge C-rate</t>
         </is>
       </c>
-      <c r="J66" s="3" t="inlineStr">
+      <c r="J67" s="3" t="inlineStr">
         <is>
           <t>Caps how much "braking" the sim's BPS can command.</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>SENSORS — WSS, motor resolver over CAN</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>WSS quantization</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>sensors.wheel_speed.quant_rpm</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>Motor-speed resolution over CAN (motor side, before the planetary divide).</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="E69" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F68" s="3" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>rpm/LSB</t>
         </is>
       </c>
-      <c r="G68" s="7" t="inlineStr">
+      <c r="G69" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER — AMK CAN resolution</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
+      <c r="H69" s="3" t="inlineStr">
         <is>
           <t>AMK CAN speed resolution</t>
         </is>
       </c>
-      <c r="I68" s="3" t="inlineStr">
+      <c r="I69" s="3" t="inlineStr">
         <is>
           <t>AMK CAN spec</t>
         </is>
       </c>
-      <c r="J68" s="3" t="inlineStr">
+      <c r="J69" s="3" t="inlineStr">
         <is>
           <t>1 motor rpm is about 1.8 mm/s of ground speed — the resolver-over-CAN path is effectively noise-free wheel speed.</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>SENSORS — SAS, steering angle, and the steering map</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>Steering map A0 (intercept)</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>A0</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>sensors.steering_angle.map_a0</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>Constant term of the handwheel -&gt; road-wheel polynomial.</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>-0.0797</t>
-        </is>
-      </c>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>deg (intercept)</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT CAR (team chart)</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>The steering curve including RWheel</t>
-        </is>
-      </c>
-      <c r="I70" s="3" t="inlineStr">
-        <is>
-          <t>Steering chart / kinematics sweep</t>
-        </is>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>Subtracted out to center the map; kept so the raw fit stays visible.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>Steering map A1 (linear)</t>
+          <t>Steering map A0 (intercept)</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A0</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>sensors.steering_angle.map_a1</t>
+          <t>sensors.steering_angle.map_a0</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Linear term — the near-center steering ratio.</t>
+          <t>Constant term of the handwheel -&gt; road-wheel polynomial.</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.0797</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>deg/deg</t>
+          <t>deg (intercept)</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
@@ -3614,44 +3614,44 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>How the VCU turns the SAS reading into a road-wheel angle.</t>
+          <t>Subtracted out to center the map; kept so the raw fit stays visible.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>Steering map A2 (quadratic)</t>
+          <t>Steering map A1 (linear)</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>sensors.steering_angle.map_a2</t>
+          <t>sensors.steering_angle.map_a1</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Quadratic term — the ratio falling off toward lock.</t>
+          <t>Linear term — the near-center steering ratio.</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>-0.000844</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>deg/deg^2</t>
+          <t>deg/deg</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>CURRENT CAR (team chart; -844E-04 read as -8.44E-04)</t>
+          <t>CURRENT CAR (team chart)</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
@@ -3666,155 +3666,155 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>Full lock 23 deg is about 103 deg of handwheel.</t>
+          <t>How the VCU turns the SAS reading into a road-wheel angle.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
+          <t>Steering map A2 (quadratic)</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>sensors.steering_angle.map_a2</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Quadratic term — the ratio falling off toward lock.</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>-0.000844</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>deg/deg^2</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (team chart; -844E-04 read as -8.44E-04)</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>The steering curve including RWheel</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>Steering chart / kinematics sweep</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>Full lock 23 deg is about 103 deg of handwheel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
           <t>SAS quantization</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>sensors.steering_angle.quant_deg</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>Steering-angle sensor resolution, at the handwheel.</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
+      <c r="E74" s="4" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="F73" s="3" t="inlineStr">
+      <c r="F74" s="3" t="inlineStr">
         <is>
           <t>deg/LSB</t>
         </is>
       </c>
-      <c r="G73" s="7" t="inlineStr">
+      <c r="G74" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER — sensor spec</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
+      <c r="H74" s="3" t="inlineStr">
         <is>
           <t>Sensor spec</t>
         </is>
       </c>
-      <c r="I73" s="3" t="inlineStr">
+      <c r="I74" s="3" t="inlineStr">
         <is>
           <t>Datasheet of the chosen SAS</t>
         </is>
       </c>
-      <c r="J73" s="3" t="inlineStr">
+      <c r="J74" s="3" t="inlineStr">
         <is>
           <t>Steering resolution the VCU actually sees.</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>SENSORS — IMU, yaw gyro and accelerometers</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>IMU gyro noise (1σ)</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>sigma_g</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>sensors.imu_6axis.gyro_noise_std</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>Yaw-gyro 1-sigma noise.</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>0.005236</t>
-        </is>
-      </c>
-      <c r="F75" s="3" t="inlineStr">
-        <is>
-          <t>rad/s (entered as deg/s, 1 sigma)</t>
-        </is>
-      </c>
-      <c r="G75" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER — IMU spec</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>IMU datasheet numbers</t>
-        </is>
-      </c>
-      <c r="I75" s="3" t="inlineStr">
-        <is>
-          <t>Chosen IMU's spec sheet</t>
-        </is>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>Goes straight into the TV feedback — sets how clean the yaw control can be.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>IMU gyro bias</t>
+          <t>IMU gyro noise (1σ)</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>b_g</t>
+          <t>sigma_g</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>sensors.imu_6axis.gyro_bias</t>
+          <t>sensors.imu_6axis.gyro_noise_std</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Constant yaw-gyro zero offset.</t>
+          <t>Yaw-gyro 1-sigma noise.</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>0.001745</t>
+          <t>0.005236</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>rad/s (entered as deg/s)</t>
+          <t>rad/s (entered as deg/s, 1 sigma)</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — uncalibrated bias</t>
+          <t>PLACEHOLDER — IMU spec</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
@@ -3824,212 +3824,212 @@
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>Chosen IMU's spec sheet, then a stationary calibration on the car</t>
+          <t>Chosen IMU's spec sheet</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>Biases the yaw-rate error the TV controller integrates.</t>
+          <t>Goes straight into the TV feedback — sets how clean the yaw control can be.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>VCU gyro low-pass</t>
+          <t>IMU gyro bias</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>f_c</t>
+          <t>b_g</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>sensors.imu_6axis.lpf_hz</t>
+          <t>sensors.imu_6axis.gyro_bias</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>First-order low-pass the VCU applies to the gyro before feedback.</t>
+          <t>Constant yaw-gyro zero offset.</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0.001745</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>Hz</t>
+          <t>rad/s (entered as deg/s)</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — VCU filter choice</t>
+          <t>PLACEHOLDER — uncalibrated bias</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>IMU datasheet numbers</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>Software choice; tune against noise</t>
+          <t>Chosen IMU's spec sheet, then a stationary calibration on the car</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>Trade: more filtering = less dither but more phase lag in the yaw loop.</t>
+          <t>Biases the yaw-rate error the TV controller integrates.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
+          <t>VCU gyro low-pass</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>f_c</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>sensors.imu_6axis.lpf_hz</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>First-order low-pass the VCU applies to the gyro before feedback.</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>Hz</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — VCU filter choice</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>Software choice; tune against noise</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>Trade: more filtering = less dither but more phase lag in the yaw loop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
           <t>IMU accel noise</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>sigma_a</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>sensors.imu_6axis.accel_noise_std</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>Accelerometer 1-sigma noise (ax, ay channels).</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
+      <c r="E79" s="4" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="F78" s="3" t="inlineStr">
+      <c r="F79" s="3" t="inlineStr">
         <is>
           <t>m/s^2</t>
         </is>
       </c>
-      <c r="G78" s="7" t="inlineStr">
+      <c r="G79" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER — IMU spec</t>
         </is>
       </c>
-      <c r="H78" s="3" t="inlineStr">
+      <c r="H79" s="3" t="inlineStr">
         <is>
           <t>IMU datasheet</t>
         </is>
       </c>
-      <c r="I78" s="3" t="inlineStr">
+      <c r="I79" s="3" t="inlineStr">
         <is>
           <t>Spec sheet</t>
         </is>
       </c>
-      <c r="J78" s="3" t="inlineStr">
+      <c r="J79" s="3" t="inlineStr">
         <is>
           <t>Feeds future estimation (vx observer, validation logging).</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>CONTROLLER GAINS — tuned in-sim; retune whenever vehicle/tire numbers move</t>
-        </is>
-      </c>
-    </row>
     <row r="80">
-      <c r="A80" s="3" t="inlineStr">
-        <is>
-          <t>s-diff proportional gain</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>Kp</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t>controllers.kp_sdiff</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t>Software differential: torque per rad/s of wheel-speed-difference error.</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F80" s="3" t="inlineStr">
-        <is>
-          <t>N*m/(rad/s)</t>
-        </is>
-      </c>
-      <c r="G80" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim)</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I80" s="3" t="inlineStr">
-        <is>
-          <t>Re-tune in sim: oscillation = too hot, sluggish = too cold</t>
-        </is>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>How hard the s-diff fights wheel-speed error.</t>
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>CONTROLLER CONSTANTS — open-loop s-diff, mirrored from sdiff.c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>s-diff integral gain</t>
+          <t>Steering ratio (handwheel : road-wheel)</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Ki</t>
+          <t>STEERING_RATIO</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>controllers.ki_sdiff</t>
+          <t>controllers.steering_ratio</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Software differential: torque per accumulated rad of error.</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>Divides handwheel angle down to road-wheel angle in sdiff.c.</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>5.4</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>N*m/rad</t>
-        </is>
-      </c>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim)</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (sdiff.c STEERING_RATIO)</t>
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr">
@@ -4039,101 +4039,101 @@
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>Team steering chart (sensors/steering_angle/params.yaml, A1 term)</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>Removes steady error (e.g. constant-radius corners).</t>
+          <t>Mirrors the C constant. NOT used by the Python controller — the sim gets its road-wheel angle from the SAS polynomial map in model/sensors/steering_angle/sas.py, which implies ~3.2:1 near center and ~7.5:1 at lock. The flat 5.4 here and that map disagree; the map is the more accurate model of the real linkage.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>s-diff integral clamp</t>
+          <t>Steer angle at full derate</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DELTA_MAX</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>controllers.i_sdiff_max</t>
+          <t>controllers.delta_max</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Anti-windup limit on the s-diff integral term.</t>
+          <t>Normalizes steer angle to 0-1 in sdiff.c (delta_norm), clamped at 1.</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>0.03491</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>N*m</t>
-        </is>
-      </c>
-      <c r="G82" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim)</t>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>SUSPECT — mirrors sdiff.c DELTA_MAX, but see note</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Confirmation from the VCU team that 2 deg is intended (see note)</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>dev/sdiff.c on the S-diff branch</t>
         </is>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>Stops the integral charging up during saturation and overshooting after.</t>
+          <t>NOT full lock — this is the angle at which the derate SATURATES. At 2 deg of road wheel (about 10.8 deg of handwheel at 5.4:1) delta_norm hits 1.0 and the inner-wheel cut is already at its maximum, so the s-diff behaves close to on/off rather than progressive.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>s-diff torque-split clamp</t>
+          <t>Friction-budget derate gain</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>dT_max</t>
+          <t>K_DERATE</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>controllers.dt_sdiff_max</t>
+          <t>controllers.k_derate</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Hard cap on how much torque the s-diff may transfer between the wheels.</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>How much total torque (both wheels) falls off as steer angle rises.</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>N*m</t>
-        </is>
-      </c>
-      <c r="G83" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim) — SAFETY-CRITICAL</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (sdiff.c K_DERATE)</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
@@ -4143,49 +4143,49 @@
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>Sized in sim against the spin scenario</t>
+          <t>dev/sdiff.c on the S-diff branch</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>Without it, an unbounded speed-difference PI dumps torque onto the loaded outer tire near the limit, burns its lateral grip (friction circle), and power-oversteers the car — the sim demonstrates exactly this if you raise the cap. The s-diff's job is trimming wheel speeds, not large torque moves.</t>
+          <t>Deliberately zeroed in commit 18f9bc7 before the first on-car run: the shared budget cut is OFF, so f = 1.0 always and f_min below is inert. The s-diff currently biases left/right without taking any total power away.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>TV proportional gain</t>
+          <t>Inner-wheel derate gain</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Kp</t>
+          <t>K_INNER</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>controllers.kp_tv</t>
+          <t>controllers.k_inner</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Torque vectoring: yaw moment per rad/s of yaw-rate error.</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>2,500</t>
+          <t>Torque cut applied to the inner (unloaded) wheel, scaled by delta_norm.</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>0.42</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>N*m/(rad/s)</t>
-        </is>
-      </c>
-      <c r="G84" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim)</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (sdiff.c K_INNER, tuned on car)</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
@@ -4195,49 +4195,49 @@
       </c>
       <c r="I84" s="3" t="inlineStr">
         <is>
-          <t>Re-tune in sim</t>
+          <t>Tuned on car across the PNR sessions</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>How hard TV chases the yaw reference.</t>
+          <t>The whole point of the s-diff: keep the inner wheel from spinning up. At full delta_norm the inner wheel gets 58% of the base torque. This is the ONE constant with real on-car provenance — 0.35 (run #1) -&gt; 0.45 (run #2, 3bd6d88) -&gt; 0.42 (run #3, 5df1baf).</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>TV integral gain</t>
+          <t>Friction-budget floor</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Ki</t>
+          <t>F_MIN</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>controllers.ki_tv</t>
+          <t>controllers.f_min</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>Torque vectoring: yaw moment per accumulated rad of error.</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>1,000</t>
+          <t>Lowest the shared (both-wheel) torque multiplier can fall to.</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>0.5</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>N*m/rad</t>
-        </is>
-      </c>
-      <c r="G85" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim)</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (sdiff.c F_MIN)</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
@@ -4247,101 +4247,101 @@
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>dev/sdiff.c on the S-diff branch</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>Steady-state yaw accuracy in long corners.</t>
+          <t>Floors the k_derate budget cut. INERT while k_derate = 0 — f never leaves 1.0, so this clamp is never reached. It matters again the moment anyone turns the shared derate back on.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>TV integral clamp</t>
+          <t>Steering deadband</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
+          <t>DEADBAND</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>controllers.deadband</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>Road-wheel angle band around center treated as "straight" (no split).</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>0.01745</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (sdiff.c DEADBAND)</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C86" s="3" t="inlineStr">
-        <is>
-          <t>controllers.i_tv_max</t>
-        </is>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t>Anti-windup limit on the TV integral.</t>
-        </is>
-      </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F86" s="3" t="inlineStr">
-        <is>
-          <t>N*m</t>
-        </is>
-      </c>
-      <c r="G86" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim)</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="I86" s="3" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>dev/sdiff.c on the S-diff branch</t>
         </is>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>Bounds windup when the reference is unreachable (e.g. full lock at speed).</t>
+          <t>Stops the inner/outer split from chattering when the driver is nominally straight. 1 deg of road wheel is about 5.4 deg of handwheel, comfortably above the SAS quantization (0.5 deg at the handwheel).</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>Yaw-moment clamp</t>
+          <t>Slew rate</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Mz_max</t>
+          <t>RATE</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>controllers.mz_max</t>
+          <t>controllers.rate</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Clamp on total commanded yaw moment.</t>
-        </is>
-      </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>600</t>
+          <t>Max speed the friction-budget and left/right multipliers may change, per second.</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>N*m</t>
-        </is>
-      </c>
-      <c r="G87" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim)</t>
+          <t>Hz</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (sdiff.c RATE)</t>
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr">
@@ -4351,192 +4351,140 @@
       </c>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>dev/sdiff.c on the S-diff branch</t>
         </is>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>Keeps TV authority bounded.</t>
+          <t>Without slew limiting, torque would jump discontinuously at the deadband edges. At 1.0/s the full 0.42 inner cut takes 0.42 s to apply — far slower than any sensor or loop latency in the stack, which is why loop delay is not modeled here.</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t>Reference aggressiveness</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>SOFTWARE-IN-THE-LOOP (sil/)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>SIL firmware boot time</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
-        <is>
-          <t>controllers.ay_frac</t>
-        </is>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>The yaw-rate reference is capped at this fraction of the friction-limited lateral acceleration.</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
-      <c r="F88" s="3" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="G88" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim)</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>sil.boot_s</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>How long the real firmware is left to boot — bench check (55 ms) plus the ADC settle loop (1 s) — before a maneuver's t = 0, measured on the firmware's own clock.</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — from main.c / initializations.c</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>The firmware's true settle time</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>Read main.c / initializations.c, or instrument the boot</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>Too short and the first samples come from an unsettled ADC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>NUMERICAL GUARDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>Low-speed guard</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>v_eps</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>numerical.v_eps</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>Minimum speed used in slip-angle / slip-ratio denominators.</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>NUMERICAL GUARD</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I88" s="3" t="inlineStr">
-        <is>
-          <t>Same</t>
-        </is>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>0.95 = ask for 95% of what grip allows — margin against an optimistic reference.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>SOFTWARE-IN-THE-LOOP (sil/)</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
-        <is>
-          <t>SIL firmware boot time</t>
-        </is>
-      </c>
-      <c r="B90" s="3" t="inlineStr">
+      <c r="I91" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t>sil.boot_s</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>How long the real firmware is left to boot — bench check (55 ms) plus the ADC settle loop (1 s) — before a maneuver's t = 0, measured on the firmware's own clock.</t>
-        </is>
-      </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="F90" s="3" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="G90" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER — from main.c / initializations.c</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>The firmware's true settle time</t>
-        </is>
-      </c>
-      <c r="I90" s="3" t="inlineStr">
-        <is>
-          <t>Read main.c / initializations.c, or instrument the boot</t>
-        </is>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>Too short and the first samples come from an unsettled ADC.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>NUMERICAL GUARDS</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>Low-speed guard</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>v_eps</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="inlineStr">
-        <is>
-          <t>numerical.v_eps</t>
-        </is>
-      </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t>Minimum speed used in slip-angle / slip-ratio denominators.</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="F92" s="3" t="inlineStr">
-        <is>
-          <t>m/s</t>
-        </is>
-      </c>
-      <c r="G92" s="3" t="inlineStr">
-        <is>
-          <t>NUMERICAL GUARD</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I92" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
+      <c r="J91" s="3" t="inlineStr">
         <is>
           <t>Below ~0.5 m/s wheel-slip math is untrustworthy — launches are out of scope until reworked.</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="8" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
         <is>
           <t>Legend:</t>
         </is>
       </c>
-      <c r="B94" s="9" t="inlineStr">
+      <c r="B93" s="9" t="inlineStr">
         <is>
           <t>GREEN value = confirmed for the CURRENT car/driver (or MEASURED). Black = report car, guess, rules, or sim-tuned. Orange status = placeholder/needs attention. Every row is generated from a params.yaml file — edit the number there, not here.</t>
         </is>
@@ -4546,23 +4494,23 @@
   <autoFilter ref="A1:J1"/>
   <mergeCells count="18">
     <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A36:J36"/>
-    <mergeCell ref="A79:J79"/>
-    <mergeCell ref="A89:J89"/>
-    <mergeCell ref="A74:J74"/>
-    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A75:J75"/>
+    <mergeCell ref="A80:J80"/>
+    <mergeCell ref="A61:J61"/>
+    <mergeCell ref="A88:J88"/>
     <mergeCell ref="A9:J9"/>
-    <mergeCell ref="A27:J27"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A62:J62"/>
-    <mergeCell ref="A67:J67"/>
-    <mergeCell ref="A91:J91"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A55:J55"/>
-    <mergeCell ref="A69:J69"/>
-    <mergeCell ref="B94:J94"/>
+    <mergeCell ref="A56:J56"/>
+    <mergeCell ref="A70:J70"/>
+    <mergeCell ref="B93:J93"/>
+    <mergeCell ref="A35:J35"/>
     <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A60:J60"/>
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A90:J90"/>
+    <mergeCell ref="A41:J41"/>
+    <mergeCell ref="A68:J68"/>
+    <mergeCell ref="A63:J63"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4574,7 +4522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4767,7 +4715,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>The signal TV controls. Its sensor is the one non-negotiable hardware item for TV.</t>
+          <t>Sets the s-diff wheel-speed target (r·track/r_wheel). Its sensor is a non-negotiable hardware item.</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4752,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>vx feeds the yaw reference and slip math; vy is why sideslip needs estimation on the real car.</t>
+          <t>vx feeds the slip math; vy is why sideslip needs estimation on the real car.</t>
         </is>
       </c>
     </row>
@@ -4841,7 +4789,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>The honest 'is the car sliding' number. TV holding yaw while β grows to 22° = a drift (found in run 007).</t>
+          <t>The honest 'is the car sliding' number.</t>
         </is>
       </c>
     </row>
@@ -5026,7 +4974,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>The quantity TV commands. (track/2)·ΔFx of it comes from the torque split.</t>
+          <t>(track/2)·ΔFx of it comes from the torque split.</t>
         </is>
       </c>
     </row>
@@ -5070,12 +5018,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Yaw-rate reference</t>
+          <t>Torque split</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>r_ref</t>
+          <t>ΔT</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -5085,131 +5033,94 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>What the driver's inputs IMPLY they want: bicycle model of steer + speed, capped by friction.</t>
+          <t>The left/right torque difference: ΔT = ΔT_sdiff, then limits applied.</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>r_ref = vx·δ/(L + K_us·vx²), |r_ref·vx| ≤ 0.95·µ·g_effective</t>
+          <t>Controller output every update</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Computed in the VCU from steering sensor + speed estimate</t>
+          <t>Commanded over CAN to the AMK inverters; they report actual torque back</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>TV steers the car toward this. Known gap: it has no sideslip term — at full lock it will happily command a drift.</t>
+          <t>The single actuator this whole project exists to command.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Torque split</t>
+          <t>Wheel torques</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>ΔT</t>
+          <t>T_RL, T_RR</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>controllers.py</t>
+          <t>controllers.py output</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>The left/right torque difference: ΔT = ΔT_sdiff + ΔT_tv, then limits applied.</t>
+          <t>Final per-wheel torque commands after every limit (peak, regen, power caps).</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Controller output every update</t>
+          <t>Base ± ΔT/2, then the limits chain</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Commanded over CAN to the AMK inverters; they report actual torque back</t>
+          <t>AMK inverters accept torque setpoints and report actuals over CAN</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>The single actuator this whole project exists to command.</t>
+          <t>What actually gets sent. The limits chain can silently shrink ΔT at high speed — log requested vs delivered on the car.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Wheel torques</t>
+          <t>Total drive power</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>T_RL, T_RR</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>controllers.py output</t>
+          <t>logged</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Final per-wheel torque commands after every limit (peak, regen, power caps).</t>
+          <t>Mechanical power at the wheels: T_RL·ω_RL + T_RR·ω_RR.</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Base ± ΔT/2, then the limits chain</t>
+          <t>Computed from torques × speeds</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>AMK inverters accept torque setpoints and report actuals over CAN</t>
+          <t>Rules energy meter measures the electrical version at the accumulator</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>What actually gets sent. The limits chain can silently shrink ΔT at high speed — log requested vs delivered on the car.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Total drive power</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>logged</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Mechanical power at the wheels: T_RL·ω_RL + T_RR·ω_RR.</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Computed from torques × speeds</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Rules energy meter measures the electrical version at the accumulator</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>The 80 kW rules cap lives here (sim: mechanical; real: electrical — real car hits it ~10–15% sooner).</t>
         </is>
@@ -5283,7 +5194,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>How the car answers a sudden steering input: rise time, overshoot, steady-state accuracy. THE test for tuning TV gains (Kp = response speed, Ki = steady error).</t>
+          <t>How the car answers a sudden steering input: rise time, overshoot, steady-state accuracy.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -5293,12 +5204,12 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Steady-state yaw rate ON the reference → yaw RMSE (run 015: TV 0.011 vs open 0.034 rad/s = 3× precision). NO overshoot/oscillation in the yaw trace (oscillation = gains too hot). Sideslip β &lt; ~1°.</t>
+          <t>NO overshoot/oscillation in the yaw trace (oscillation = gains too hot). Sideslip β &lt; ~1°.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>TV configs must win yaw RMSE; all configs stable.</t>
+          <t>All configs stable.</t>
         </is>
       </c>
     </row>
@@ -5357,12 +5268,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Yaw RMSE through reversals; β bounded and symmetric; amplitude NOT growing cycle to cycle (growth = impending spin — exactly how open &amp; s-diff-only died at full lock); Δω flips sign cleanly each reversal.</t>
+          <t>β bounded and symmetric; amplitude NOT growing cycle to cycle (growth = impending spin); Δω flips sign cleanly each reversal.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>TV configs track through reversals; nothing diverges at the default point.</t>
+          <t>Nothing diverges at the default point.</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5322,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>The physical steering lock — robustness test point, not an operating point (at 40 mph the friction cap saturates the yaw reference at ~5°).</t>
+          <t>The physical steering lock — robustness test point, not an operating point.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -5421,12 +5332,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Full-lock hairpin: the s-diff κ-containment headline. Full-lock slalom at 40 mph: which configs survive (TV yes / open &amp; s-diff-only spin). Found the TV-drifts-when-saturated design gap (FINDINGS 8-bis).</t>
+          <t>Full-lock hairpin: the s-diff κ-containment headline. Full-lock slalom at 40 mph: which configs survive.</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>TV configs survive; β stays bounded.</t>
+          <t>β stays bounded.</t>
         </is>
       </c>
     </row>

--- a/docs/datasheets/FSAE-Sim Parameters.xlsx
+++ b/docs/datasheets/FSAE-Sim Parameters.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J93"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1692,138 +1692,138 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
+          <t>Driven wheels</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>n_drv</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>drivetrain.driven_wheels</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>How many wheels receive drive torque. 4 = one motor per upright; 2 = the rear pair only, which is what the current build runs.</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (four motors fitted, the rear pair commissioned)</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Which inverters are commissioned on the car</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Powertrain: count enabled inverters</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>The scale between "peak torque at ONE wheel" and "peak torque the driver can ask for". Every axle-torque budget in the sim is n_drv * T_wheel_max: the maneuver throttle steps, the APPS pedal map, the driver adapter's exact inverse of it, and the plot ceilings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
           <t>Regen speed cutoff</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>drivetrain.regen_speed_cutoff</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Below this speed no negative (regen) torque is commanded.</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>m/s (~5 km/h)</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>RULES VALUE (approx.)</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>Nothing (rulebook)</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>Confirm in the current-year rulebook</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>Rules restrict regen near standstill; also keeps the sim's low-speed slip math out of its untrustworthy zone.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>AERO</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Lift coefficient</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>C_L</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>aero.cl_coeff</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Lift (downforce) coefficient, referenced to frontal_area.</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>3.18</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>FROM REPORT (old car's aero)</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>Current car's downforce coefficient</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>CFD, then straight-line coast-down / load-cell validation</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>Downforce = 0.5*rho*C_L*A*v^2 — free grip that grows with speed^2.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Drag coefficient</t>
+          <t>Lift coefficient</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>C_D</t>
+          <t>C_L</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>aero.cd_coeff</t>
+          <t>aero.cl_coeff</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Drag coefficient, same reference area.</t>
+          <t>Lift (downforce) coefficient, referenced to frontal_area.</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -1838,368 +1838,368 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Current car's drag coefficient</t>
+          <t>Current car's downforce coefficient</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>CFD + coast-down test</t>
+          <t>CFD, then straight-line coast-down / load-cell validation</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>Sets top-speed force budget and the torque needed to hold speed in every maneuver.</t>
+          <t>Downforce = 0.5*rho*C_L*A*v^2 — free grip that grows with speed^2.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Frontal area</t>
+          <t>Drag coefficient</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>A_F</t>
+          <t>C_D</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>aero.frontal_area</t>
+          <t>aero.cd_coeff</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Aerodynamic frontal reference area.</t>
+          <t>Drag coefficient, same reference area.</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>1.106</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>m^2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>FROM REPORT</t>
+          <t>FROM REPORT (old car's aero)</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Projected frontal area</t>
+          <t>Current car's drag coefficient</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>CAD projection</t>
+          <t>CFD + coast-down test</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>Only the products C*A enter the physics — keep coefficient and area consistent.</t>
+          <t>Sets top-speed force budget and the torque needed to hold speed in every maneuver.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
+          <t>Frontal area</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>A_F</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>aero.frontal_area</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Aerodynamic frontal reference area.</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>1.106</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>m^2</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>FROM REPORT</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Projected frontal area</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>CAD projection</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>Only the products C*A enter the physics — keep coefficient and area consistent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
           <t>ClA (computed)</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>C_L*A</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>aero.ClA</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>The downforce product the sim actually uses.</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>3.517</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>m^2</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="3">
+      <c r="I33" s="3">
         <f> aero.cl_coeff * aero.frontal_area</f>
         <v/>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>CdA (computed)</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>C_D*A</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>aero.CdA</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>The drag product the sim actually uses.</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>1.504</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>m^2</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="3">
+      <c r="I34" s="3">
         <f> aero.cd_coeff * aero.frontal_area</f>
         <v/>
       </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>Aero balance</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>pct_aero_f</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>aero.balance_front</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Fraction of total downforce landing on the FRONT axle (0.45 = 45/55).</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
+      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER — pure guess</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>Center-of-pressure position</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
         <is>
           <t>CFD (aero team) — ask for CP height too</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>Moves grip between axles as speed rises — shapes high-speed balance directly. One of the last pure guesses outside tires.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>STEERING GEOMETRY</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Ackermann fraction</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>pct_A</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>steering.ackermann_fraction</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>How much of the geometric (100%) Ackermann inner/outer steer split the steering actually delivers. 0.0 = parallel steer (both fronts get the same angle), 1.0 = full geometric Ackermann, negative = anti-Ackermann.</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER (parallel) — RWheel curve needed</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>The steering curve: both wheels' angles vs handwheel angle</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr">
+      <c r="I37" s="3" t="inlineStr">
         <is>
           <t>From the steering chart: the LWheel curve is on file, need the RWheel polynomial from the same chart (or a few x, LWheel, RWheel point triples).</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>Only matters at large steer angles: at 5 deg the split is ~+/-0.2 deg; at the 23 deg full-lock hairpin it is ~+/-4 deg per wheel. Proven to flip whether s-diff-only survives the hairpin (runs 007 vs 008).</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>LOAD TRANSFER</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Front spring rate</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>ks_f</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>loads.spring_rate_front</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>Front suspension spring rate. Used ONLY through its ratio to the rear.</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>19.3</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>N/mm (ratio only)</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>FROM REPORT</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>Front roll stiffness incl. ARBs and motion ratios</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>Suspension team</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>Numerator of the lateral load-transfer split.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Rear spring rate</t>
+          <t>Front spring rate</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>ks_r</t>
+          <t>ks_f</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>loads.spring_rate_rear</t>
+          <t>loads.spring_rate_front</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Rear suspension spring rate. Used ONLY through its ratio to the front.</t>
+          <t>Front suspension spring rate. Used ONLY through its ratio to the rear.</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>Rear roll stiffness incl. ARBs and motion ratios</t>
+          <t>Front roll stiffness incl. ARBs and motion ratios</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -2224,144 +2224,144 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>Denominator half of the lateral load-transfer split.</t>
+          <t>Numerator of the lateral load-transfer split.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
+          <t>Rear spring rate</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>ks_r</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>loads.spring_rate_rear</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Rear suspension spring rate. Used ONLY through its ratio to the front.</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>24.8</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>N/mm (ratio only)</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>FROM REPORT</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Rear roll stiffness incl. ARBs and motion ratios</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>Suspension team</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>Denominator half of the lateral load-transfer split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
           <t>Front lateral-transfer fraction</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>loads.lat_transfer_frac_front</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Share of total LATERAL load transfer reacted by the FRONT axle, set by the front/rear roll-stiffness split.</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>0.4376</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>FROM REPORT (spring-rate ratio only) — crude</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>Front vs rear roll stiffness</t>
         </is>
       </c>
-      <c r="I40" s="3">
+      <c r="I41" s="3">
         <f> loads.spring_rate_front / (loads.spring_rate_front + loads.spring_rate_rear)</f>
         <v/>
       </c>
-      <c r="J40" s="3" t="inlineStr">
+      <c r="J41" s="3" t="inlineStr">
         <is>
           <t>Which axle eats the load transfer = which axle loses grip first — trades understeer/oversteer at the limit.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>TIRES — TTC ROUND 9 FIT (R20 compound, 2026-08-31); surrogate sizes, road µ = belt × 0.67 pending skidpad</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>Belt→road grip scale</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>tires.mu_road_scale</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Belt-&gt;asphalt grip scaling. Calspan's sandpaper belt grips harder than track asphalt; common practice scales the fitted peak mu by ~0.65-0.70 for on-road prediction (stiffnesses/shapes carry over unscaled).</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>0.67</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G42" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER — skidpad measures this</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>Steady-state skidpad lateral g</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>Skidpad test vs sim prediction</t>
-        </is>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>Multiplies EVERY grip number — the single biggest absolute-accuracy lever left. VALIDATE on skidpad; that measurement replaces this guess with truth.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Belt peak µ, lateral</t>
+          <t>Belt→road grip scale</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>mu_belt_y</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>tires.belt_mu_lat</t>
+          <t>tires.mu_road_scale</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Peak LATERAL friction coefficient as fitted on the Calspan belt.</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>2.593</t>
+          <t>Belt-&gt;asphalt grip scaling. Calspan's sandpaper belt grips harder than track asphalt; common practice scales the fitted peak mu by ~0.65-0.70 for on-road prediction (stiffnesses/shapes carry over unscaled).</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>0.67</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -2369,51 +2369,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G43" s="6" t="inlineStr">
-        <is>
-          <t>TTC FIT R9</t>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — skidpad measures this</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Steady-state skidpad lateral g</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>tire_fit.py on Round 9 cornering runs (surrogate spread +/-6%)</t>
+          <t>Skidpad test vs sim prediction</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>Scaled by mu_road_scale to give the road value the sim uses.</t>
+          <t>Multiplies EVERY grip number — the single biggest absolute-accuracy lever left. VALIDATE on skidpad; that measurement replaces this guess with truth.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Belt peak µ, longitudinal</t>
+          <t>Belt peak µ, lateral</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>mu_belt_x</t>
+          <t>mu_belt_y</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>tires.belt_mu_long</t>
+          <t>tires.belt_mu_lat</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Peak LONGITUDINAL friction coefficient as fitted on the belt.</t>
+          <t>Peak LATERAL friction coefficient as fitted on the Calspan belt.</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>2.359</t>
+          <t>2.593</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>tire_fit.py on Round 9 drive/brake runs</t>
+          <t>tire_fit.py on Round 9 cornering runs (surrogate spread +/-6%)</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -2445,279 +2445,279 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
+          <t>Belt peak µ, longitudinal</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>mu_belt_x</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>tires.belt_mu_long</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Peak LONGITUDINAL friction coefficient as fitted on the belt.</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>2.359</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>TTC FIT R9</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>tire_fit.py on Round 9 drive/brake runs</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>Scaled by mu_road_scale to give the road value the sim uses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
           <t>Peak friction coefficient</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>mu0</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>tires.mu0</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Peak grip per newton of load, at the nominal load (road value).</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>1.737</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G45" s="6" t="inlineStr">
+      <c r="G46" s="6" t="inlineStr">
         <is>
           <t>TTC FIT R9</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t>Peak mu at several loads</t>
         </is>
       </c>
-      <c r="I45" s="3">
+      <c r="I46" s="3">
         <f> tires.mu_road_scale * tires.belt_mu_lat</f>
         <v/>
       </c>
-      <c r="J45" s="3" t="inlineStr">
+      <c r="J46" s="3" t="inlineStr">
         <is>
           <t>THE grip number. Max lateral g, spin thresholds, everything — the single most important number in the sim.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>Peak longitudinal friction</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>mu0x</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>tires.mu0_long</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>Drive/brake grip peak — fitted 9% below lateral; combined slip caps on the friction ELLIPSE in tire.py.</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>1.581</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G46" s="6" t="inlineStr">
+      <c r="G47" s="6" t="inlineStr">
         <is>
           <t>TTC FIT R9</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="3">
+      <c r="I47" s="3">
         <f> tires.mu_road_scale * tires.belt_mu_long</f>
         <v/>
       </c>
-      <c r="J46" s="3" t="inlineStr">
+      <c r="J47" s="3" t="inlineStr">
         <is>
           <t>Sets wheelspin threshold and traction capability.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Load sensitivity</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>s_mu</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>tires.s_mu</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>Load sensitivity — how much the friction COEFFICIENT drops as vertical load rises: mu = mu0 * (1 - s_mu*(Fz/Fz_nom - 1)). Shared by the lateral and longitudinal peaks.</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>0.112</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>—/100% load</t>
-        </is>
-      </c>
-      <c r="G47" s="6" t="inlineStr">
-        <is>
-          <t>TTC FIT R9</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>mu at low vs high load</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>Same TTC fit</t>
-        </is>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>The reason load transfer costs grip and torque placement matters at all. Zero would make TV pointless.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
+          <t>Load sensitivity</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>s_mu</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>tires.s_mu</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Load sensitivity — how much the friction COEFFICIENT drops as vertical load rises: mu = mu0 * (1 - s_mu*(Fz/Fz_nom - 1)). Shared by the lateral and longitudinal peaks.</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>0.112</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>—/100% load</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>TTC FIT R9</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>mu at low vs high load</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>Same TTC fit</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>The reason load transfer costs grip and torque placement matters at all. Zero would make TV pointless.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
           <t>Nominal tire load</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>Fz_nom</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>tires.Fz_nom</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>The "nominal" vertical load at which mu0 is defined (~one static corner weight).</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>618.6</t>
         </is>
       </c>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G48" s="3" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>DERIVED (follows the masses automatically)</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="3">
+      <c r="I49" s="3">
         <f> (mass.car_no_driver + mass.driver) * environment.g / 4.0</f>
         <v/>
       </c>
-      <c r="J48" s="3" t="inlineStr">
+      <c r="J49" s="3" t="inlineStr">
         <is>
           <t>Reference point for the load-sensitivity line.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>Front cornering stiffness</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>c_alpha_f</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>tires.c_alpha_front</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>Normalized cornering stiffness of a FRONT tire: lateral force per radian of slip angle, per newton of load (C_alpha = this * Fz).</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>1/rad</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t>TTC FIT R9 (same tire all round)</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>Slope of Fy vs slip angle at small angles</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>TTC cornering sweep</t>
-        </is>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>Front-axle responsiveness; with rear stiffness sets the understeer gradient K_us the TV reference uses.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Rear cornering stiffness</t>
+          <t>Front cornering stiffness</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>c_alpha_r</t>
+          <t>c_alpha_f</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>tires.c_alpha_rear</t>
+          <t>tires.c_alpha_front</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Same, for a REAR tire.</t>
+          <t>Normalized cornering stiffness of a FRONT tire: lateral force per radian of slip angle, per newton of load (C_alpha = this * Fz).</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Same, rear</t>
+          <t>Slope of Fy vs slip angle at small angles</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
@@ -2747,91 +2747,91 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>Rear grip slope — stability side of the understeer gradient.</t>
+          <t>Front-axle responsiveness; with rear stiffness sets the understeer gradient K_us the TV reference uses.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Longitudinal slip stiffness</t>
+          <t>Rear cornering stiffness</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>c_kappa</t>
+          <t>c_alpha_r</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>tires.c_kappa</t>
+          <t>tires.c_alpha_rear</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Normalized longitudinal slip stiffness: drive/brake force per unit slip ratio per newton (C_kappa = this * Fz).</t>
+          <t>Same, for a REAR tire.</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>1/slip</t>
+          <t>1/rad</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>TTC FIT R9</t>
+          <t>TTC FIT R9 (same tire all round)</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>Slope of Fx vs slip ratio</t>
+          <t>Same, rear</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>TTC drive/brake sweep</t>
+          <t>TTC cornering sweep</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>Sets wheel-spin dynamics speed — the s-diff's plant. Gains retune if it moves.</t>
+          <t>Rear grip slope — stability side of the understeer gradient.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Lateral shape factor</t>
+          <t>Longitudinal slip stiffness</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>C_y</t>
+          <t>c_kappa</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>tires.shape_c_lat</t>
+          <t>tires.c_kappa</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Magic Formula shape factor — how sharply lateral force peaks.</t>
+          <t>Normalized longitudinal slip stiffness: drive/brake force per unit slip ratio per newton (C_kappa = this * Fz).</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>1.397</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1/slip</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
@@ -2841,44 +2841,44 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Curve shape near/past the peak</t>
+          <t>Slope of Fx vs slip ratio</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>TTC fit</t>
+          <t>TTC drive/brake sweep</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>With E_y, sets where the curve peaks (currently 11.6 deg — real slicks ~6-10 deg) and how it lets go.</t>
+          <t>Sets wheel-spin dynamics speed — the s-diff's plant. Gains retune if it moves.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Lateral curvature factor</t>
+          <t>Lateral shape factor</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>E_y</t>
+          <t>C_y</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>tires.curv_e_lat</t>
+          <t>tires.shape_c_lat</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Magic Formula curvature factor — fall-off past the lateral peak.</t>
+          <t>Magic Formula shape factor — how sharply lateral force peaks.</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>1.397</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>Post-peak behavior</t>
+          <t>Curve shape near/past the peak</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
@@ -2903,34 +2903,34 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>Gentle vs snappy breakaway — currently more forgiving than a real slick.</t>
+          <t>With E_y, sets where the curve peaks (currently 11.6 deg — real slicks ~6-10 deg) and how it lets go.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Longitudinal shape factor</t>
+          <t>Lateral curvature factor</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>C_x</t>
+          <t>E_y</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>tires.shape_c_long</t>
+          <t>tires.curv_e_lat</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Same idea, drive/brake direction.</t>
+          <t>Magic Formula curvature factor — fall-off past the lateral peak.</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>1.705</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Curve shape</t>
+          <t>Post-peak behavior</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
@@ -2955,125 +2955,125 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>Sets the peak slip ratio (~0.10) — also the replay's red-wheel spin threshold.</t>
+          <t>Gentle vs snappy breakaway — currently more forgiving than a real slick.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
+          <t>Longitudinal shape factor</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>C_x</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>tires.shape_c_long</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Same idea, drive/brake direction.</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>1.705</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>TTC FIT R9</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Curve shape</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>TTC fit</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>Sets the peak slip ratio (~0.10) — also the replay's red-wheel spin threshold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
           <t>Longitudinal curvature factor</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>E_x</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>tires.curv_e_long</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>Fall-off past the longitudinal peak.</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>0.389</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G55" s="6" t="inlineStr">
+      <c r="G56" s="6" t="inlineStr">
         <is>
           <t>TTC FIT R9</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="H56" s="3" t="inlineStr">
         <is>
           <t>Post-peak behavior</t>
         </is>
       </c>
-      <c r="I55" s="3" t="inlineStr">
+      <c r="I56" s="3" t="inlineStr">
         <is>
           <t>TTC fit</t>
         </is>
       </c>
-      <c r="J55" s="3" t="inlineStr">
+      <c r="J56" s="3" t="inlineStr">
         <is>
           <t>How violently a spinning wheel loses force — feeds the wheelspin runaway.</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>SENSORS &amp; VCU — the VCU itself</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>VCU loop rate</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>sensors.vcu.rate_hz</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>VCU control-loop rate — how often sensors are sampled and torque commands are recomputed (physics still integrates at 4 kHz).</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t>Hz</t>
-        </is>
-      </c>
-      <c r="G57" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER — ask software team</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>The real VCU loop rate</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>Software team</t>
-        </is>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>Gains proven stable at 100 Hz (verify.py section H); make it match reality before quoting controller performance.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>Plausibility cut threshold</t>
+          <t>VCU loop rate</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -3083,49 +3083,49 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>sensors.vcu.plaus_apps_cut</t>
+          <t>sensors.vcu.rate_hz</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>APPS percentage above which, while braking, motor power must be cut.</t>
+          <t>VCU control-loop rate — how often sensors are sampled and torque commands are recomputed (physics still integrates at 4 kHz).</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="inlineStr">
-        <is>
-          <t>RULES VALUE (EV.4.7)</t>
+          <t>Hz</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — ask software team</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>The real VCU loop rate</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>Rulebook (confirm current year)</t>
+          <t>Software team</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>Implemented and unit-tested (verify I3); the pedal_check maneuver demonstrates it.</t>
+          <t>Gains proven stable at 100 Hz (verify.py section H); make it match reality before quoting controller performance.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>Plausibility restore threshold</t>
+          <t>Plausibility cut threshold</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -3135,17 +3135,17 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>sensors.vcu.plaus_apps_restore</t>
+          <t>sensors.vcu.plaus_apps_cut</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>APPS percentage the pedal must fall below before power is restored.</t>
+          <t>APPS percentage above which, while braking, motor power must be cut.</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -3170,184 +3170,184 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>The latch that makes the cut a latch and not a flicker.</t>
+          <t>Implemented and unit-tested (verify I3); the pedal_check maneuver demonstrates it.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
+          <t>Plausibility restore threshold</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>sensors.vcu.plaus_apps_restore</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>APPS percentage the pedal must fall below before power is restored.</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>RULES VALUE (EV.4.7)</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>Rulebook (confirm current year)</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>The latch that makes the cut a latch and not a flicker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
           <t>Sensor noise seed</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>sensors.vcu.seed</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>Seed for the sensor-noise generator — runs are exactly repeatable and all four controller configs see IDENTICAL noise.</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F60" s="3" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G60" s="3" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
         <is>
           <t>NUMERICAL GUARD (repeatability)</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
+      <c r="H61" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="3" t="inlineStr">
+      <c r="I61" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J60" s="3" t="inlineStr">
+      <c r="J61" s="3" t="inlineStr">
         <is>
           <t>Fair comparisons and reproducible runs.</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>SENSORS — APPS, accelerator pedal position</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>APPS quantization</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>sensors.throttle_pos.quant_pct</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>Accelerator pedal position resolution.</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="E63" s="4" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="F62" s="3" t="inlineStr">
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>%/LSB</t>
         </is>
       </c>
-      <c r="G62" s="7" t="inlineStr">
+      <c r="G63" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER — sensor spec</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
+      <c r="H63" s="3" t="inlineStr">
         <is>
           <t>APPS sensor spec</t>
         </is>
       </c>
-      <c r="I62" s="3" t="inlineStr">
+      <c r="I63" s="3" t="inlineStr">
         <is>
           <t>Datasheet</t>
         </is>
       </c>
-      <c r="J62" s="3" t="inlineStr">
+      <c r="J63" s="3" t="inlineStr">
         <is>
           <t>Torque request granularity.</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>SENSORS — BPS, brake pressure</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>BPS full range</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>sensors.brake_pressure_sens.range_bar</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>Brake pressure sensor full range.</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="G64" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER — sensor spec</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>BPS spec + brake system pressures</t>
-        </is>
-      </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t>Brake team: line pressure at threshold/full braking</t>
-        </is>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>Sets the pressure that maps to full regen.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>BPS quantization</t>
+          <t>BPS full range</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -3357,22 +3357,22 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>sensors.brake_pressure_sens.quant_bar</t>
+          <t>sensors.brake_pressure_sens.range_bar</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Brake pressure sensor resolution.</t>
+          <t>Brake pressure sensor full range.</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>bar/LSB</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
@@ -3382,24 +3382,24 @@
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>BPS spec</t>
+          <t>BPS spec + brake system pressures</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>Datasheet</t>
+          <t>Brake team: line pressure at threshold/full braking</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>Regen command granularity.</t>
+          <t>Sets the pressure that maps to full regen.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>BPS actuated threshold</t>
+          <t>BPS quantization</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -3409,244 +3409,244 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>sensors.brake_pressure_sens.actuated_bar</t>
+          <t>sensors.brake_pressure_sens.quant_bar</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Pressure above which the brake counts as "actuated" for the rules check.</t>
+          <t>Brake pressure sensor resolution.</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>bar</t>
+          <t>bar/LSB</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — calibration choice</t>
+          <t>PLACEHOLDER — sensor spec</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>Brake system pressures</t>
+          <t>BPS spec</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>Brake team: line pressure at threshold braking</t>
+          <t>Datasheet</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>Defines "braking" for the EV.4.7 plausibility check.</t>
+          <t>Regen command granularity.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
+          <t>BPS actuated threshold</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>sensors.brake_pressure_sens.actuated_bar</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Pressure above which the brake counts as "actuated" for the rules check.</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — calibration choice</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>Brake system pressures</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>Brake team: line pressure at threshold braking</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>Defines "braking" for the EV.4.7 plausibility check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
           <t>Max regen torque</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>sensors.brake_pressure_sens.t_regen_max</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>Total rear-axle REGEN torque at full brake pressure (both motors).</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
+      <c r="E68" s="4" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="F67" s="3" t="inlineStr">
+      <c r="F68" s="3" t="inlineStr">
         <is>
           <t>N*m</t>
         </is>
       </c>
-      <c r="G67" s="7" t="inlineStr">
+      <c r="G68" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER — battery charge limit sets this</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr">
+      <c r="H68" s="3" t="inlineStr">
         <is>
           <t>Allowed charge current -&gt; torque</t>
         </is>
       </c>
-      <c r="I67" s="3" t="inlineStr">
+      <c r="I68" s="3" t="inlineStr">
         <is>
           <t>Accumulator team: max charge C-rate</t>
         </is>
       </c>
-      <c r="J67" s="3" t="inlineStr">
+      <c r="J68" s="3" t="inlineStr">
         <is>
           <t>Caps how much "braking" the sim's BPS can command.</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>SENSORS — WSS, motor resolver over CAN</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>WSS quantization</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>sensors.wheel_speed.quant_rpm</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>Motor-speed resolution over CAN (motor side, before the planetary divide).</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
+      <c r="E70" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="F70" s="3" t="inlineStr">
         <is>
           <t>rpm/LSB</t>
         </is>
       </c>
-      <c r="G69" s="7" t="inlineStr">
+      <c r="G70" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER — AMK CAN resolution</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
+      <c r="H70" s="3" t="inlineStr">
         <is>
           <t>AMK CAN speed resolution</t>
         </is>
       </c>
-      <c r="I69" s="3" t="inlineStr">
+      <c r="I70" s="3" t="inlineStr">
         <is>
           <t>AMK CAN spec</t>
         </is>
       </c>
-      <c r="J69" s="3" t="inlineStr">
+      <c r="J70" s="3" t="inlineStr">
         <is>
           <t>1 motor rpm is about 1.8 mm/s of ground speed — the resolver-over-CAN path is effectively noise-free wheel speed.</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>SENSORS — SAS, steering angle, and the steering map</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>Steering map A0 (intercept)</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>A0</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>sensors.steering_angle.map_a0</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>Constant term of the handwheel -&gt; road-wheel polynomial.</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t>-0.0797</t>
-        </is>
-      </c>
-      <c r="F71" s="3" t="inlineStr">
-        <is>
-          <t>deg (intercept)</t>
-        </is>
-      </c>
-      <c r="G71" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT CAR (team chart)</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>The steering curve including RWheel</t>
-        </is>
-      </c>
-      <c r="I71" s="3" t="inlineStr">
-        <is>
-          <t>Steering chart / kinematics sweep</t>
-        </is>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>Subtracted out to center the map; kept so the raw fit stays visible.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>Steering map A1 (linear)</t>
+          <t>Steering map A0 (intercept)</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A0</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>sensors.steering_angle.map_a1</t>
+          <t>sensors.steering_angle.map_a0</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Linear term — the near-center steering ratio.</t>
+          <t>Constant term of the handwheel -&gt; road-wheel polynomial.</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.0797</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>deg/deg</t>
+          <t>deg (intercept)</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
@@ -3666,44 +3666,44 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>How the VCU turns the SAS reading into a road-wheel angle.</t>
+          <t>Subtracted out to center the map; kept so the raw fit stays visible.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>Steering map A2 (quadratic)</t>
+          <t>Steering map A1 (linear)</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>sensors.steering_angle.map_a2</t>
+          <t>sensors.steering_angle.map_a1</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Quadratic term — the ratio falling off toward lock.</t>
+          <t>Linear term — the near-center steering ratio.</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>-0.000844</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>deg/deg^2</t>
+          <t>deg/deg</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>CURRENT CAR (team chart; -844E-04 read as -8.44E-04)</t>
+          <t>CURRENT CAR (team chart)</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
@@ -3718,155 +3718,155 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>Full lock 23 deg is about 103 deg of handwheel.</t>
+          <t>How the VCU turns the SAS reading into a road-wheel angle.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
+          <t>Steering map A2 (quadratic)</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>sensors.steering_angle.map_a2</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Quadratic term — the ratio falling off toward lock.</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>-0.000844</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>deg/deg^2</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (team chart; -844E-04 read as -8.44E-04)</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>The steering curve including RWheel</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>Steering chart / kinematics sweep</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>Full lock 23 deg is about 103 deg of handwheel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
           <t>SAS quantization</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>sensors.steering_angle.quant_deg</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>Steering-angle sensor resolution, at the handwheel.</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
+      <c r="E75" s="4" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="F74" s="3" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr">
         <is>
           <t>deg/LSB</t>
         </is>
       </c>
-      <c r="G74" s="7" t="inlineStr">
+      <c r="G75" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER — sensor spec</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
+      <c r="H75" s="3" t="inlineStr">
         <is>
           <t>Sensor spec</t>
         </is>
       </c>
-      <c r="I74" s="3" t="inlineStr">
+      <c r="I75" s="3" t="inlineStr">
         <is>
           <t>Datasheet of the chosen SAS</t>
         </is>
       </c>
-      <c r="J74" s="3" t="inlineStr">
+      <c r="J75" s="3" t="inlineStr">
         <is>
           <t>Steering resolution the VCU actually sees.</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>SENSORS — IMU, yaw gyro and accelerometers</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>IMU gyro noise (1σ)</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>sigma_g</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t>sensors.imu_6axis.gyro_noise_std</t>
-        </is>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
-        <is>
-          <t>Yaw-gyro 1-sigma noise.</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>0.005236</t>
-        </is>
-      </c>
-      <c r="F76" s="3" t="inlineStr">
-        <is>
-          <t>rad/s (entered as deg/s, 1 sigma)</t>
-        </is>
-      </c>
-      <c r="G76" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER — IMU spec</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>IMU datasheet numbers</t>
-        </is>
-      </c>
-      <c r="I76" s="3" t="inlineStr">
-        <is>
-          <t>Chosen IMU's spec sheet</t>
-        </is>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>Goes straight into the TV feedback — sets how clean the yaw control can be.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>IMU gyro bias</t>
+          <t>IMU gyro noise (1σ)</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>b_g</t>
+          <t>sigma_g</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>sensors.imu_6axis.gyro_bias</t>
+          <t>sensors.imu_6axis.gyro_noise_std</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Constant yaw-gyro zero offset.</t>
+          <t>Yaw-gyro 1-sigma noise.</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>0.001745</t>
+          <t>0.005236</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>rad/s (entered as deg/s)</t>
+          <t>rad/s (entered as deg/s, 1 sigma)</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — uncalibrated bias</t>
+          <t>PLACEHOLDER — IMU spec</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
@@ -3876,269 +3876,269 @@
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>Chosen IMU's spec sheet, then a stationary calibration on the car</t>
+          <t>Chosen IMU's spec sheet</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>Biases the yaw-rate error the TV controller integrates.</t>
+          <t>Goes straight into the TV feedback — sets how clean the yaw control can be.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>VCU gyro low-pass</t>
+          <t>IMU gyro bias</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>f_c</t>
+          <t>b_g</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>sensors.imu_6axis.lpf_hz</t>
+          <t>sensors.imu_6axis.gyro_bias</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>First-order low-pass the VCU applies to the gyro before feedback.</t>
+          <t>Constant yaw-gyro zero offset.</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0.001745</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>Hz</t>
+          <t>rad/s (entered as deg/s)</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — VCU filter choice</t>
+          <t>PLACEHOLDER — uncalibrated bias</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>IMU datasheet numbers</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>Software choice; tune against noise</t>
+          <t>Chosen IMU's spec sheet, then a stationary calibration on the car</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>Trade: more filtering = less dither but more phase lag in the yaw loop.</t>
+          <t>Biases the yaw-rate error the TV controller integrates.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
+          <t>VCU gyro low-pass</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>f_c</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>sensors.imu_6axis.lpf_hz</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>First-order low-pass the VCU applies to the gyro before feedback.</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>Hz</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — VCU filter choice</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>Software choice; tune against noise</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>Trade: more filtering = less dither but more phase lag in the yaw loop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
           <t>IMU accel noise</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>sigma_a</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>sensors.imu_6axis.accel_noise_std</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>Accelerometer 1-sigma noise (ax, ay channels).</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
+      <c r="E80" s="4" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="F79" s="3" t="inlineStr">
+      <c r="F80" s="3" t="inlineStr">
         <is>
           <t>m/s^2</t>
         </is>
       </c>
-      <c r="G79" s="7" t="inlineStr">
+      <c r="G80" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER — IMU spec</t>
         </is>
       </c>
-      <c r="H79" s="3" t="inlineStr">
+      <c r="H80" s="3" t="inlineStr">
         <is>
           <t>IMU datasheet</t>
         </is>
       </c>
-      <c r="I79" s="3" t="inlineStr">
+      <c r="I80" s="3" t="inlineStr">
         <is>
           <t>Spec sheet</t>
         </is>
       </c>
-      <c r="J79" s="3" t="inlineStr">
+      <c r="J80" s="3" t="inlineStr">
         <is>
           <t>Feeds future estimation (vx observer, validation logging).</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>CONTROLLER CONSTANTS — open-loop s-diff, mirrored from sdiff.c</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>Steering ratio (handwheel : road-wheel)</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>STEERING_RATIO</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>controllers.steering_ratio</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>Divides handwheel angle down to road-wheel angle in sdiff.c.</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>5.4</t>
-        </is>
-      </c>
-      <c r="F81" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G81" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT CAR (sdiff.c STEERING_RATIO)</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I81" s="3" t="inlineStr">
-        <is>
-          <t>Team steering chart (sensors/steering_angle/params.yaml, A1 term)</t>
-        </is>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>Mirrors the C constant. NOT used by the Python controller — the sim gets its road-wheel angle from the SAS polynomial map in model/sensors/steering_angle/sas.py, which implies ~3.2:1 near center and ~7.5:1 at lock. The flat 5.4 here and that map disagree; the map is the more accurate model of the real linkage.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>Steer angle at full derate</t>
+          <t>Steering ratio (handwheel : road-wheel)</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>DELTA_MAX</t>
+          <t>STEERING_RATIO</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>controllers.delta_max</t>
+          <t>controllers.steering_ratio</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Normalizes steer angle to 0-1 in sdiff.c (delta_norm), clamped at 1.</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>0.03491</t>
+          <t>Divides handwheel angle down to road-wheel angle in sdiff.c.</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>5.4</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="G82" s="7" t="inlineStr">
-        <is>
-          <t>SUSPECT — mirrors sdiff.c DELTA_MAX, but see note</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (sdiff.c STEERING_RATIO)</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>Confirmation from the VCU team that 2 deg is intended (see note)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t>dev/sdiff.c on the S-diff branch</t>
+          <t>Team steering chart (sensors/steering_angle/params.yaml, A1 term)</t>
         </is>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>NOT full lock — this is the angle at which the derate SATURATES. At 2 deg of road wheel (about 10.8 deg of handwheel at 5.4:1) delta_norm hits 1.0 and the inner-wheel cut is already at its maximum, so the s-diff behaves close to on/off rather than progressive.</t>
+          <t>Mirrors the C constant. NOT used by the Python controller — the sim gets its road-wheel angle from the SAS polynomial map in model/sensors/steering_angle/sas.py, which implies ~3.2:1 near center and ~7.5:1 at lock. The flat 5.4 here and that map disagree; the map is the more accurate model of the real linkage.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>Friction-budget derate gain</t>
+          <t>Steer angle at full derate</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>K_DERATE</t>
+          <t>DELTA_MAX</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>controllers.k_derate</t>
+          <t>controllers.delta_max</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>How much total torque (both wheels) falls off as steer angle rises.</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>Normalizes steer angle to 0-1 in sdiff.c (delta_norm), clamped at 1.</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>0.03491</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G83" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT CAR (sdiff.c K_DERATE)</t>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>SUSPECT — mirrors sdiff.c DELTA_MAX, but see note</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Confirmation from the VCU team that 2 deg is intended (see note)</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
@@ -4148,34 +4148,34 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>Deliberately zeroed in commit 18f9bc7 before the first on-car run: the shared budget cut is OFF, so f = 1.0 always and f_min below is inert. The s-diff currently biases left/right without taking any total power away.</t>
+          <t>NOT full lock — this is the angle at which the derate SATURATES. At 2 deg of road wheel (about 10.8 deg of handwheel at 5.4:1) delta_norm hits 1.0 and the inner-wheel cut is already at its maximum, so the s-diff behaves close to on/off rather than progressive.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>Inner-wheel derate gain</t>
+          <t>Friction-budget derate gain</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>K_INNER</t>
+          <t>K_DERATE</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>controllers.k_inner</t>
+          <t>controllers.k_derate</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Torque cut applied to the inner (unloaded) wheel, scaled by delta_norm.</t>
+          <t>How much total torque (both wheels) falls off as steer angle rises.</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>CURRENT CAR (sdiff.c K_INNER, tuned on car)</t>
+          <t>CURRENT CAR (sdiff.c K_DERATE)</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
@@ -4195,39 +4195,39 @@
       </c>
       <c r="I84" s="3" t="inlineStr">
         <is>
-          <t>Tuned on car across the PNR sessions</t>
+          <t>dev/sdiff.c on the S-diff branch</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>The whole point of the s-diff: keep the inner wheel from spinning up. At full delta_norm the inner wheel gets 58% of the base torque. This is the ONE constant with real on-car provenance — 0.35 (run #1) -&gt; 0.45 (run #2, 3bd6d88) -&gt; 0.42 (run #3, 5df1baf).</t>
+          <t>Deliberately zeroed in commit 18f9bc7 before the first on-car run: the shared budget cut is OFF, so f = 1.0 always and f_min below is inert. The s-diff currently biases left/right without taking any total power away.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>Friction-budget floor</t>
+          <t>Inner-wheel derate gain</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>F_MIN</t>
+          <t>K_INNER</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>controllers.f_min</t>
+          <t>controllers.k_inner</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>Lowest the shared (both-wheel) torque multiplier can fall to.</t>
+          <t>Torque cut applied to the inner (unloaded) wheel, scaled by delta_norm.</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>CURRENT CAR (sdiff.c F_MIN)</t>
+          <t>CURRENT CAR (sdiff.c K_INNER, tuned on car)</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
@@ -4247,49 +4247,49 @@
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>dev/sdiff.c on the S-diff branch</t>
+          <t>Tuned on car across the PNR sessions</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>Floors the k_derate budget cut. INERT while k_derate = 0 — f never leaves 1.0, so this clamp is never reached. It matters again the moment anyone turns the shared derate back on.</t>
+          <t>The whole point of the s-diff: keep the inner wheel from spinning up. At full delta_norm the inner wheel gets 58% of the base torque. This is the ONE constant with real on-car provenance — 0.35 (run #1) -&gt; 0.45 (run #2, 3bd6d88) -&gt; 0.42 (run #3, 5df1baf).</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>Steering deadband</t>
+          <t>Friction-budget floor</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>DEADBAND</t>
+          <t>F_MIN</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>controllers.deadband</t>
+          <t>controllers.f_min</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Road-wheel angle band around center treated as "straight" (no split).</t>
+          <t>Lowest the shared (both-wheel) torque multiplier can fall to.</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>0.01745</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>CURRENT CAR (sdiff.c DEADBAND)</t>
+          <t>CURRENT CAR (sdiff.c F_MIN)</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
@@ -4304,187 +4304,239 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>Stops the inner/outer split from chattering when the driver is nominally straight. 1 deg of road wheel is about 5.4 deg of handwheel, comfortably above the SAS quantization (0.5 deg at the handwheel).</t>
+          <t>Floors the k_derate budget cut. INERT while k_derate = 0 — f never leaves 1.0, so this clamp is never reached. It matters again the moment anyone turns the shared derate back on.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
+          <t>Steering deadband</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>DEADBAND</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>controllers.deadband</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>Road-wheel angle band around center treated as "straight" (no split).</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>0.01745</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (sdiff.c DEADBAND)</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>dev/sdiff.c on the S-diff branch</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>Stops the inner/outer split from chattering when the driver is nominally straight. 1 deg of road wheel is about 5.4 deg of handwheel, comfortably above the SAS quantization (0.5 deg at the handwheel).</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
           <t>Slew rate</t>
         </is>
       </c>
-      <c r="B87" s="3" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>RATE</t>
         </is>
       </c>
-      <c r="C87" s="3" t="inlineStr">
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>controllers.rate</t>
         </is>
       </c>
-      <c r="D87" s="3" t="inlineStr">
+      <c r="D88" s="3" t="inlineStr">
         <is>
           <t>Max speed the friction-budget and left/right multipliers may change, per second.</t>
         </is>
       </c>
-      <c r="E87" s="5" t="inlineStr">
+      <c r="E88" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F87" s="3" t="inlineStr">
+      <c r="F88" s="3" t="inlineStr">
         <is>
           <t>Hz</t>
         </is>
       </c>
-      <c r="G87" s="6" t="inlineStr">
+      <c r="G88" s="6" t="inlineStr">
         <is>
           <t>CURRENT CAR (sdiff.c RATE)</t>
         </is>
       </c>
-      <c r="H87" s="3" t="inlineStr">
+      <c r="H88" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="3" t="inlineStr">
+      <c r="I88" s="3" t="inlineStr">
         <is>
           <t>dev/sdiff.c on the S-diff branch</t>
         </is>
       </c>
-      <c r="J87" s="3" t="inlineStr">
+      <c r="J88" s="3" t="inlineStr">
         <is>
           <t>Without slew limiting, torque would jump discontinuously at the deadband edges. At 1.0/s the full 0.42 inner cut takes 0.42 s to apply — far slower than any sensor or loop latency in the stack, which is why loop delay is not modeled here.</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>SOFTWARE-IN-THE-LOOP (sil/)</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="3" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>SIL firmware boot time</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C89" s="3" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>sil.boot_s</t>
         </is>
       </c>
-      <c r="D89" s="3" t="inlineStr">
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>How long the real firmware is left to boot — bench check (55 ms) plus the ADC settle loop (1 s) — before a maneuver's t = 0, measured on the firmware's own clock.</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
+      <c r="E90" s="4" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="F89" s="3" t="inlineStr">
+      <c r="F90" s="3" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="G89" s="7" t="inlineStr">
+      <c r="G90" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER — from main.c / initializations.c</t>
         </is>
       </c>
-      <c r="H89" s="3" t="inlineStr">
+      <c r="H90" s="3" t="inlineStr">
         <is>
           <t>The firmware's true settle time</t>
         </is>
       </c>
-      <c r="I89" s="3" t="inlineStr">
+      <c r="I90" s="3" t="inlineStr">
         <is>
           <t>Read main.c / initializations.c, or instrument the boot</t>
         </is>
       </c>
-      <c r="J89" s="3" t="inlineStr">
+      <c r="J90" s="3" t="inlineStr">
         <is>
           <t>Too short and the first samples come from an unsettled ADC.</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>NUMERICAL GUARDS</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
         <is>
           <t>Low-speed guard</t>
         </is>
       </c>
-      <c r="B91" s="3" t="inlineStr">
+      <c r="B92" s="3" t="inlineStr">
         <is>
           <t>v_eps</t>
         </is>
       </c>
-      <c r="C91" s="3" t="inlineStr">
+      <c r="C92" s="3" t="inlineStr">
         <is>
           <t>numerical.v_eps</t>
         </is>
       </c>
-      <c r="D91" s="3" t="inlineStr">
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>Minimum speed used in slip-angle / slip-ratio denominators.</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
+      <c r="E92" s="4" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="F91" s="3" t="inlineStr">
+      <c r="F92" s="3" t="inlineStr">
         <is>
           <t>m/s</t>
         </is>
       </c>
-      <c r="G91" s="3" t="inlineStr">
+      <c r="G92" s="3" t="inlineStr">
         <is>
           <t>NUMERICAL GUARD</t>
         </is>
       </c>
-      <c r="H91" s="3" t="inlineStr">
+      <c r="H92" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="3" t="inlineStr">
+      <c r="I92" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J91" s="3" t="inlineStr">
+      <c r="J92" s="3" t="inlineStr">
         <is>
           <t>Below ~0.5 m/s wheel-slip math is untrustworthy — launches are out of scope until reworked.</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="8" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
         <is>
           <t>Legend:</t>
         </is>
       </c>
-      <c r="B93" s="9" t="inlineStr">
+      <c r="B94" s="9" t="inlineStr">
         <is>
           <t>GREEN value = confirmed for the CURRENT car/driver (or MEASURED). Black = report car, guess, rules, or sim-tuned. Orange status = placeholder/needs attention. Every row is generated from a params.yaml file — edit the number there, not here.</t>
         </is>
@@ -4494,23 +4546,23 @@
   <autoFilter ref="A1:J1"/>
   <mergeCells count="18">
     <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A75:J75"/>
-    <mergeCell ref="A80:J80"/>
-    <mergeCell ref="A61:J61"/>
-    <mergeCell ref="A88:J88"/>
+    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="A89:J89"/>
     <mergeCell ref="A9:J9"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A56:J56"/>
-    <mergeCell ref="A70:J70"/>
-    <mergeCell ref="B93:J93"/>
-    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="A62:J62"/>
+    <mergeCell ref="B94:J94"/>
+    <mergeCell ref="A91:J91"/>
+    <mergeCell ref="A69:J69"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A57:J57"/>
+    <mergeCell ref="A38:J38"/>
     <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A28:J28"/>
-    <mergeCell ref="A90:J90"/>
-    <mergeCell ref="A41:J41"/>
-    <mergeCell ref="A68:J68"/>
-    <mergeCell ref="A63:J63"/>
+    <mergeCell ref="A81:J81"/>
+    <mergeCell ref="A64:J64"/>
+    <mergeCell ref="A42:J42"/>
+    <mergeCell ref="A76:J76"/>
+    <mergeCell ref="A71:J71"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/datasheets/FSAE-Sim Parameters.xlsx
+++ b/docs/datasheets/FSAE-Sim Parameters.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J94"/>
+  <dimension ref="A1:J96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1588,22 +1588,22 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Wheel spin inertia</t>
+          <t>Wheel spin inertia, rear corner</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>I_w</t>
+          <t>I_w,r</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>drivetrain.I_wheel</t>
+          <t>drivetrain.I_wheel_rear</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Spin inertia of ONE rear corner about the axle: tire + rim + brake rotor + hub + (motor rotor inertia * gear_ratio^2).</t>
+          <t>Spin inertia of ONE REAR corner about the axle: tire + rim + brake rotor + hub + (motor rotor inertia * gear_ratio^2).</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Rotating inertia of one corner</t>
+          <t>Rotating inertia of one rear corner</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -1633,249 +1633,248 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>Sets how fast an unloaded wheel spins up — the s-diff's whole problem. Controller gains are sensitive to it: retune when it changes.</t>
+          <t>Sets how fast an unloaded wheel spins up — the s-diff's whole problem. Controller gains are sensitive to it: retune when it changes. Together with I_wheel_front it also sets the effective mass the car must accelerate, which verify.py D1 measures against a closed-form coast-down.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Total power cap</t>
+          <t>Wheel spin inertia, front corner</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>P_max</t>
+          <t>I_w,f</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>drivetrain.power_cap_total</t>
+          <t>drivetrain.I_wheel_front</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>FSAE EV rules limit on total drive power (EV.4.2, 80 kW at the accumulator).</t>
+          <t>Spin inertia of ONE FRONT corner about the axle. Same construction as the rear — same tire, same rim, same in-upright motor and planetary, same brake rotor — so the same number, written as a formula so the ASSUMPTION is visible in the data rather than buried in code.</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>80,000</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>kg*m^2</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>RULES VALUE (simplified)</t>
+          <t>DERIVED — front corner ASSUMED identical to rear; replace when CAD says otherwise</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Nothing (rulebook)</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>Confirm in the current-year rulebook</t>
-        </is>
+          <t>Rotating inertia of one front corner (CAD)</t>
+        </is>
+      </c>
+      <c r="I26" s="3">
+        <f> drivetrain.I_wheel_rear</f>
+        <v/>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>Hard ceiling. The sim applies it to mechanical power (no drivetrain losses modeled) — the real car hits it ~10-15% earlier.</t>
+          <t>The front rotor spins whether or not that motor is energised, so this number is real for the 2-rear build too. It is the term the sim dropped when it called the fronts "massless free-rollers": worth 2*I/r_w^2 = 13.4 kg of apparent mass, 5.3% of the car, and 0.6% on a 3 s coast-down.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Driven wheels</t>
+          <t>Total power cap</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>n_drv</t>
+          <t>P_max</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>drivetrain.driven_wheels</t>
+          <t>drivetrain.power_cap_total</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>How many wheels receive drive torque. 4 = one motor per upright; 2 = the rear pair only, which is what the current build runs.</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>FSAE EV rules limit on total drive power (EV.4.2, 80 kW at the accumulator).</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>80,000</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT CAR (four motors fitted, the rear pair commissioned)</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>RULES VALUE (simplified)</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Which inverters are commissioned on the car</t>
+          <t>Nothing (rulebook)</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Powertrain: count enabled inverters</t>
+          <t>Confirm in the current-year rulebook</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>The scale between "peak torque at ONE wheel" and "peak torque the driver can ask for". Every axle-torque budget in the sim is n_drv * T_wheel_max: the maneuver throttle steps, the APPS pedal map, the driver adapter's exact inverse of it, and the plot ceilings.</t>
+          <t>Hard ceiling. The sim applies it to mechanical power (no drivetrain losses modeled) — the real car hits it ~10-15% earlier.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
+          <t>Driven wheels</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n_drv</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>drivetrain.driven_wheels</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>How many wheels receive drive torque. 4 = one motor per upright; 2 = the rear pair only, which is what the current build runs.</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (four motors fitted, the rear pair commissioned)</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Which inverters are commissioned on the car</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Powertrain: count enabled inverters</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>The scale between "peak torque at ONE wheel" and "peak torque the driver can ask for". Every axle-torque budget in the sim is n_drv * T_wheel_max: the maneuver throttle steps, the APPS pedal map, the driver adapter's exact inverse of it, and the plot ceilings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
           <t>Regen speed cutoff</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>drivetrain.regen_speed_cutoff</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Below this speed no negative (regen) torque is commanded.</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>m/s (~5 km/h)</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>RULES VALUE (approx.)</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>Nothing (rulebook)</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>Confirm in the current-year rulebook</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>Rules restrict regen near standstill; also keeps the sim's low-speed slip math out of its untrustworthy zone.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>AERO</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Lift coefficient</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>C_L</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>aero.cl_coeff</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Lift (downforce) coefficient, referenced to frontal_area.</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>3.18</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>FROM REPORT (old car's aero)</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Current car's downforce coefficient</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>CFD, then straight-line coast-down / load-cell validation</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>Downforce = 0.5*rho*C_L*A*v^2 — free grip that grows with speed^2.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Drag coefficient</t>
+          <t>Lift coefficient</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>C_D</t>
+          <t>C_L</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>aero.cd_coeff</t>
+          <t>aero.cl_coeff</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Drag coefficient, same reference area.</t>
+          <t>Lift (downforce) coefficient, referenced to frontal_area.</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -1890,368 +1889,368 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Current car's drag coefficient</t>
+          <t>Current car's downforce coefficient</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>CFD + coast-down test</t>
+          <t>CFD, then straight-line coast-down / load-cell validation</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>Sets top-speed force budget and the torque needed to hold speed in every maneuver.</t>
+          <t>Downforce = 0.5*rho*C_L*A*v^2 — free grip that grows with speed^2.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Frontal area</t>
+          <t>Drag coefficient</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>A_F</t>
+          <t>C_D</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>aero.frontal_area</t>
+          <t>aero.cd_coeff</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Aerodynamic frontal reference area.</t>
+          <t>Drag coefficient, same reference area.</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>1.106</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>m^2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>FROM REPORT</t>
+          <t>FROM REPORT (old car's aero)</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Projected frontal area</t>
+          <t>Current car's drag coefficient</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>CAD projection</t>
+          <t>CFD + coast-down test</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>Only the products C*A enter the physics — keep coefficient and area consistent.</t>
+          <t>Sets top-speed force budget and the torque needed to hold speed in every maneuver.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
+          <t>Frontal area</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>A_F</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>aero.frontal_area</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Aerodynamic frontal reference area.</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>1.106</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>m^2</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>FROM REPORT</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Projected frontal area</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>CAD projection</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>Only the products C*A enter the physics — keep coefficient and area consistent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
           <t>ClA (computed)</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>C_L*A</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>aero.ClA</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>The downforce product the sim actually uses.</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>3.517</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>m^2</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="3">
+      <c r="I34" s="3">
         <f> aero.cl_coeff * aero.frontal_area</f>
         <v/>
       </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>CdA (computed)</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>C_D*A</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>aero.CdA</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>The drag product the sim actually uses.</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>1.504</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>m^2</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="3">
+      <c r="I35" s="3">
         <f> aero.cd_coeff * aero.frontal_area</f>
         <v/>
       </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>Aero balance</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>pct_aero_f</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>aero.balance_front</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Fraction of total downforce landing on the FRONT axle (0.45 = 45/55).</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER — pure guess</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>Center-of-pressure position</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="I36" s="3" t="inlineStr">
         <is>
           <t>CFD (aero team) — ask for CP height too</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>Moves grip between axles as speed rises — shapes high-speed balance directly. One of the last pure guesses outside tires.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>STEERING GEOMETRY</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Ackermann fraction</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>pct_A</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>steering.ackermann_fraction</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>How much of the geometric (100%) Ackermann inner/outer steer split the steering actually delivers. 0.0 = parallel steer (both fronts get the same angle), 1.0 = full geometric Ackermann, negative = anti-Ackermann.</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="G38" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER (parallel) — RWheel curve needed</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>The steering curve: both wheels' angles vs handwheel angle</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr">
+      <c r="I38" s="3" t="inlineStr">
         <is>
           <t>From the steering chart: the LWheel curve is on file, need the RWheel polynomial from the same chart (or a few x, LWheel, RWheel point triples).</t>
         </is>
       </c>
-      <c r="J37" s="3" t="inlineStr">
+      <c r="J38" s="3" t="inlineStr">
         <is>
           <t>Only matters at large steer angles: at 5 deg the split is ~+/-0.2 deg; at the 23 deg full-lock hairpin it is ~+/-4 deg per wheel. Proven to flip whether s-diff-only survives the hairpin (runs 007 vs 008).</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>LOAD TRANSFER</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Front spring rate</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>ks_f</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>loads.spring_rate_front</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>Front suspension spring rate. Used ONLY through its ratio to the rear.</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>19.3</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>N/mm (ratio only)</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>FROM REPORT</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>Front roll stiffness incl. ARBs and motion ratios</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>Suspension team</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>Numerator of the lateral load-transfer split.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Rear spring rate</t>
+          <t>Front spring rate</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>ks_r</t>
+          <t>ks_f</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>loads.spring_rate_rear</t>
+          <t>loads.spring_rate_front</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Rear suspension spring rate. Used ONLY through its ratio to the front.</t>
+          <t>Front suspension spring rate. Used ONLY through its ratio to the rear.</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -2266,7 +2265,7 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Rear roll stiffness incl. ARBs and motion ratios</t>
+          <t>Front roll stiffness incl. ARBs and motion ratios</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -2276,144 +2275,144 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>Denominator half of the lateral load-transfer split.</t>
+          <t>Numerator of the lateral load-transfer split.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
+          <t>Rear spring rate</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>ks_r</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>loads.spring_rate_rear</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Rear suspension spring rate. Used ONLY through its ratio to the front.</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>24.8</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>N/mm (ratio only)</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>FROM REPORT</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Rear roll stiffness incl. ARBs and motion ratios</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>Suspension team</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>Denominator half of the lateral load-transfer split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
           <t>Front lateral-transfer fraction</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>loads.lat_transfer_frac_front</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>Share of total LATERAL load transfer reacted by the FRONT axle, set by the front/rear roll-stiffness split.</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>0.4376</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>FROM REPORT (spring-rate ratio only) — crude</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>Front vs rear roll stiffness</t>
         </is>
       </c>
-      <c r="I41" s="3">
+      <c r="I42" s="3">
         <f> loads.spring_rate_front / (loads.spring_rate_front + loads.spring_rate_rear)</f>
         <v/>
       </c>
-      <c r="J41" s="3" t="inlineStr">
+      <c r="J42" s="3" t="inlineStr">
         <is>
           <t>Which axle eats the load transfer = which axle loses grip first — trades understeer/oversteer at the limit.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>TIRES — TTC ROUND 9 FIT (R20 compound, 2026-08-31); surrogate sizes, road µ = belt × 0.67 pending skidpad</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Belt→road grip scale</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>tires.mu_road_scale</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Belt-&gt;asphalt grip scaling. Calspan's sandpaper belt grips harder than track asphalt; common practice scales the fitted peak mu by ~0.65-0.70 for on-road prediction (stiffnesses/shapes carry over unscaled).</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>0.67</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G43" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER — skidpad measures this</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>Steady-state skidpad lateral g</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>Skidpad test vs sim prediction</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>Multiplies EVERY grip number — the single biggest absolute-accuracy lever left. VALIDATE on skidpad; that measurement replaces this guess with truth.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Belt peak µ, lateral</t>
+          <t>Belt→road grip scale</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>mu_belt_y</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>tires.belt_mu_lat</t>
+          <t>tires.mu_road_scale</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Peak LATERAL friction coefficient as fitted on the Calspan belt.</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>2.593</t>
+          <t>Belt-&gt;asphalt grip scaling. Calspan's sandpaper belt grips harder than track asphalt; common practice scales the fitted peak mu by ~0.65-0.70 for on-road prediction (stiffnesses/shapes carry over unscaled).</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>0.67</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -2421,51 +2420,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G44" s="6" t="inlineStr">
-        <is>
-          <t>TTC FIT R9</t>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — skidpad measures this</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Steady-state skidpad lateral g</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>tire_fit.py on Round 9 cornering runs (surrogate spread +/-6%)</t>
+          <t>Skidpad test vs sim prediction</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>Scaled by mu_road_scale to give the road value the sim uses.</t>
+          <t>Multiplies EVERY grip number — the single biggest absolute-accuracy lever left. VALIDATE on skidpad; that measurement replaces this guess with truth.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Belt peak µ, longitudinal</t>
+          <t>Belt peak µ, lateral</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>mu_belt_x</t>
+          <t>mu_belt_y</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>tires.belt_mu_long</t>
+          <t>tires.belt_mu_lat</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Peak LONGITUDINAL friction coefficient as fitted on the belt.</t>
+          <t>Peak LATERAL friction coefficient as fitted on the Calspan belt.</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>2.359</t>
+          <t>2.593</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -2485,7 +2484,7 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>tire_fit.py on Round 9 drive/brake runs</t>
+          <t>tire_fit.py on Round 9 cornering runs (surrogate spread +/-6%)</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -2497,279 +2496,279 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
+          <t>Belt peak µ, longitudinal</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>mu_belt_x</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>tires.belt_mu_long</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Peak LONGITUDINAL friction coefficient as fitted on the belt.</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>2.359</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>TTC FIT R9</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>tire_fit.py on Round 9 drive/brake runs</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>Scaled by mu_road_scale to give the road value the sim uses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
           <t>Peak friction coefficient</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>mu0</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>tires.mu0</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>Peak grip per newton of load, at the nominal load (road value).</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>1.737</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G46" s="6" t="inlineStr">
+      <c r="G47" s="6" t="inlineStr">
         <is>
           <t>TTC FIT R9</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr">
         <is>
           <t>Peak mu at several loads</t>
         </is>
       </c>
-      <c r="I46" s="3">
+      <c r="I47" s="3">
         <f> tires.mu_road_scale * tires.belt_mu_lat</f>
         <v/>
       </c>
-      <c r="J46" s="3" t="inlineStr">
+      <c r="J47" s="3" t="inlineStr">
         <is>
           <t>THE grip number. Max lateral g, spin thresholds, everything — the single most important number in the sim.</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>Peak longitudinal friction</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>mu0x</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>tires.mu0_long</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>Drive/brake grip peak — fitted 9% below lateral; combined slip caps on the friction ELLIPSE in tire.py.</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>1.581</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G47" s="6" t="inlineStr">
+      <c r="G48" s="6" t="inlineStr">
         <is>
           <t>TTC FIT R9</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="3">
+      <c r="I48" s="3">
         <f> tires.mu_road_scale * tires.belt_mu_long</f>
         <v/>
       </c>
-      <c r="J47" s="3" t="inlineStr">
+      <c r="J48" s="3" t="inlineStr">
         <is>
           <t>Sets wheelspin threshold and traction capability.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Load sensitivity</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>s_mu</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>tires.s_mu</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>Load sensitivity — how much the friction COEFFICIENT drops as vertical load rises: mu = mu0 * (1 - s_mu*(Fz/Fz_nom - 1)). Shared by the lateral and longitudinal peaks.</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>0.112</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>—/100% load</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="inlineStr">
-        <is>
-          <t>TTC FIT R9</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>mu at low vs high load</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>Same TTC fit</t>
-        </is>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>The reason load transfer costs grip and torque placement matters at all. Zero would make TV pointless.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
+          <t>Load sensitivity</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>s_mu</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>tires.s_mu</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Load sensitivity — how much the friction COEFFICIENT drops as vertical load rises: mu = mu0 * (1 - s_mu*(Fz/Fz_nom - 1)). Shared by the lateral and longitudinal peaks.</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>0.112</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>—/100% load</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>TTC FIT R9</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>mu at low vs high load</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>Same TTC fit</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>The reason load transfer costs grip and torque placement matters at all. Zero would make TV pointless.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
           <t>Nominal tire load</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>Fz_nom</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>tires.Fz_nom</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>The "nominal" vertical load at which mu0 is defined (~one static corner weight).</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>618.6</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="F50" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="G50" s="3" t="inlineStr">
         <is>
           <t>DERIVED (follows the masses automatically)</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
+      <c r="H50" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="3">
+      <c r="I50" s="3">
         <f> (mass.car_no_driver + mass.driver) * environment.g / 4.0</f>
         <v/>
       </c>
-      <c r="J49" s="3" t="inlineStr">
+      <c r="J50" s="3" t="inlineStr">
         <is>
           <t>Reference point for the load-sensitivity line.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>Front cornering stiffness</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>c_alpha_f</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>tires.c_alpha_front</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>Normalized cornering stiffness of a FRONT tire: lateral force per radian of slip angle, per newton of load (C_alpha = this * Fz).</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>1/rad</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>TTC FIT R9 (same tire all round)</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>Slope of Fy vs slip angle at small angles</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t>TTC cornering sweep</t>
-        </is>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>Front-axle responsiveness; with rear stiffness sets the understeer gradient K_us the TV reference uses.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Rear cornering stiffness</t>
+          <t>Front cornering stiffness</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>c_alpha_r</t>
+          <t>c_alpha_f</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>tires.c_alpha_rear</t>
+          <t>tires.c_alpha_front</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Same, for a REAR tire.</t>
+          <t>Normalized cornering stiffness of a FRONT tire: lateral force per radian of slip angle, per newton of load (C_alpha = this * Fz).</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -2789,7 +2788,7 @@
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>Same, rear</t>
+          <t>Slope of Fy vs slip angle at small angles</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
@@ -2799,91 +2798,91 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>Rear grip slope — stability side of the understeer gradient.</t>
+          <t>Front-axle responsiveness; with rear stiffness sets the understeer gradient K_us the TV reference uses.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Longitudinal slip stiffness</t>
+          <t>Rear cornering stiffness</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>c_kappa</t>
+          <t>c_alpha_r</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>tires.c_kappa</t>
+          <t>tires.c_alpha_rear</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Normalized longitudinal slip stiffness: drive/brake force per unit slip ratio per newton (C_kappa = this * Fz).</t>
+          <t>Same, for a REAR tire.</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>1/slip</t>
+          <t>1/rad</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>TTC FIT R9</t>
+          <t>TTC FIT R9 (same tire all round)</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Slope of Fx vs slip ratio</t>
+          <t>Same, rear</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>TTC drive/brake sweep</t>
+          <t>TTC cornering sweep</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>Sets wheel-spin dynamics speed — the s-diff's plant. Gains retune if it moves.</t>
+          <t>Rear grip slope — stability side of the understeer gradient.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Lateral shape factor</t>
+          <t>Longitudinal slip stiffness</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>C_y</t>
+          <t>c_kappa</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>tires.shape_c_lat</t>
+          <t>tires.c_kappa</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Magic Formula shape factor — how sharply lateral force peaks.</t>
+          <t>Normalized longitudinal slip stiffness: drive/brake force per unit slip ratio per newton (C_kappa = this * Fz).</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>1.397</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1/slip</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
@@ -2893,44 +2892,44 @@
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>Curve shape near/past the peak</t>
+          <t>Slope of Fx vs slip ratio</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>TTC fit</t>
+          <t>TTC drive/brake sweep</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>With E_y, sets where the curve peaks (currently 11.6 deg — real slicks ~6-10 deg) and how it lets go.</t>
+          <t>Sets wheel-spin dynamics speed — the s-diff's plant. Gains retune if it moves.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Lateral curvature factor</t>
+          <t>Lateral shape factor</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>E_y</t>
+          <t>C_y</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>tires.curv_e_lat</t>
+          <t>tires.shape_c_lat</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Magic Formula curvature factor — fall-off past the lateral peak.</t>
+          <t>Magic Formula shape factor — how sharply lateral force peaks.</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>1.397</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -2945,7 +2944,7 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Post-peak behavior</t>
+          <t>Curve shape near/past the peak</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
@@ -2955,34 +2954,34 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>Gentle vs snappy breakaway — currently more forgiving than a real slick.</t>
+          <t>With E_y, sets where the curve peaks (currently 11.6 deg — real slicks ~6-10 deg) and how it lets go.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Longitudinal shape factor</t>
+          <t>Lateral curvature factor</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>C_x</t>
+          <t>E_y</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>tires.shape_c_long</t>
+          <t>tires.curv_e_lat</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Same idea, drive/brake direction.</t>
+          <t>Magic Formula curvature factor — fall-off past the lateral peak.</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>1.705</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -2997,7 +2996,7 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>Curve shape</t>
+          <t>Post-peak behavior</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -3007,125 +3006,125 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>Sets the peak slip ratio (~0.10) — also the replay's red-wheel spin threshold.</t>
+          <t>Gentle vs snappy breakaway — currently more forgiving than a real slick.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
+          <t>Longitudinal shape factor</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>C_x</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>tires.shape_c_long</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Same idea, drive/brake direction.</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>1.705</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>TTC FIT R9</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Curve shape</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>TTC fit</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>Sets the peak slip ratio (~0.10) — also the replay's red-wheel spin threshold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
           <t>Longitudinal curvature factor</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>E_x</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>tires.curv_e_long</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>Fall-off past the longitudinal peak.</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
         <is>
           <t>0.389</t>
         </is>
       </c>
-      <c r="F56" s="3" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G56" s="6" t="inlineStr">
+      <c r="G57" s="6" t="inlineStr">
         <is>
           <t>TTC FIT R9</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr">
         <is>
           <t>Post-peak behavior</t>
         </is>
       </c>
-      <c r="I56" s="3" t="inlineStr">
+      <c r="I57" s="3" t="inlineStr">
         <is>
           <t>TTC fit</t>
         </is>
       </c>
-      <c r="J56" s="3" t="inlineStr">
+      <c r="J57" s="3" t="inlineStr">
         <is>
           <t>How violently a spinning wheel loses force — feeds the wheelspin runaway.</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>SENSORS &amp; VCU — the VCU itself</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>VCU loop rate</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>sensors.vcu.rate_hz</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>VCU control-loop rate — how often sensors are sampled and torque commands are recomputed (physics still integrates at 4 kHz).</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="F58" s="3" t="inlineStr">
-        <is>
-          <t>Hz</t>
-        </is>
-      </c>
-      <c r="G58" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER — ask software team</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>The real VCU loop rate</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t>Software team</t>
-        </is>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>Gains proven stable at 100 Hz (verify.py section H); make it match reality before quoting controller performance.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>Plausibility cut threshold</t>
+          <t>VCU loop rate</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -3135,49 +3134,49 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>sensors.vcu.plaus_apps_cut</t>
+          <t>sensors.vcu.rate_hz</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>APPS percentage above which, while braking, motor power must be cut.</t>
+          <t>VCU control-loop rate — how often sensors are sampled and torque commands are recomputed (physics still integrates at 4 kHz).</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>RULES VALUE (EV.4.7)</t>
+          <t>Hz</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — ask software team</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>The real VCU loop rate</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>Rulebook (confirm current year)</t>
+          <t>Software team</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>Implemented and unit-tested (verify I3); the pedal_check maneuver demonstrates it.</t>
+          <t>Gains proven stable at 100 Hz (verify.py section H); make it match reality before quoting controller performance.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Plausibility restore threshold</t>
+          <t>Plausibility cut threshold</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -3187,17 +3186,17 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>sensors.vcu.plaus_apps_restore</t>
+          <t>sensors.vcu.plaus_apps_cut</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>APPS percentage the pedal must fall below before power is restored.</t>
+          <t>APPS percentage above which, while braking, motor power must be cut.</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -3222,184 +3221,184 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>The latch that makes the cut a latch and not a flicker.</t>
+          <t>Implemented and unit-tested (verify I3); the pedal_check maneuver demonstrates it.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
+          <t>Plausibility restore threshold</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>sensors.vcu.plaus_apps_restore</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>APPS percentage the pedal must fall below before power is restored.</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>RULES VALUE (EV.4.7)</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>Rulebook (confirm current year)</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>The latch that makes the cut a latch and not a flicker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
           <t>Sensor noise seed</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>sensors.vcu.seed</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>Seed for the sensor-noise generator — runs are exactly repeatable and all four controller configs see IDENTICAL noise.</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F61" s="3" t="inlineStr">
+      <c r="F62" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G61" s="3" t="inlineStr">
+      <c r="G62" s="3" t="inlineStr">
         <is>
           <t>NUMERICAL GUARD (repeatability)</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr">
+      <c r="H62" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="3" t="inlineStr">
+      <c r="I62" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J61" s="3" t="inlineStr">
+      <c r="J62" s="3" t="inlineStr">
         <is>
           <t>Fair comparisons and reproducible runs.</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>SENSORS — APPS, accelerator pedal position</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>APPS quantization</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>sensors.throttle_pos.quant_pct</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>Accelerator pedal position resolution.</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="F63" s="3" t="inlineStr">
+      <c r="F64" s="3" t="inlineStr">
         <is>
           <t>%/LSB</t>
         </is>
       </c>
-      <c r="G63" s="7" t="inlineStr">
+      <c r="G64" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER — sensor spec</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
+      <c r="H64" s="3" t="inlineStr">
         <is>
           <t>APPS sensor spec</t>
         </is>
       </c>
-      <c r="I63" s="3" t="inlineStr">
+      <c r="I64" s="3" t="inlineStr">
         <is>
           <t>Datasheet</t>
         </is>
       </c>
-      <c r="J63" s="3" t="inlineStr">
+      <c r="J64" s="3" t="inlineStr">
         <is>
           <t>Torque request granularity.</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>SENSORS — BPS, brake pressure</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>BPS full range</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>sensors.brake_pressure_sens.range_bar</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>Brake pressure sensor full range.</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="G65" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER — sensor spec</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>BPS spec + brake system pressures</t>
-        </is>
-      </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t>Brake team: line pressure at threshold/full braking</t>
-        </is>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>Sets the pressure that maps to full regen.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>BPS quantization</t>
+          <t>BPS full range</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -3409,22 +3408,22 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>sensors.brake_pressure_sens.quant_bar</t>
+          <t>sensors.brake_pressure_sens.range_bar</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Brake pressure sensor resolution.</t>
+          <t>Brake pressure sensor full range.</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>bar/LSB</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
@@ -3434,24 +3433,24 @@
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>BPS spec</t>
+          <t>BPS spec + brake system pressures</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>Datasheet</t>
+          <t>Brake team: line pressure at threshold/full braking</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>Regen command granularity.</t>
+          <t>Sets the pressure that maps to full regen.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>BPS actuated threshold</t>
+          <t>BPS quantization</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -3461,244 +3460,244 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>sensors.brake_pressure_sens.actuated_bar</t>
+          <t>sensors.brake_pressure_sens.quant_bar</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Pressure above which the brake counts as "actuated" for the rules check.</t>
+          <t>Brake pressure sensor resolution.</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>bar</t>
+          <t>bar/LSB</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — calibration choice</t>
+          <t>PLACEHOLDER — sensor spec</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>Brake system pressures</t>
+          <t>BPS spec</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>Brake team: line pressure at threshold braking</t>
+          <t>Datasheet</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>Defines "braking" for the EV.4.7 plausibility check.</t>
+          <t>Regen command granularity.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
+          <t>BPS actuated threshold</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>sensors.brake_pressure_sens.actuated_bar</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Pressure above which the brake counts as "actuated" for the rules check.</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — calibration choice</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Brake system pressures</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>Brake team: line pressure at threshold braking</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>Defines "braking" for the EV.4.7 plausibility check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
           <t>Max regen torque</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>sensors.brake_pressure_sens.t_regen_max</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>Total rear-axle REGEN torque at full brake pressure (both motors).</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="E69" s="4" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="F68" s="3" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>N*m</t>
         </is>
       </c>
-      <c r="G68" s="7" t="inlineStr">
+      <c r="G69" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER — battery charge limit sets this</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
+      <c r="H69" s="3" t="inlineStr">
         <is>
           <t>Allowed charge current -&gt; torque</t>
         </is>
       </c>
-      <c r="I68" s="3" t="inlineStr">
+      <c r="I69" s="3" t="inlineStr">
         <is>
           <t>Accumulator team: max charge C-rate</t>
         </is>
       </c>
-      <c r="J68" s="3" t="inlineStr">
+      <c r="J69" s="3" t="inlineStr">
         <is>
           <t>Caps how much "braking" the sim's BPS can command.</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>SENSORS — WSS, motor resolver over CAN</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>WSS quantization</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>sensors.wheel_speed.quant_rpm</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>Motor-speed resolution over CAN (motor side, before the planetary divide).</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="E71" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F70" s="3" t="inlineStr">
+      <c r="F71" s="3" t="inlineStr">
         <is>
           <t>rpm/LSB</t>
         </is>
       </c>
-      <c r="G70" s="7" t="inlineStr">
+      <c r="G71" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER — AMK CAN resolution</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
+      <c r="H71" s="3" t="inlineStr">
         <is>
           <t>AMK CAN speed resolution</t>
         </is>
       </c>
-      <c r="I70" s="3" t="inlineStr">
+      <c r="I71" s="3" t="inlineStr">
         <is>
           <t>AMK CAN spec</t>
         </is>
       </c>
-      <c r="J70" s="3" t="inlineStr">
+      <c r="J71" s="3" t="inlineStr">
         <is>
           <t>1 motor rpm is about 1.8 mm/s of ground speed — the resolver-over-CAN path is effectively noise-free wheel speed.</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>SENSORS — SAS, steering angle, and the steering map</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>Steering map A0 (intercept)</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>A0</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>sensors.steering_angle.map_a0</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>Constant term of the handwheel -&gt; road-wheel polynomial.</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>-0.0797</t>
-        </is>
-      </c>
-      <c r="F72" s="3" t="inlineStr">
-        <is>
-          <t>deg (intercept)</t>
-        </is>
-      </c>
-      <c r="G72" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT CAR (team chart)</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>The steering curve including RWheel</t>
-        </is>
-      </c>
-      <c r="I72" s="3" t="inlineStr">
-        <is>
-          <t>Steering chart / kinematics sweep</t>
-        </is>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>Subtracted out to center the map; kept so the raw fit stays visible.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>Steering map A1 (linear)</t>
+          <t>Steering map A0 (intercept)</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A0</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>sensors.steering_angle.map_a1</t>
+          <t>sensors.steering_angle.map_a0</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Linear term — the near-center steering ratio.</t>
+          <t>Constant term of the handwheel -&gt; road-wheel polynomial.</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.0797</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>deg/deg</t>
+          <t>deg (intercept)</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
@@ -3718,44 +3717,44 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>How the VCU turns the SAS reading into a road-wheel angle.</t>
+          <t>Subtracted out to center the map; kept so the raw fit stays visible.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>Steering map A2 (quadratic)</t>
+          <t>Steering map A1 (linear)</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>sensors.steering_angle.map_a2</t>
+          <t>sensors.steering_angle.map_a1</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Quadratic term — the ratio falling off toward lock.</t>
+          <t>Linear term — the near-center steering ratio.</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>-0.000844</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>deg/deg^2</t>
+          <t>deg/deg</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>CURRENT CAR (team chart; -844E-04 read as -8.44E-04)</t>
+          <t>CURRENT CAR (team chart)</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
@@ -3770,155 +3769,155 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>Full lock 23 deg is about 103 deg of handwheel.</t>
+          <t>How the VCU turns the SAS reading into a road-wheel angle.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
+          <t>Steering map A2 (quadratic)</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>sensors.steering_angle.map_a2</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Quadratic term — the ratio falling off toward lock.</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>-0.000844</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>deg/deg^2</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (team chart; -844E-04 read as -8.44E-04)</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>The steering curve including RWheel</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>Steering chart / kinematics sweep</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>Full lock 23 deg is about 103 deg of handwheel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
           <t>SAS quantization</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>sensors.steering_angle.quant_deg</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>Steering-angle sensor resolution, at the handwheel.</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
+      <c r="E76" s="4" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr">
+      <c r="F76" s="3" t="inlineStr">
         <is>
           <t>deg/LSB</t>
         </is>
       </c>
-      <c r="G75" s="7" t="inlineStr">
+      <c r="G76" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER — sensor spec</t>
         </is>
       </c>
-      <c r="H75" s="3" t="inlineStr">
+      <c r="H76" s="3" t="inlineStr">
         <is>
           <t>Sensor spec</t>
         </is>
       </c>
-      <c r="I75" s="3" t="inlineStr">
+      <c r="I76" s="3" t="inlineStr">
         <is>
           <t>Datasheet of the chosen SAS</t>
         </is>
       </c>
-      <c r="J75" s="3" t="inlineStr">
+      <c r="J76" s="3" t="inlineStr">
         <is>
           <t>Steering resolution the VCU actually sees.</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>SENSORS — IMU, yaw gyro and accelerometers</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>IMU gyro noise (1σ)</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>sigma_g</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>sensors.imu_6axis.gyro_noise_std</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>Yaw-gyro 1-sigma noise.</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>0.005236</t>
-        </is>
-      </c>
-      <c r="F77" s="3" t="inlineStr">
-        <is>
-          <t>rad/s (entered as deg/s, 1 sigma)</t>
-        </is>
-      </c>
-      <c r="G77" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER — IMU spec</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>IMU datasheet numbers</t>
-        </is>
-      </c>
-      <c r="I77" s="3" t="inlineStr">
-        <is>
-          <t>Chosen IMU's spec sheet</t>
-        </is>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>Goes straight into the TV feedback — sets how clean the yaw control can be.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>IMU gyro bias</t>
+          <t>IMU gyro noise (1σ)</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>b_g</t>
+          <t>sigma_g</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>sensors.imu_6axis.gyro_bias</t>
+          <t>sensors.imu_6axis.gyro_noise_std</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Constant yaw-gyro zero offset.</t>
+          <t>Yaw-gyro 1-sigma noise.</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>0.001745</t>
+          <t>0.005236</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>rad/s (entered as deg/s)</t>
+          <t>rad/s (entered as deg/s, 1 sigma)</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — uncalibrated bias</t>
+          <t>PLACEHOLDER — IMU spec</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
@@ -3928,269 +3927,269 @@
       </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>Chosen IMU's spec sheet, then a stationary calibration on the car</t>
+          <t>Chosen IMU's spec sheet</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>Biases the yaw-rate error the TV controller integrates.</t>
+          <t>Goes straight into the TV feedback — sets how clean the yaw control can be.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>VCU gyro low-pass</t>
+          <t>IMU gyro bias</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>f_c</t>
+          <t>b_g</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>sensors.imu_6axis.lpf_hz</t>
+          <t>sensors.imu_6axis.gyro_bias</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>First-order low-pass the VCU applies to the gyro before feedback.</t>
+          <t>Constant yaw-gyro zero offset.</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0.001745</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>Hz</t>
+          <t>rad/s (entered as deg/s)</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — VCU filter choice</t>
+          <t>PLACEHOLDER — uncalibrated bias</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>IMU datasheet numbers</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>Software choice; tune against noise</t>
+          <t>Chosen IMU's spec sheet, then a stationary calibration on the car</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>Trade: more filtering = less dither but more phase lag in the yaw loop.</t>
+          <t>Biases the yaw-rate error the TV controller integrates.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
+          <t>VCU gyro low-pass</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>f_c</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>sensors.imu_6axis.lpf_hz</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>First-order low-pass the VCU applies to the gyro before feedback.</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>Hz</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — VCU filter choice</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>Software choice; tune against noise</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>Trade: more filtering = less dither but more phase lag in the yaw loop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
           <t>IMU accel noise</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>sigma_a</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>sensors.imu_6axis.accel_noise_std</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>Accelerometer 1-sigma noise (ax, ay channels).</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
+      <c r="E81" s="4" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="F80" s="3" t="inlineStr">
+      <c r="F81" s="3" t="inlineStr">
         <is>
           <t>m/s^2</t>
         </is>
       </c>
-      <c r="G80" s="7" t="inlineStr">
+      <c r="G81" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER — IMU spec</t>
         </is>
       </c>
-      <c r="H80" s="3" t="inlineStr">
+      <c r="H81" s="3" t="inlineStr">
         <is>
           <t>IMU datasheet</t>
         </is>
       </c>
-      <c r="I80" s="3" t="inlineStr">
+      <c r="I81" s="3" t="inlineStr">
         <is>
           <t>Spec sheet</t>
         </is>
       </c>
-      <c r="J80" s="3" t="inlineStr">
+      <c r="J81" s="3" t="inlineStr">
         <is>
           <t>Feeds future estimation (vx observer, validation logging).</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>CONTROLLER CONSTANTS — open-loop s-diff, mirrored from sdiff.c</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>Steering ratio (handwheel : road-wheel)</t>
-        </is>
-      </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>STEERING_RATIO</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t>controllers.steering_ratio</t>
-        </is>
-      </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t>Divides handwheel angle down to road-wheel angle in sdiff.c.</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>5.4</t>
-        </is>
-      </c>
-      <c r="F82" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT CAR (sdiff.c STEERING_RATIO)</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I82" s="3" t="inlineStr">
-        <is>
-          <t>Team steering chart (sensors/steering_angle/params.yaml, A1 term)</t>
-        </is>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>Mirrors the C constant. NOT used by the Python controller — the sim gets its road-wheel angle from the SAS polynomial map in model/sensors/steering_angle/sas.py, which implies ~3.2:1 near center and ~7.5:1 at lock. The flat 5.4 here and that map disagree; the map is the more accurate model of the real linkage.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>Steer angle at full derate</t>
+          <t>Steering ratio (handwheel : road-wheel)</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>DELTA_MAX</t>
+          <t>STEERING_RATIO</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>controllers.delta_max</t>
+          <t>controllers.steering_ratio</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Normalizes steer angle to 0-1 in sdiff.c (delta_norm), clamped at 1.</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>0.03491</t>
+          <t>Divides handwheel angle down to road-wheel angle in sdiff.c.</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>5.4</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="G83" s="7" t="inlineStr">
-        <is>
-          <t>SUSPECT — mirrors sdiff.c DELTA_MAX, but see note</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (sdiff.c STEERING_RATIO)</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>Confirmation from the VCU team that 2 deg is intended (see note)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>dev/sdiff.c on the S-diff branch</t>
+          <t>Team steering chart (sensors/steering_angle/params.yaml, A1 term)</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>NOT full lock — this is the angle at which the derate SATURATES. At 2 deg of road wheel (about 10.8 deg of handwheel at 5.4:1) delta_norm hits 1.0 and the inner-wheel cut is already at its maximum, so the s-diff behaves close to on/off rather than progressive.</t>
+          <t>Mirrors the C constant. NOT used by the Python controller — the sim gets its road-wheel angle from the SAS polynomial map in model/sensors/steering_angle/sas.py, which implies ~3.2:1 near center and ~7.5:1 at lock. The flat 5.4 here and that map disagree; the map is the more accurate model of the real linkage.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>Friction-budget derate gain</t>
+          <t>Steer angle at full derate</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>K_DERATE</t>
+          <t>DELTA_MAX</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>controllers.k_derate</t>
+          <t>controllers.delta_max</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>How much total torque (both wheels) falls off as steer angle rises.</t>
-        </is>
-      </c>
-      <c r="E84" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>Normalizes steer angle to 0-1 in sdiff.c (delta_norm), clamped at 1.</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>0.03491</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT CAR (sdiff.c K_DERATE)</t>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>SUSPECT — mirrors sdiff.c DELTA_MAX, but see note</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Confirmation from the VCU team that 2 deg is intended (see note)</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
@@ -4200,34 +4199,34 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>Deliberately zeroed in commit 18f9bc7 before the first on-car run: the shared budget cut is OFF, so f = 1.0 always and f_min below is inert. The s-diff currently biases left/right without taking any total power away.</t>
+          <t>NOT full lock — this is the angle at which the derate SATURATES. At 2 deg of road wheel (about 10.8 deg of handwheel at 5.4:1) delta_norm hits 1.0 and the inner-wheel cut is already at its maximum, so the s-diff behaves close to on/off rather than progressive.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>Inner-wheel derate gain</t>
+          <t>Friction-budget derate gain</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>K_INNER</t>
+          <t>K_DERATE</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>controllers.k_inner</t>
+          <t>controllers.k_derate</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>Torque cut applied to the inner (unloaded) wheel, scaled by delta_norm.</t>
+          <t>How much total torque (both wheels) falls off as steer angle rises.</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -4237,7 +4236,7 @@
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>CURRENT CAR (sdiff.c K_INNER, tuned on car)</t>
+          <t>CURRENT CAR (sdiff.c K_DERATE)</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
@@ -4247,39 +4246,39 @@
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>Tuned on car across the PNR sessions</t>
+          <t>dev/sdiff.c on the S-diff branch</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>The whole point of the s-diff: keep the inner wheel from spinning up. At full delta_norm the inner wheel gets 58% of the base torque. This is the ONE constant with real on-car provenance — 0.35 (run #1) -&gt; 0.45 (run #2, 3bd6d88) -&gt; 0.42 (run #3, 5df1baf).</t>
+          <t>Deliberately zeroed in commit 18f9bc7 before the first on-car run: the shared budget cut is OFF, so f = 1.0 always and f_min below is inert. The s-diff currently biases left/right without taking any total power away.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>Friction-budget floor</t>
+          <t>Inner-wheel derate gain</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>F_MIN</t>
+          <t>K_INNER</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>controllers.f_min</t>
+          <t>controllers.k_inner</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Lowest the shared (both-wheel) torque multiplier can fall to.</t>
+          <t>Torque cut applied to the inner (unloaded) wheel, scaled by delta_norm.</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
@@ -4289,7 +4288,7 @@
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>CURRENT CAR (sdiff.c F_MIN)</t>
+          <t>CURRENT CAR (sdiff.c K_INNER, tuned on car)</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
@@ -4299,49 +4298,49 @@
       </c>
       <c r="I86" s="3" t="inlineStr">
         <is>
-          <t>dev/sdiff.c on the S-diff branch</t>
+          <t>Tuned on car across the PNR sessions</t>
         </is>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>Floors the k_derate budget cut. INERT while k_derate = 0 — f never leaves 1.0, so this clamp is never reached. It matters again the moment anyone turns the shared derate back on.</t>
+          <t>The whole point of the s-diff: keep the inner wheel from spinning up. At full delta_norm the inner wheel gets 58% of the base torque. This is the ONE constant with real on-car provenance — 0.35 (run #1) -&gt; 0.45 (run #2, 3bd6d88) -&gt; 0.42 (run #3, 5df1baf).</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>Steering deadband</t>
+          <t>Friction-budget floor</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>DEADBAND</t>
+          <t>F_MIN</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>controllers.deadband</t>
+          <t>controllers.f_min</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Road-wheel angle band around center treated as "straight" (no split).</t>
+          <t>Lowest the shared (both-wheel) torque multiplier can fall to.</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>0.01745</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>CURRENT CAR (sdiff.c DEADBAND)</t>
+          <t>CURRENT CAR (sdiff.c F_MIN)</t>
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr">
@@ -4356,187 +4355,291 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>Stops the inner/outer split from chattering when the driver is nominally straight. 1 deg of road wheel is about 5.4 deg of handwheel, comfortably above the SAS quantization (0.5 deg at the handwheel).</t>
+          <t>Floors the k_derate budget cut. INERT while k_derate = 0 — f never leaves 1.0, so this clamp is never reached. It matters again the moment anyone turns the shared derate back on.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
+          <t>Steering deadband</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>DEADBAND</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>controllers.deadband</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>Road-wheel angle band around center treated as "straight" (no split).</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>0.01745</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (sdiff.c DEADBAND)</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>dev/sdiff.c on the S-diff branch</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>Stops the inner/outer split from chattering when the driver is nominally straight. 1 deg of road wheel is about 5.4 deg of handwheel, comfortably above the SAS quantization (0.5 deg at the handwheel).</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
           <t>Slew rate</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>RATE</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>controllers.rate</t>
         </is>
       </c>
-      <c r="D88" s="3" t="inlineStr">
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>Max speed the friction-budget and left/right multipliers may change, per second.</t>
         </is>
       </c>
-      <c r="E88" s="5" t="inlineStr">
+      <c r="E89" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F88" s="3" t="inlineStr">
+      <c r="F89" s="3" t="inlineStr">
         <is>
           <t>Hz</t>
         </is>
       </c>
-      <c r="G88" s="6" t="inlineStr">
+      <c r="G89" s="6" t="inlineStr">
         <is>
           <t>CURRENT CAR (sdiff.c RATE)</t>
         </is>
       </c>
-      <c r="H88" s="3" t="inlineStr">
+      <c r="H89" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I88" s="3" t="inlineStr">
+      <c r="I89" s="3" t="inlineStr">
         <is>
           <t>dev/sdiff.c on the S-diff branch</t>
         </is>
       </c>
-      <c r="J88" s="3" t="inlineStr">
+      <c r="J89" s="3" t="inlineStr">
         <is>
           <t>Without slew limiting, torque would jump discontinuously at the deadband edges. At 1.0/s the full 0.42 inner cut takes 0.42 s to apply — far slower than any sensor or loop latency in the stack, which is why loop delay is not modeled here.</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>SOFTWARE-IN-THE-LOOP (sil/)</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>SIL firmware boot time</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>sil.boot_s</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>How long the real firmware is left to boot — bench check (55 ms) plus the ADC settle loop (1 s) — before a maneuver's t = 0, measured on the firmware's own clock.</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
+      <c r="E91" s="4" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="F90" s="3" t="inlineStr">
+      <c r="F91" s="3" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="G90" s="7" t="inlineStr">
+      <c r="G91" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER — from main.c / initializations.c</t>
         </is>
       </c>
-      <c r="H90" s="3" t="inlineStr">
+      <c r="H91" s="3" t="inlineStr">
         <is>
           <t>The firmware's true settle time</t>
         </is>
       </c>
-      <c r="I90" s="3" t="inlineStr">
+      <c r="I91" s="3" t="inlineStr">
         <is>
           <t>Read main.c / initializations.c, or instrument the boot</t>
         </is>
       </c>
-      <c r="J90" s="3" t="inlineStr">
+      <c r="J91" s="3" t="inlineStr">
         <is>
           <t>Too short and the first samples come from an unsettled ADC.</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>NUMERICAL GUARDS</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="3" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
         <is>
           <t>Low-speed guard</t>
         </is>
       </c>
-      <c r="B92" s="3" t="inlineStr">
+      <c r="B93" s="3" t="inlineStr">
         <is>
           <t>v_eps</t>
         </is>
       </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="C93" s="3" t="inlineStr">
         <is>
           <t>numerical.v_eps</t>
         </is>
       </c>
-      <c r="D92" s="3" t="inlineStr">
+      <c r="D93" s="3" t="inlineStr">
         <is>
           <t>Minimum speed used in slip-angle / slip-ratio denominators.</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
+      <c r="E93" s="4" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="F92" s="3" t="inlineStr">
+      <c r="F93" s="3" t="inlineStr">
         <is>
           <t>m/s</t>
         </is>
       </c>
-      <c r="G92" s="3" t="inlineStr">
+      <c r="G93" s="3" t="inlineStr">
         <is>
           <t>NUMERICAL GUARD</t>
         </is>
       </c>
-      <c r="H92" s="3" t="inlineStr">
+      <c r="H93" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I92" s="3" t="inlineStr">
+      <c r="I93" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J92" s="3" t="inlineStr">
+      <c r="J93" s="3" t="inlineStr">
         <is>
           <t>Below ~0.5 m/s wheel-slip math is untrustworthy — launches are out of scope until reworked.</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="8" t="inlineStr">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>Wheel-speed guard</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>w_eps</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>numerical.w_eps</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>Floor on |wheel speed| when converting a per-motor POWER limit into a torque limit (T_lim = P_peak / max(|omega|, w_eps)).</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>rad/s</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>NUMERICAL GUARD</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>Nothing (numerical)</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>P = T*omega, so at standstill the power limit permits infinite torque. Flooring the divisor caps it at P_peak/w_eps instead, which the per-wheel peak-torque limit then covers. 5 rad/s is ~1.1 m/s of ground speed, below the regen cutoff, so it never binds while the car is actually driving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
         <is>
           <t>Legend:</t>
         </is>
       </c>
-      <c r="B94" s="9" t="inlineStr">
+      <c r="B96" s="9" t="inlineStr">
         <is>
           <t>GREEN value = confirmed for the CURRENT car/driver (or MEASURED). Black = report car, guess, rules, or sim-tuned. Orange status = placeholder/needs attention. Every row is generated from a params.yaml file — edit the number there, not here.</t>
         </is>
@@ -4546,23 +4649,23 @@
   <autoFilter ref="A1:J1"/>
   <mergeCells count="18">
     <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A36:J36"/>
-    <mergeCell ref="A89:J89"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A58:J58"/>
     <mergeCell ref="A9:J9"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A62:J62"/>
-    <mergeCell ref="B94:J94"/>
-    <mergeCell ref="A91:J91"/>
-    <mergeCell ref="A69:J69"/>
-    <mergeCell ref="A29:J29"/>
-    <mergeCell ref="A57:J57"/>
-    <mergeCell ref="A38:J38"/>
+    <mergeCell ref="A70:J70"/>
+    <mergeCell ref="A92:J92"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A39:J39"/>
+    <mergeCell ref="A77:J77"/>
+    <mergeCell ref="A65:J65"/>
+    <mergeCell ref="A43:J43"/>
     <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A81:J81"/>
-    <mergeCell ref="A64:J64"/>
-    <mergeCell ref="A42:J42"/>
-    <mergeCell ref="A76:J76"/>
-    <mergeCell ref="A71:J71"/>
+    <mergeCell ref="A72:J72"/>
+    <mergeCell ref="B96:J96"/>
+    <mergeCell ref="A82:J82"/>
+    <mergeCell ref="A90:J90"/>
+    <mergeCell ref="A63:J63"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/datasheets/FSAE-Sim Parameters.xlsx
+++ b/docs/datasheets/FSAE-Sim Parameters.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J96"/>
+  <dimension ref="A1:J98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3330,16 +3330,61 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>SENSORS — APPS, accelerator pedal position</t>
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>vx estimator time constant</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>tau_vx</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>sensors.vcu.vx_tau</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>How fast the wheel-speed measurement pulls the ground-speed estimate.</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>TUNED (sim)</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>Corner exit at high throttle — shortest tau that still rides out a spin event</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>Short enough that the estimate cannot drift far on the accelerometer alone, long enough that one quantization LSB of wheel speed does not shake the slip ratios a traction guard reads. Applied as dt/(dt+tau), so the filter behaves identically at the 100 Hz VCU rate and the 4 kHz rate verify I4 uses.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>APPS quantization</t>
+          <t>Wheel-speed scatter reference</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -3349,56 +3394,56 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>sensors.throttle_pos.quant_pct</t>
+          <t>sensors.vcu.vx_spread_ref</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Accelerator pedal position resolution.</t>
+          <t>Spread between fastest and slowest wheel (as ground speed) at which the estimator stops trusting the wheels and coasts on the accelerometer.</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>%/LSB</t>
-        </is>
-      </c>
-      <c r="G64" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER — sensor spec</t>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>TUNED (sim)</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>APPS sensor spec</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>Datasheet</t>
+          <t>Track tests — the largest HONEST spread that corner geometry produces</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>Torque request granularity.</t>
+          <t>With four DRIVEN wheels there is no undriven reference left: under power every wheel over-reads, so min(w)*r_wheel is no longer a lower bound on ground speed. Scatter is the signal that says "some corner is slipping". 1.5 m/s sits above the r*track difference real cornering produces (about 0.6 m/s at 1 rad/s) and below a genuine spin event.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>SENSORS — BPS, brake pressure</t>
+          <t>SENSORS — APPS, accelerator pedal position</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>BPS full range</t>
+          <t>APPS quantization</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -3408,22 +3453,22 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>sensors.brake_pressure_sens.range_bar</t>
+          <t>sensors.throttle_pos.quant_pct</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Brake pressure sensor full range.</t>
+          <t>Accelerator pedal position resolution.</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>bar</t>
+          <t>%/LSB</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
@@ -3433,76 +3478,31 @@
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>BPS spec + brake system pressures</t>
+          <t>APPS sensor spec</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>Brake team: line pressure at threshold/full braking</t>
+          <t>Datasheet</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>Sets the pressure that maps to full regen.</t>
+          <t>Torque request granularity.</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>BPS quantization</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>sensors.brake_pressure_sens.quant_bar</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>Brake pressure sensor resolution.</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>bar/LSB</t>
-        </is>
-      </c>
-      <c r="G67" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER — sensor spec</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>BPS spec</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>Regen command granularity.</t>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>SENSORS — BPS, brake pressure</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>BPS actuated threshold</t>
+          <t>BPS full range</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -3512,17 +3512,17 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>sensors.brake_pressure_sens.actuated_bar</t>
+          <t>sensors.brake_pressure_sens.range_bar</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Pressure above which the brake counts as "actuated" for the rules check.</t>
+          <t>Brake pressure sensor full range.</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -3532,29 +3532,29 @@
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — calibration choice</t>
+          <t>PLACEHOLDER — sensor spec</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>Brake system pressures</t>
+          <t>BPS spec + brake system pressures</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>Brake team: line pressure at threshold braking</t>
+          <t>Brake team: line pressure at threshold/full braking</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>Defines "braking" for the EV.4.7 plausibility check.</t>
+          <t>Sets the pressure that maps to full regen.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>Max regen torque</t>
+          <t>BPS quantization</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -3564,56 +3564,101 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>sensors.brake_pressure_sens.t_regen_max</t>
+          <t>sensors.brake_pressure_sens.quant_bar</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Total rear-axle REGEN torque at full brake pressure (both motors).</t>
+          <t>Brake pressure sensor resolution.</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>N*m</t>
+          <t>bar/LSB</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — battery charge limit sets this</t>
+          <t>PLACEHOLDER — sensor spec</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>Allowed charge current -&gt; torque</t>
+          <t>BPS spec</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>Accumulator team: max charge C-rate</t>
+          <t>Datasheet</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>Caps how much "braking" the sim's BPS can command.</t>
+          <t>Regen command granularity.</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>SENSORS — WSS, motor resolver over CAN</t>
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>BPS actuated threshold</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>sensors.brake_pressure_sens.actuated_bar</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Pressure above which the brake counts as "actuated" for the rules check.</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — calibration choice</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>Brake system pressures</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>Brake team: line pressure at threshold braking</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>Defines "braking" for the EV.4.7 plausibility check.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>WSS quantization</t>
+          <t>Max regen torque</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -3623,190 +3668,145 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>sensors.wheel_speed.quant_rpm</t>
+          <t>sensors.brake_pressure_sens.t_regen_max</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Motor-speed resolution over CAN (motor side, before the planetary divide).</t>
+          <t>Total rear-axle REGEN torque at full brake pressure (both motors).</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>250</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>rpm/LSB</t>
+          <t>N*m</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — AMK CAN resolution</t>
+          <t>PLACEHOLDER — battery charge limit sets this</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>AMK CAN speed resolution</t>
+          <t>Allowed charge current -&gt; torque</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>AMK CAN spec</t>
+          <t>Accumulator team: max charge C-rate</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>1 motor rpm is about 1.8 mm/s of ground speed — the resolver-over-CAN path is effectively noise-free wheel speed.</t>
+          <t>Caps how much "braking" the sim's BPS can command.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>SENSORS — SAS, steering angle, and the steering map</t>
+          <t>SENSORS — WSS, motor resolver over CAN</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>Steering map A0 (intercept)</t>
+          <t>WSS quantization</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>A0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>sensors.steering_angle.map_a0</t>
+          <t>sensors.wheel_speed.quant_rpm</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Constant term of the handwheel -&gt; road-wheel polynomial.</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>-0.0797</t>
+          <t>Motor-speed resolution over CAN (motor side, before the planetary divide).</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>deg (intercept)</t>
-        </is>
-      </c>
-      <c r="G73" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT CAR (team chart)</t>
+          <t>rpm/LSB</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — AMK CAN resolution</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>The steering curve including RWheel</t>
+          <t>AMK CAN speed resolution</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>Steering chart / kinematics sweep</t>
+          <t>AMK CAN spec</t>
         </is>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>Subtracted out to center the map; kept so the raw fit stays visible.</t>
+          <t>1 motor rpm is about 1.8 mm/s of ground speed — the resolver-over-CAN path is effectively noise-free wheel speed.</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>Steering map A1 (linear)</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>sensors.steering_angle.map_a1</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>Linear term — the near-center steering ratio.</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>0.31</t>
-        </is>
-      </c>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t>deg/deg</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT CAR (team chart)</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>The steering curve including RWheel</t>
-        </is>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>Steering chart / kinematics sweep</t>
-        </is>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>How the VCU turns the SAS reading into a road-wheel angle.</t>
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>SENSORS — SAS, steering angle, and the steering map</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>Steering map A2 (quadratic)</t>
+          <t>Steering map A0 (intercept)</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A0</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>sensors.steering_angle.map_a2</t>
+          <t>sensors.steering_angle.map_a0</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Quadratic term — the ratio falling off toward lock.</t>
+          <t>Constant term of the handwheel -&gt; road-wheel polynomial.</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>-0.000844</t>
+          <t>-0.0797</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>deg/deg^2</t>
+          <t>deg (intercept)</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>CURRENT CAR (team chart; -844E-04 read as -8.44E-04)</t>
+          <t>CURRENT CAR (team chart)</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
@@ -3821,412 +3821,412 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>Full lock 23 deg is about 103 deg of handwheel.</t>
+          <t>Subtracted out to center the map; kept so the raw fit stays visible.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>SAS quantization</t>
+          <t>Steering map A1 (linear)</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>sensors.steering_angle.quant_deg</t>
+          <t>sensors.steering_angle.map_a1</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Steering-angle sensor resolution, at the handwheel.</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>0.5</t>
+          <t>Linear term — the near-center steering ratio.</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>0.31</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>deg/LSB</t>
-        </is>
-      </c>
-      <c r="G76" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER — sensor spec</t>
+          <t>deg/deg</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (team chart)</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>Sensor spec</t>
+          <t>The steering curve including RWheel</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>Datasheet of the chosen SAS</t>
+          <t>Steering chart / kinematics sweep</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>Steering resolution the VCU actually sees.</t>
+          <t>How the VCU turns the SAS reading into a road-wheel angle.</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>SENSORS — IMU, yaw gyro and accelerometers</t>
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>Steering map A2 (quadratic)</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>sensors.steering_angle.map_a2</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>Quadratic term — the ratio falling off toward lock.</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>-0.000844</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>deg/deg^2</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (team chart; -844E-04 read as -8.44E-04)</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>The steering curve including RWheel</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>Steering chart / kinematics sweep</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>Full lock 23 deg is about 103 deg of handwheel.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>IMU gyro noise (1σ)</t>
+          <t>SAS quantization</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>sigma_g</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>sensors.imu_6axis.gyro_noise_std</t>
+          <t>sensors.steering_angle.quant_deg</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Yaw-gyro 1-sigma noise.</t>
+          <t>Steering-angle sensor resolution, at the handwheel.</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>0.005236</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>rad/s (entered as deg/s, 1 sigma)</t>
+          <t>deg/LSB</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — IMU spec</t>
+          <t>PLACEHOLDER — sensor spec</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>IMU datasheet numbers</t>
+          <t>Sensor spec</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>Chosen IMU's spec sheet</t>
+          <t>Datasheet of the chosen SAS</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>Goes straight into the TV feedback — sets how clean the yaw control can be.</t>
+          <t>Steering resolution the VCU actually sees.</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>IMU gyro bias</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>b_g</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>sensors.imu_6axis.gyro_bias</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>Constant yaw-gyro zero offset.</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>0.001745</t>
-        </is>
-      </c>
-      <c r="F79" s="3" t="inlineStr">
-        <is>
-          <t>rad/s (entered as deg/s)</t>
-        </is>
-      </c>
-      <c r="G79" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER — uncalibrated bias</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>IMU datasheet numbers</t>
-        </is>
-      </c>
-      <c r="I79" s="3" t="inlineStr">
-        <is>
-          <t>Chosen IMU's spec sheet, then a stationary calibration on the car</t>
-        </is>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>Biases the yaw-rate error the TV controller integrates.</t>
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>SENSORS — IMU, yaw gyro and accelerometers</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>VCU gyro low-pass</t>
+          <t>IMU gyro noise (1σ)</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>f_c</t>
+          <t>sigma_g</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>sensors.imu_6axis.lpf_hz</t>
+          <t>sensors.imu_6axis.gyro_noise_std</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>First-order low-pass the VCU applies to the gyro before feedback.</t>
+          <t>Yaw-gyro 1-sigma noise.</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0.005236</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>Hz</t>
+          <t>rad/s (entered as deg/s, 1 sigma)</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — VCU filter choice</t>
+          <t>PLACEHOLDER — IMU spec</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>IMU datasheet numbers</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>Software choice; tune against noise</t>
+          <t>Chosen IMU's spec sheet</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>Trade: more filtering = less dither but more phase lag in the yaw loop.</t>
+          <t>Goes straight into the TV feedback — sets how clean the yaw control can be.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>IMU accel noise</t>
+          <t>IMU gyro bias</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>sigma_a</t>
+          <t>b_g</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>sensors.imu_6axis.accel_noise_std</t>
+          <t>sensors.imu_6axis.gyro_bias</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Accelerometer 1-sigma noise (ax, ay channels).</t>
+          <t>Constant yaw-gyro zero offset.</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.001745</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>m/s^2</t>
+          <t>rad/s (entered as deg/s)</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — IMU spec</t>
+          <t>PLACEHOLDER — uncalibrated bias</t>
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>IMU datasheet</t>
+          <t>IMU datasheet numbers</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>Spec sheet</t>
+          <t>Chosen IMU's spec sheet, then a stationary calibration on the car</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>Feeds future estimation (vx observer, validation logging).</t>
+          <t>Biases the yaw-rate error the TV controller integrates.</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>CONTROLLER CONSTANTS — open-loop s-diff, mirrored from sdiff.c</t>
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>VCU gyro low-pass</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>f_c</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>sensors.imu_6axis.lpf_hz</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>First-order low-pass the VCU applies to the gyro before feedback.</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>Hz</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — VCU filter choice</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>Software choice; tune against noise</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>Trade: more filtering = less dither but more phase lag in the yaw loop.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>Steering ratio (handwheel : road-wheel)</t>
+          <t>IMU accel noise</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>STEERING_RATIO</t>
+          <t>sigma_a</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>controllers.steering_ratio</t>
+          <t>sensors.imu_6axis.accel_noise_std</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Divides handwheel angle down to road-wheel angle in sdiff.c.</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="inlineStr">
-        <is>
-          <t>5.4</t>
+          <t>Accelerometer 1-sigma noise (ax, ay channels).</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G83" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT CAR (sdiff.c STEERING_RATIO)</t>
+          <t>m/s^2</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — IMU spec</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>IMU datasheet</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>Team steering chart (sensors/steering_angle/params.yaml, A1 term)</t>
+          <t>Spec sheet</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>Mirrors the C constant. NOT used by the Python controller — the sim gets its road-wheel angle from the SAS polynomial map in model/sensors/steering_angle/sas.py, which implies ~3.2:1 near center and ~7.5:1 at lock. The flat 5.4 here and that map disagree; the map is the more accurate model of the real linkage.</t>
+          <t>Feeds future estimation (vx observer, validation logging).</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>Steer angle at full derate</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>DELTA_MAX</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="inlineStr">
-        <is>
-          <t>controllers.delta_max</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t>Normalizes steer angle to 0-1 in sdiff.c (delta_norm), clamped at 1.</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>0.03491</t>
-        </is>
-      </c>
-      <c r="F84" s="3" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="G84" s="7" t="inlineStr">
-        <is>
-          <t>SUSPECT — mirrors sdiff.c DELTA_MAX, but see note</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>Confirmation from the VCU team that 2 deg is intended (see note)</t>
-        </is>
-      </c>
-      <c r="I84" s="3" t="inlineStr">
-        <is>
-          <t>dev/sdiff.c on the S-diff branch</t>
-        </is>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>NOT full lock — this is the angle at which the derate SATURATES. At 2 deg of road wheel (about 10.8 deg of handwheel at 5.4:1) delta_norm hits 1.0 and the inner-wheel cut is already at its maximum, so the s-diff behaves close to on/off rather than progressive.</t>
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>CONTROLLER CONSTANTS — open-loop s-diff, mirrored from sdiff.c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>Friction-budget derate gain</t>
+          <t>Steering ratio (handwheel : road-wheel)</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>K_DERATE</t>
+          <t>STEERING_RATIO</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>controllers.k_derate</t>
+          <t>controllers.steering_ratio</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>How much total torque (both wheels) falls off as steer angle rises.</t>
+          <t>Divides handwheel angle down to road-wheel angle in sdiff.c.</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>CURRENT CAR (sdiff.c K_DERATE)</t>
+          <t>CURRENT CAR (sdiff.c STEERING_RATIO)</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
@@ -4246,91 +4246,91 @@
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>dev/sdiff.c on the S-diff branch</t>
+          <t>Team steering chart (sensors/steering_angle/params.yaml, A1 term)</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>Deliberately zeroed in commit 18f9bc7 before the first on-car run: the shared budget cut is OFF, so f = 1.0 always and f_min below is inert. The s-diff currently biases left/right without taking any total power away.</t>
+          <t>Mirrors the C constant. NOT used by the Python controller — the sim gets its road-wheel angle from the SAS polynomial map in model/sensors/steering_angle/sas.py, which implies ~3.2:1 near center and ~7.5:1 at lock. The flat 5.4 here and that map disagree; the map is the more accurate model of the real linkage.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>Inner-wheel derate gain</t>
+          <t>Steer angle at full derate</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>K_INNER</t>
+          <t>DELTA_MAX</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>controllers.k_inner</t>
+          <t>controllers.delta_max</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Torque cut applied to the inner (unloaded) wheel, scaled by delta_norm.</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>0.42</t>
+          <t>Normalizes steer angle to 0-1 in sdiff.c (delta_norm), clamped at 1.</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>0.03491</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT CAR (sdiff.c K_INNER, tuned on car)</t>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>SUSPECT — mirrors sdiff.c DELTA_MAX, but see note</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Confirmation from the VCU team that 2 deg is intended (see note)</t>
         </is>
       </c>
       <c r="I86" s="3" t="inlineStr">
         <is>
-          <t>Tuned on car across the PNR sessions</t>
+          <t>dev/sdiff.c on the S-diff branch</t>
         </is>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>The whole point of the s-diff: keep the inner wheel from spinning up. At full delta_norm the inner wheel gets 58% of the base torque. This is the ONE constant with real on-car provenance — 0.35 (run #1) -&gt; 0.45 (run #2, 3bd6d88) -&gt; 0.42 (run #3, 5df1baf).</t>
+          <t>NOT full lock — this is the angle at which the derate SATURATES. At 2 deg of road wheel (about 10.8 deg of handwheel at 5.4:1) delta_norm hits 1.0 and the inner-wheel cut is already at its maximum, so the s-diff behaves close to on/off rather than progressive.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>Friction-budget floor</t>
+          <t>Friction-budget derate gain</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>F_MIN</t>
+          <t>K_DERATE</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>controllers.f_min</t>
+          <t>controllers.k_derate</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Lowest the shared (both-wheel) torque multiplier can fall to.</t>
+          <t>How much total torque (both wheels) falls off as steer angle rises.</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>CURRENT CAR (sdiff.c F_MIN)</t>
+          <t>CURRENT CAR (sdiff.c K_DERATE)</t>
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr">
@@ -4355,44 +4355,44 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>Floors the k_derate budget cut. INERT while k_derate = 0 — f never leaves 1.0, so this clamp is never reached. It matters again the moment anyone turns the shared derate back on.</t>
+          <t>Deliberately zeroed in commit 18f9bc7 before the first on-car run: the shared budget cut is OFF, so f = 1.0 always and f_min below is inert. The s-diff currently biases left/right without taking any total power away.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>Steering deadband</t>
+          <t>Inner-wheel derate gain</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>DEADBAND</t>
+          <t>K_INNER</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>controllers.deadband</t>
+          <t>controllers.k_inner</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Road-wheel angle band around center treated as "straight" (no split).</t>
+          <t>Torque cut applied to the inner (unloaded) wheel, scaled by delta_norm.</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>0.01745</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
         <is>
-          <t>CURRENT CAR (sdiff.c DEADBAND)</t>
+          <t>CURRENT CAR (sdiff.c K_INNER, tuned on car)</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
@@ -4402,49 +4402,49 @@
       </c>
       <c r="I88" s="3" t="inlineStr">
         <is>
-          <t>dev/sdiff.c on the S-diff branch</t>
+          <t>Tuned on car across the PNR sessions</t>
         </is>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>Stops the inner/outer split from chattering when the driver is nominally straight. 1 deg of road wheel is about 5.4 deg of handwheel, comfortably above the SAS quantization (0.5 deg at the handwheel).</t>
+          <t>The whole point of the s-diff: keep the inner wheel from spinning up. At full delta_norm the inner wheel gets 58% of the base torque. This is the ONE constant with real on-car provenance — 0.35 (run #1) -&gt; 0.45 (run #2, 3bd6d88) -&gt; 0.42 (run #3, 5df1baf).</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>Slew rate</t>
+          <t>Friction-budget floor</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>RATE</t>
+          <t>F_MIN</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>controllers.rate</t>
+          <t>controllers.f_min</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Max speed the friction-budget and left/right multipliers may change, per second.</t>
+          <t>Lowest the shared (both-wheel) torque multiplier can fall to.</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>Hz</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>CURRENT CAR (sdiff.c RATE)</t>
+          <t>CURRENT CAR (sdiff.c F_MIN)</t>
         </is>
       </c>
       <c r="H89" s="3" t="inlineStr">
@@ -4459,187 +4459,291 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>Without slew limiting, torque would jump discontinuously at the deadband edges. At 1.0/s the full 0.42 inner cut takes 0.42 s to apply — far slower than any sensor or loop latency in the stack, which is why loop delay is not modeled here.</t>
+          <t>Floors the k_derate budget cut. INERT while k_derate = 0 — f never leaves 1.0, so this clamp is never reached. It matters again the moment anyone turns the shared derate back on.</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>SOFTWARE-IN-THE-LOOP (sil/)</t>
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>Steering deadband</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>DEADBAND</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>controllers.deadband</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Road-wheel angle band around center treated as "straight" (no split).</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>0.01745</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (sdiff.c DEADBAND)</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>dev/sdiff.c on the S-diff branch</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>Stops the inner/outer split from chattering when the driver is nominally straight. 1 deg of road wheel is about 5.4 deg of handwheel, comfortably above the SAS quantization (0.5 deg at the handwheel).</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>SIL firmware boot time</t>
+          <t>Slew rate</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>RATE</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>sil.boot_s</t>
+          <t>controllers.rate</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>How long the real firmware is left to boot — bench check (55 ms) plus the ADC settle loop (1 s) — before a maneuver's t = 0, measured on the firmware's own clock.</t>
-        </is>
-      </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>1.5</t>
+          <t>Max speed the friction-budget and left/right multipliers may change, per second.</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="G91" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER — from main.c / initializations.c</t>
+          <t>Hz</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (sdiff.c RATE)</t>
         </is>
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>The firmware's true settle time</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>Read main.c / initializations.c, or instrument the boot</t>
+          <t>dev/sdiff.c on the S-diff branch</t>
         </is>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>Too short and the first samples come from an unsettled ADC.</t>
+          <t>Without slew limiting, torque would jump discontinuously at the deadband edges. At 1.0/s the full 0.42 inner cut takes 0.42 s to apply — far slower than any sensor or loop latency in the stack, which is why loop delay is not modeled here.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>NUMERICAL GUARDS</t>
+          <t>SOFTWARE-IN-THE-LOOP (sil/)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
+          <t>SIL firmware boot time</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>sil.boot_s</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>How long the real firmware is left to boot — bench check (55 ms) plus the ADC settle loop (1 s) — before a maneuver's t = 0, measured on the firmware's own clock.</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — from main.c / initializations.c</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>The firmware's true settle time</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>Read main.c / initializations.c, or instrument the boot</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>Too short and the first samples come from an unsettled ADC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>NUMERICAL GUARDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
           <t>Low-speed guard</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>v_eps</t>
         </is>
       </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="C95" s="3" t="inlineStr">
         <is>
           <t>numerical.v_eps</t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr">
+      <c r="D95" s="3" t="inlineStr">
         <is>
           <t>Minimum speed used in slip-angle / slip-ratio denominators.</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
+      <c r="E95" s="4" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="F93" s="3" t="inlineStr">
+      <c r="F95" s="3" t="inlineStr">
         <is>
           <t>m/s</t>
         </is>
       </c>
-      <c r="G93" s="3" t="inlineStr">
+      <c r="G95" s="3" t="inlineStr">
         <is>
           <t>NUMERICAL GUARD</t>
         </is>
       </c>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I93" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J93" s="3" t="inlineStr">
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
         <is>
           <t>Below ~0.5 m/s wheel-slip math is untrustworthy — launches are out of scope until reworked.</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="3" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t>Wheel-speed guard</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B96" s="3" t="inlineStr">
         <is>
           <t>w_eps</t>
         </is>
       </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="C96" s="3" t="inlineStr">
         <is>
           <t>numerical.w_eps</t>
         </is>
       </c>
-      <c r="D94" s="3" t="inlineStr">
+      <c r="D96" s="3" t="inlineStr">
         <is>
           <t>Floor on |wheel speed| when converting a per-motor POWER limit into a torque limit (T_lim = P_peak / max(|omega|, w_eps)).</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
+      <c r="E96" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F94" s="3" t="inlineStr">
+      <c r="F96" s="3" t="inlineStr">
         <is>
           <t>rad/s</t>
         </is>
       </c>
-      <c r="G94" s="3" t="inlineStr">
+      <c r="G96" s="3" t="inlineStr">
         <is>
           <t>NUMERICAL GUARD</t>
         </is>
       </c>
-      <c r="H94" s="3" t="inlineStr">
+      <c r="H96" s="3" t="inlineStr">
         <is>
           <t>Nothing (numerical)</t>
         </is>
       </c>
-      <c r="I94" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
         <is>
           <t>P = T*omega, so at standstill the power limit permits infinite torque. Flooring the divisor caps it at P_peak/w_eps instead, which the per-wheel peak-torque limit then covers. 5 rad/s is ~1.1 m/s of ground speed, below the regen cutoff, so it never binds while the car is actually driving.</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="8" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
         <is>
           <t>Legend:</t>
         </is>
       </c>
-      <c r="B96" s="9" t="inlineStr">
+      <c r="B98" s="9" t="inlineStr">
         <is>
           <t>GREEN value = confirmed for the CURRENT car/driver (or MEASURED). Black = report car, guess, rules, or sim-tuned. Orange status = placeholder/needs attention. Every row is generated from a params.yaml file — edit the number there, not here.</t>
         </is>
@@ -4650,22 +4754,22 @@
   <mergeCells count="18">
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A84:J84"/>
+    <mergeCell ref="A79:J79"/>
+    <mergeCell ref="A94:J94"/>
+    <mergeCell ref="B98:J98"/>
     <mergeCell ref="A58:J58"/>
+    <mergeCell ref="A74:J74"/>
     <mergeCell ref="A9:J9"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A70:J70"/>
+    <mergeCell ref="A67:J67"/>
     <mergeCell ref="A92:J92"/>
     <mergeCell ref="A30:J30"/>
     <mergeCell ref="A39:J39"/>
-    <mergeCell ref="A77:J77"/>
     <mergeCell ref="A65:J65"/>
     <mergeCell ref="A43:J43"/>
     <mergeCell ref="A16:J16"/>
     <mergeCell ref="A72:J72"/>
-    <mergeCell ref="B96:J96"/>
-    <mergeCell ref="A82:J82"/>
-    <mergeCell ref="A90:J90"/>
-    <mergeCell ref="A63:J63"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/datasheets/FSAE-Sim Parameters.xlsx
+++ b/docs/datasheets/FSAE-Sim Parameters.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J98"/>
+  <dimension ref="A1:J113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>CURRENT CAR (four motors fitted, the rear pair commissioned)</t>
+          <t>CURRENT CAR (four motors fitted, one per upright)</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
@@ -4570,103 +4570,148 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>SOFTWARE-IN-THE-LOOP (sil/)</t>
+          <t>CONTROLLER — four-corner torque allocator (AWD, sim design output)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>SIL firmware boot time</t>
+          <t>Base front torque share</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>frac_f0</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>sil.boot_s</t>
+          <t>controllers.awd.frac_front_base</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>How long the real firmware is left to boot — bench check (55 ms) plus the ADC settle loop (1 s) — before a maneuver's t = 0, measured on the firmware's own clock.</t>
+          <t>Front-axle share of total drive torque before any load-transfer correction.</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="G93" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER — from main.c / initializations.c</t>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>TUNED (sim)</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>The firmware's true settle time</t>
+          <t>A front/rear bias decision from the powertrain team</t>
         </is>
       </c>
       <c r="I93" s="3" t="inlineStr">
         <is>
-          <t>Read main.c / initializations.c, or instrument the boot</t>
+          <t>Start near geometry.weight_fraction_front (0.4344), then sweep in the corner tests</t>
         </is>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>Too short and the first samples come from an unsettled ADC.</t>
+          <t>With k_load = 1 this is the whole split at zero acceleration. Slightly ABOVE the static front weight fraction on purpose: mu rises as load falls, so the lightly loaded front axle makes a little more grip per newton than its load share implies (0.8 points at rest, 2.3 at 1.2 g). This offset absorbs most of that.</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>NUMERICAL GUARDS</t>
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>Load-following gain</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>K_LOAD</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>controllers.awd.k_load</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>How strongly the axle split follows the estimated normal-load split.</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>TUNED (sim)</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>Sweep 0 -&gt; 1 across corner_exit and the track matrix</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>frac_front = frac_front_base + k_load*(Fz_front_share - static_front_share). 1.0 = torque tracks axle load; 0 = a fixed split that ignores load transfer. The front share falls 0.434 -&gt; 0.283 at 1 g, so this gain moves ~15 points of the split. It is the biggest single lever in the allocator, and the reason it exists: an even four-way split spins the fronts above ~500 N*m of request.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>Low-speed guard</t>
+          <t>Front share floor</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>v_eps</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>numerical.v_eps</t>
+          <t>controllers.awd.frac_front_min</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Minimum speed used in slip-angle / slip-ratio denominators.</t>
+          <t>Lowest front-axle torque share the allocator may command.</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>NUMERICAL GUARD</t>
+          <t>TUNED (sim)</t>
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr">
@@ -4676,74 +4721,764 @@
       </c>
       <c r="I95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Set above zero so the front inverters never fully idle mid-corner</t>
         </is>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>Below ~0.5 m/s wheel-slip math is untrustworthy — launches are out of scope until reworked.</t>
+          <t>At 1.5 g the load estimate alone asks for 0.21, so this floor is not normally active. It exists so a bad ax estimate can never fully unload the front motors, which would make their resolver speeds useless to the spin guard and to the ground-speed estimator that depends on all four corners disagreeing honestly.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
+          <t>Front share ceiling</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>controllers.awd.frac_front_max</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>Highest front-axle torque share the allocator may command.</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>TUNED (sim)</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>Corner tests; the binding case is regen, not drive</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>The front tires are also making the car's steering force, so their longitudinal budget is smaller than a pure load estimate implies. Under regen the load moves forward and the raw estimate asks for more than this, so this ceiling is the one that actually binds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>Axle-split slew rate</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>controllers.awd.frac_rate</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>Maximum rate of change of the front torque share, per second.</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>Hz</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>TUNED (sim)</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>Fast enough not to lag a throttle step, slow enough not to step the actuators</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>The load estimate follows the torque REQUEST, which the driver can step. Slewing the share (the same slew() the s-diff uses) keeps a pedal step from stepping the front/rear split. At 2.0/s a full 0.44 -&gt; 0.10 swing takes 0.17 s.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>Feedforward accel clamp</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>controllers.awd.ax_est_max</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>Clamp on the feedforward longitudinal-acceleration estimate.</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>m/s^2</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>TUNED (sim) — set near mu_x*g</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>tires.mu0_long * environment.g = 1.58*9.81 = 15.5 m/s^2</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>The estimate believes the REQUEST. Four wheels at peak (1092 N*m) imply 18.9 m/s^2 = 1.93 g, far past what the tires can deliver, and an over-read here over-predicts rearward load transfer and starves the front — the exact failure the allocator exists to avoid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>Left/right load exponent</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>controllers.awd.load_exponent</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>Exponent on each corner's estimated vertical load when sharing that axle's torque.</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>TUNED (sim)</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>Sweep 0 -&gt; 1.5 on corner exit; watch inner-wheel slip against outer-wheel margin</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>share_i = Fz_i^p / sum(Fz^p) within an axle. p = 0 is EXACTLY an open differential (which is how the baseline config is built, and a bit-exact check); p = 1 is load-proportional; p &gt; 1 deliberately over-biases the outer wheel. Chosen over the s-diff's steering-angle law because it needs no deadband — the split fades to 50/50 on its own as lateral acceleration goes away — and because it is correct in right-hand corners without any "left is inner" assumption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>Minimum wheel share</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>controllers.awd.share_min</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>Smallest fraction of an axle's torque one wheel may be given.</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>NUMERICAL GUARD</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>The load estimate clamps a lifted wheel to Fz = 0, which would ask for a 100/0 split the torque limits cannot produce anyway. This keeps a little torque on the unloaded wheel so its speed stays informative to the spin guard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>Lateral-accel feedforward fraction</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>controllers.awd.ay_ff_frac</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>Blend of the kinematic steer estimate into the lateral-acceleration estimate.</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>TUNED (sim)</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>Step steer — raise until the split leads turn-in without overshooting</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>ay = (1-f)*r*vx + f*vx^2*delta/L. The yaw-rate term is truthful but lags the steering input; the kinematic term has no lag but ignores tire compliance. 0.3 buys phase lead at corner entry for little steady-state cost. (This is torque_vectoring.py's yaw reference reused as a LOAD estimator rather than a closed-loop target — a far lower-risk use of the same expression.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>Lateral accel clamp</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>controllers.awd.ay_est_max</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>Clamp on the lateral-acceleration estimate used for load transfer.</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>m/s^2</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>NUMERICAL GUARD</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>r*vx is a product of two estimates; a gyro spike or a vx estimate that has followed four spinning wheels could otherwise saturate the left/right split. 20 m/s^2 (~2 g) is above anything the tires can make, so this never acts in normal running.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>Spin-guard slip threshold</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>kappa_lim</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>controllers.awd.kappa_lim</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>Slip-ratio magnitude at which the per-corner spin guard starts cutting torque.</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>TUNED (sim)</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>MagicFormulaTire.kappa_at_peak() at static load — 0.100 front, 0.097 rear</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>Set just below the tire's own peak-force slip, so the guard acts BEFORE more wheel speed starts making less force. Uses |kappa|, so it also catches a wheel locking under regen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>Spin-guard gain</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>K_SPIN</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>controllers.awd.k_spin</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>Proportional cut applied per unit of slip overshoot past kappa_lim.</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>TUNED (sim)</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" s="3" t="inlineStr">
+        <is>
+          <t>Corner exit at 65-100% throttle; raise until inner-wheel slip is contained</t>
+        </is>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>h = 1 - k_spin*(|kappa| - kappa_lim)/kappa_lim, floored at spin_floor. Proportional only, no integrator, so there is no gain that needs retuning when the VCU rate changes — which is the standing finding in verify section H.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>Spin-guard floor</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>controllers.awd.spin_floor</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>Lowest multiplier the spin guard may apply to one corner.</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>TUNED (sim)</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>Never take a corner to zero: a wheel with no torque gives up its share of drive force AND its slip signal stops being informative. 0.3 keeps both.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>Spin-guard release rate</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>controllers.awd.spin_release_rate</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>Rate at which a cut corner is allowed back to full torque, per second.</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>Hz</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>TUNED (sim)</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>Deliberately asymmetric — the cut is immediate, the restore is rate limited. That is what stops a wheel cycling between spinning and gripping, and it is why the guard needs no state beyond one multiplier per corner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>SOFTWARE-IN-THE-LOOP (sil/)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>SIL firmware boot time</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>sil.boot_s</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>How long the real firmware is left to boot — bench check (55 ms) plus the ADC settle loop (1 s) — before a maneuver's t = 0, measured on the firmware's own clock.</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — from main.c / initializations.c</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>The firmware's true settle time</t>
+        </is>
+      </c>
+      <c r="I108" s="3" t="inlineStr">
+        <is>
+          <t>Read main.c / initializations.c, or instrument the boot</t>
+        </is>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>Too short and the first samples come from an unsettled ADC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>NUMERICAL GUARDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>Low-speed guard</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>v_eps</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>numerical.v_eps</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>Minimum speed used in slip-angle / slip-ratio denominators.</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>NUMERICAL GUARD</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>Below ~0.5 m/s wheel-slip math is untrustworthy — launches are out of scope until reworked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
           <t>Wheel-speed guard</t>
         </is>
       </c>
-      <c r="B96" s="3" t="inlineStr">
+      <c r="B111" s="3" t="inlineStr">
         <is>
           <t>w_eps</t>
         </is>
       </c>
-      <c r="C96" s="3" t="inlineStr">
+      <c r="C111" s="3" t="inlineStr">
         <is>
           <t>numerical.w_eps</t>
         </is>
       </c>
-      <c r="D96" s="3" t="inlineStr">
+      <c r="D111" s="3" t="inlineStr">
         <is>
           <t>Floor on |wheel speed| when converting a per-motor POWER limit into a torque limit (T_lim = P_peak / max(|omega|, w_eps)).</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
+      <c r="E111" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F96" s="3" t="inlineStr">
+      <c r="F111" s="3" t="inlineStr">
         <is>
           <t>rad/s</t>
         </is>
       </c>
-      <c r="G96" s="3" t="inlineStr">
+      <c r="G111" s="3" t="inlineStr">
         <is>
           <t>NUMERICAL GUARD</t>
         </is>
       </c>
-      <c r="H96" s="3" t="inlineStr">
+      <c r="H111" s="3" t="inlineStr">
         <is>
           <t>Nothing (numerical)</t>
         </is>
       </c>
-      <c r="I96" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
         <is>
           <t>P = T*omega, so at standstill the power limit permits infinite torque. Flooring the divisor caps it at P_peak/w_eps instead, which the per-wheel peak-torque limit then covers. 5 rad/s is ~1.1 m/s of ground speed, below the regen cutoff, so it never binds while the car is actually driving.</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="8" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="8" t="inlineStr">
         <is>
           <t>Legend:</t>
         </is>
       </c>
-      <c r="B98" s="9" t="inlineStr">
+      <c r="B113" s="9" t="inlineStr">
         <is>
           <t>GREEN value = confirmed for the CURRENT car/driver (or MEASURED). Black = report car, guess, rules, or sim-tuned. Orange status = placeholder/needs attention. Every row is generated from a params.yaml file — edit the number there, not here.</t>
         </is>
@@ -4751,25 +5486,26 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
-  <mergeCells count="18">
+  <mergeCells count="19">
     <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A84:J84"/>
-    <mergeCell ref="A79:J79"/>
-    <mergeCell ref="A94:J94"/>
-    <mergeCell ref="B98:J98"/>
+    <mergeCell ref="A109:J109"/>
+    <mergeCell ref="A43:J43"/>
+    <mergeCell ref="A72:J72"/>
     <mergeCell ref="A58:J58"/>
-    <mergeCell ref="A74:J74"/>
     <mergeCell ref="A9:J9"/>
-    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A67:J67"/>
     <mergeCell ref="A92:J92"/>
     <mergeCell ref="A30:J30"/>
     <mergeCell ref="A39:J39"/>
+    <mergeCell ref="A107:J107"/>
+    <mergeCell ref="A79:J79"/>
     <mergeCell ref="A65:J65"/>
-    <mergeCell ref="A43:J43"/>
     <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A72:J72"/>
+    <mergeCell ref="B113:J113"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A84:J84"/>
+    <mergeCell ref="A74:J74"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/datasheets/FSAE-Sim Parameters.xlsx
+++ b/docs/datasheets/FSAE-Sim Parameters.xlsx
@@ -1477,7 +1477,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>Not used directly by the physics — it SETS motor peak power below. 4 motors x ~20 kW at 380 V = 80 kW exactly (the 4WD end state); the current 2-rear build tops out at ~40 kW, so the 80 kW cap is unreachable until 4WD.</t>
+          <t>Not used directly by the physics — it SETS motor peak power below. 4 motors x 20 kW at 380 V = 80 kW, which is EXACTLY the rules cap. That leaves the cap zero headroom, so it can never bind: the per-motor power limit is the operative constraint at every speed. See power_cap_total.</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>Caps torque above ~17 m/s (37 mph): at 40 mph only 256 of 273 N*m is available. The 2-rear build tops out around 40 kW.</t>
+          <t>Caps torque above ~17 m/s (37 mph): at 40 mph only 256 of 273 N*m is available. Four motors top out at 80 kW — numerically identical to the rules cap, so THIS per-motor limit is what actually binds, not the cap.</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>Hard ceiling. The sim applies it to mechanical power (no drivetrain losses modeled) — the real car hits it ~10-15% earlier.</t>
+          <t>Hard ceiling. The sim applies it to mechanical power (no drivetrain losses modeled) — the real car hits it ~10-15% earlier. PRESENTLY UNREACHABLE: driven_wheels * motor_power_peak == this value exactly, so the per-motor clip already implies it and the total-cap branch is dead code (verify F16 reports the zero headroom). It becomes live the moment motor_power_peak is revised upward — that number is DERIVED from kit curves by three methods spanning 18.1-20.3 kW — or if driveline losses are ever modelled, since the rules limit is electrical at the accumulator while this one is applied to mechanical power.</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Total rear-axle REGEN torque at full brake pressure (both motors).</t>
+          <t>Total REGEN torque at full brake pressure, across ALL driven wheels.</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -5648,17 +5648,17 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>ω_RL, ω_RR</t>
+          <t>ω_FL, ω_FR, ω_RL, ω_RR</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>states 7–8</t>
+          <t>states 7–10</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Rear wheel rotational speeds — real states with their own differential equation I·ω̇ = T − r·Fx.</t>
+          <t>Wheel rotational speeds, one per corner — real states with their own differential equation I·ω̇ = T − r·Fx.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>T_RL, T_RR</t>
+          <t>T_FL, T_FR, T_RL, T_RR</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>controllers.py output</t>
+          <t>torque_allocator.py output</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Mechanical power at the wheels: T_RL·ω_RL + T_RR·ω_RR.</t>
+          <t>Mechanical power at the wheels: Σ T_i·ω_i over the four wheels.</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
